--- a/restaurant_analytics/data/data.xlsx
+++ b/restaurant_analytics/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cardi\Documents\git-repo\swe_dev\restaurant_analytics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB09943-C97B-49BD-A480-578BBFCB31A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE974AB-1030-4DB3-ADB0-A1A27CA5E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31680" yWindow="1485" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -582,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -716,19 +716,127 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBA3A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBA3A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -748,82 +856,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -851,6 +883,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFBA3A3"/>
       <color rgb="FFFF7C80"/>
       <color rgb="FFFF5050"/>
     </mruColors>
@@ -18806,16 +18839,16 @@
         <v>66</v>
       </c>
       <c r="E661" s="8">
-        <v>35.200000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="F661" s="8">
-        <v>0.20100000000000001</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="G661" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H661" s="8">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="662" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18832,7 +18865,7 @@
         <v>50</v>
       </c>
       <c r="E662" s="8">
-        <v>27</v>
+        <v>27.9</v>
       </c>
       <c r="F662" s="8">
         <v>0</v>
@@ -18841,7 +18874,7 @@
         <v>0</v>
       </c>
       <c r="H662" s="8">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="663" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18858,7 +18891,7 @@
         <v>20</v>
       </c>
       <c r="E663" s="8">
-        <v>33.4</v>
+        <v>31.5</v>
       </c>
       <c r="F663" s="8">
         <v>0</v>
@@ -18867,7 +18900,7 @@
         <v>0</v>
       </c>
       <c r="H663" s="8">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="664" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18884,7 +18917,7 @@
         <v>20</v>
       </c>
       <c r="E664" s="8">
-        <v>41.5</v>
+        <v>40.1</v>
       </c>
       <c r="F664" s="8">
         <v>0</v>
@@ -18893,7 +18926,7 @@
         <v>0</v>
       </c>
       <c r="H664" s="8">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="665" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18910,16 +18943,16 @@
         <v>35</v>
       </c>
       <c r="E665" s="8">
-        <v>25.7</v>
+        <v>32</v>
       </c>
       <c r="F665" s="8">
-        <v>7.0999999999999994E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G665" s="8">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H665" s="8">
-        <v>17.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="666" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18936,10 +18969,10 @@
         <v>11</v>
       </c>
       <c r="E666" s="8">
-        <v>19.2</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F666" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="G666" s="8">
         <v>0.98399999999999999</v>
@@ -18962,16 +18995,16 @@
         <v>81</v>
       </c>
       <c r="E667" s="8">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="F667" s="8">
-        <v>9.8000000000000004E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="G667" s="8">
-        <v>3.9</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H667" s="8">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="668" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18988,16 +19021,16 @@
         <v>174</v>
       </c>
       <c r="E668" s="8">
-        <v>15.3</v>
+        <v>18.7</v>
       </c>
       <c r="F668" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="G668" s="8">
-        <v>0.98399999999999999</v>
+        <v>0</v>
       </c>
       <c r="H668" s="8">
-        <v>14.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="669" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19014,16 +19047,16 @@
         <v>18</v>
       </c>
       <c r="E669" s="8">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="F669" s="8">
-        <v>0.02</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G669" s="8">
         <v>0</v>
       </c>
       <c r="H669" s="8">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="670" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19040,16 +19073,16 @@
         <v>16</v>
       </c>
       <c r="E670" s="8">
-        <v>5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F670" s="8">
         <v>0</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H670" s="8">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="I670" t="s">
         <v>32</v>
@@ -19069,16 +19102,16 @@
         <v>23</v>
       </c>
       <c r="E671" s="8">
-        <v>12.6</v>
+        <v>7.7</v>
       </c>
       <c r="F671" s="8">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G671" s="8">
         <v>0.98399999999999999</v>
       </c>
       <c r="H671" s="8">
-        <v>7.9</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="672" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19095,16 +19128,16 @@
         <v>103</v>
       </c>
       <c r="E672" s="8">
-        <v>26.8</v>
+        <v>25.7</v>
       </c>
       <c r="F672" s="8">
-        <v>7.4999999999999997E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G672" s="8">
         <v>0.98399999999999999</v>
       </c>
       <c r="H672" s="8">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="673" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19121,16 +19154,16 @@
         <v>43</v>
       </c>
       <c r="E673" s="8">
-        <v>17.2</v>
+        <v>20.8</v>
       </c>
       <c r="F673" s="8">
         <v>0</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H673" s="8">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="674" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19147,16 +19180,16 @@
         <v>38</v>
       </c>
       <c r="E674" s="8">
-        <v>-6.3</v>
+        <v>-1.3</v>
       </c>
       <c r="F674" s="8">
         <v>0</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H674" s="8">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="675" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19173,16 +19206,16 @@
         <v>156</v>
       </c>
       <c r="E675" s="8">
-        <v>-0.9</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="F675" s="8">
-        <v>4.2999999999999997E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G675" s="8">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H675" s="8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="676" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19199,16 +19232,16 @@
         <v>40</v>
       </c>
       <c r="E676" s="8">
-        <v>9.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F676" s="8">
-        <v>0.14599999999999999</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="G676" s="8">
-        <v>0.2</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H676" s="8">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="677" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19283,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H679" s="8">
         <v>9.1</v>
@@ -19309,7 +19342,7 @@
         <v>0</v>
       </c>
       <c r="G680" s="8">
-        <v>0.08</v>
+        <v>2.008</v>
       </c>
       <c r="H680" s="8">
         <v>5.8</v>
@@ -19335,7 +19368,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H681" s="8">
         <v>10.4</v>
@@ -19361,7 +19394,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>2.992</v>
       </c>
       <c r="H682" s="8">
         <v>13.2</v>
@@ -19381,7 +19414,7 @@
         <v>62</v>
       </c>
       <c r="E683" s="8">
-        <v>19.399999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F683" s="8">
         <v>0</v>
@@ -19390,7 +19423,7 @@
         <v>0</v>
       </c>
       <c r="H683" s="8">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="684" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19407,16 +19440,16 @@
         <v>51</v>
       </c>
       <c r="E684" s="8">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="F684" s="8">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H684" s="8">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="685" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19433,13 +19466,13 @@
         <v>42</v>
       </c>
       <c r="E685" s="8">
-        <v>20.5</v>
+        <v>21.6</v>
       </c>
       <c r="F685" s="8">
         <v>0</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H685" s="8">
         <v>7.3</v>
@@ -19459,7 +19492,7 @@
         <v>38</v>
       </c>
       <c r="E686" s="8">
-        <v>17.8</v>
+        <v>21.6</v>
       </c>
       <c r="F686" s="8">
         <v>0</v>
@@ -19468,7 +19501,7 @@
         <v>0</v>
       </c>
       <c r="H686" s="8">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="687" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19485,16 +19518,16 @@
         <v>29</v>
       </c>
       <c r="E687" s="8">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="F687" s="8">
-        <v>0</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G687" s="8">
         <v>0</v>
       </c>
       <c r="H687" s="8">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="688" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19511,16 +19544,16 @@
         <v>140</v>
       </c>
       <c r="E688" s="8">
-        <v>24</v>
+        <v>31.1</v>
       </c>
       <c r="F688" s="8">
-        <v>0</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="G688" s="8">
         <v>0</v>
       </c>
       <c r="H688" s="8">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="689" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19534,22 +19567,19 @@
         <v>46060</v>
       </c>
       <c r="D689" s="13">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="E689" s="8">
-        <v>22.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="F689" s="8">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G689" s="8">
         <v>0</v>
       </c>
       <c r="H689" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="J689" s="8">
-        <v>12.49</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="690" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19563,25 +19593,22 @@
         <v>46061</v>
       </c>
       <c r="D690" s="13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E690" s="8">
-        <v>27</v>
+        <v>25.3</v>
       </c>
       <c r="F690" s="8">
-        <v>0</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G690" s="8">
         <v>0</v>
       </c>
       <c r="H690" s="8">
-        <v>10.5</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I690" t="s">
         <v>33</v>
-      </c>
-      <c r="J690" s="8">
-        <v>11.16</v>
       </c>
     </row>
     <row r="691" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19595,10 +19622,10 @@
         <v>46062</v>
       </c>
       <c r="D691" s="13">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E691" s="8">
-        <v>39</v>
+        <v>31.3</v>
       </c>
       <c r="F691" s="8">
         <v>0</v>
@@ -19607,10 +19634,7 @@
         <v>0</v>
       </c>
       <c r="H691" s="8">
-        <v>10.4</v>
-      </c>
-      <c r="J691" s="8">
-        <v>4.835</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="692" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19624,10 +19648,10 @@
         <v>46063</v>
       </c>
       <c r="D692" s="13">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E692" s="8">
-        <v>40</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="F692" s="8">
         <v>0</v>
@@ -19636,10 +19660,7 @@
         <v>0</v>
       </c>
       <c r="H692" s="8">
-        <v>11</v>
-      </c>
-      <c r="J692" s="8">
-        <v>6.9499999999999993</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="693" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19653,10 +19674,10 @@
         <v>46064</v>
       </c>
       <c r="D693" s="13">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E693" s="8">
-        <v>33.5</v>
+        <v>31.1</v>
       </c>
       <c r="F693" s="8">
         <v>0</v>
@@ -19665,10 +19686,7 @@
         <v>0</v>
       </c>
       <c r="H693" s="8">
-        <v>9</v>
-      </c>
-      <c r="J693" s="8">
-        <v>5.1749999999999998</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="694" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19682,10 +19700,10 @@
         <v>46065</v>
       </c>
       <c r="D694" s="13">
-        <v>48.5</v>
+        <v>37</v>
       </c>
       <c r="E694" s="8">
-        <v>29</v>
+        <v>31.3</v>
       </c>
       <c r="F694" s="8">
         <v>0</v>
@@ -19694,10 +19712,7 @@
         <v>0</v>
       </c>
       <c r="H694" s="8">
-        <v>7</v>
-      </c>
-      <c r="J694" s="8">
-        <v>5.0549999999999997</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="695" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19711,10 +19726,10 @@
         <v>46066</v>
       </c>
       <c r="D695" s="13">
-        <v>88.5</v>
+        <v>199</v>
       </c>
       <c r="E695" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F695" s="8">
         <v>0</v>
@@ -19723,10 +19738,7 @@
         <v>0</v>
       </c>
       <c r="H695" s="8">
-        <v>5</v>
-      </c>
-      <c r="J695" s="8">
-        <v>8.1950000000000003</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="696" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19740,10 +19752,10 @@
         <v>46067</v>
       </c>
       <c r="D696" s="13">
-        <v>186.5</v>
+        <v>283</v>
       </c>
       <c r="E696" s="8">
-        <v>28</v>
+        <v>36.9</v>
       </c>
       <c r="F696" s="8">
         <v>0</v>
@@ -19752,13 +19764,10 @@
         <v>0</v>
       </c>
       <c r="H696" s="8">
-        <v>9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I696" s="40" t="s">
         <v>34</v>
-      </c>
-      <c r="J696" s="8">
-        <v>35.335000000000001</v>
       </c>
     </row>
     <row r="697" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19772,10 +19781,10 @@
         <v>46068</v>
       </c>
       <c r="D697" s="13">
-        <v>43.5</v>
+        <v>91</v>
       </c>
       <c r="E697" s="8">
-        <v>35.5</v>
+        <v>44.2</v>
       </c>
       <c r="F697" s="8">
         <v>0.03</v>
@@ -19784,10 +19793,7 @@
         <v>0</v>
       </c>
       <c r="H697" s="8">
-        <v>10</v>
-      </c>
-      <c r="J697" s="8">
-        <v>3.8650000000000002</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="698" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19801,25 +19807,22 @@
         <v>46069</v>
       </c>
       <c r="D698" s="13">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E698" s="8">
-        <v>40</v>
+        <v>48.9</v>
       </c>
       <c r="F698" s="8">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G698" s="8">
         <v>0.19</v>
       </c>
       <c r="H698" s="8">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="I698" s="40" t="s">
         <v>35</v>
-      </c>
-      <c r="J698" s="8">
-        <v>9.754999999999999</v>
       </c>
     </row>
     <row r="699" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19836,16 +19839,16 @@
         <v>44</v>
       </c>
       <c r="E699" s="8">
-        <v>41</v>
+        <v>48.4</v>
       </c>
       <c r="F699" s="8">
-        <v>0.51</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G699" s="8">
         <v>0</v>
       </c>
       <c r="H699" s="8">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J699" s="8">
         <v>8.6750000000000007</v>
@@ -19865,7 +19868,7 @@
         <v>41</v>
       </c>
       <c r="E700" s="8">
-        <v>39</v>
+        <v>53.6</v>
       </c>
       <c r="F700" s="8">
         <v>0</v>
@@ -19874,7 +19877,7 @@
         <v>0.04</v>
       </c>
       <c r="H700" s="8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I700" s="40" t="s">
         <v>37</v>
@@ -19897,7 +19900,7 @@
         <v>55</v>
       </c>
       <c r="E701" s="8">
-        <v>27.5</v>
+        <v>45.3</v>
       </c>
       <c r="F701" s="8">
         <v>0</v>
@@ -19906,7 +19909,7 @@
         <v>0</v>
       </c>
       <c r="H701" s="8">
-        <v>15</v>
+        <v>9.1</v>
       </c>
       <c r="J701" s="8">
         <v>6.1549999999999994</v>
@@ -19926,7 +19929,7 @@
         <v>91</v>
       </c>
       <c r="E702" s="8">
-        <v>20.5</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="F702" s="8">
         <v>0.06</v>
@@ -19935,7 +19938,7 @@
         <v>1.2</v>
       </c>
       <c r="H702" s="8">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I702" s="40" t="s">
         <v>10</v>
@@ -19958,7 +19961,7 @@
         <v>128.5</v>
       </c>
       <c r="E703" s="8">
-        <v>19.5</v>
+        <v>31.6</v>
       </c>
       <c r="F703" s="8">
         <v>0</v>
@@ -19967,7 +19970,7 @@
         <v>0</v>
       </c>
       <c r="H703" s="8">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="J703" s="8">
         <v>15.030000000000001</v>
@@ -19987,7 +19990,7 @@
         <v>41.5</v>
       </c>
       <c r="E704" s="8">
-        <v>19</v>
+        <v>28.4</v>
       </c>
       <c r="F704" s="8">
         <v>0</v>
@@ -20016,7 +20019,7 @@
         <v>42</v>
       </c>
       <c r="E705" s="8">
-        <v>18.5</v>
+        <v>28.8</v>
       </c>
       <c r="F705" s="8">
         <v>0</v>
@@ -20025,7 +20028,7 @@
         <v>0</v>
       </c>
       <c r="H705" s="8">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="J705" s="8">
         <v>6.26</v>
@@ -20045,7 +20048,7 @@
         <v>45.5</v>
       </c>
       <c r="E706" s="8">
-        <v>19.5</v>
+        <v>31.8</v>
       </c>
       <c r="F706" s="8">
         <v>0</v>
@@ -20054,7 +20057,7 @@
         <v>0</v>
       </c>
       <c r="H706" s="8">
-        <v>5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J706" s="8">
         <v>6.83</v>
@@ -20387,10 +20390,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A717">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20401,7 +20404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8670AF5D-84FB-432F-8F14-677D63D19C50}">
-  <dimension ref="A1:U269"/>
+  <dimension ref="A1:X269"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -33386,54 +33389,54 @@
         <v>37</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="63">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A224" s="13">
         <v>41</v>
       </c>
-      <c r="B224" s="64">
+      <c r="B224" s="21">
         <v>46049</v>
       </c>
-      <c r="C224" s="65">
+      <c r="C224">
         <v>54</v>
       </c>
-      <c r="D224" s="65">
+      <c r="D224">
         <v>44</v>
       </c>
-      <c r="E224" s="65">
+      <c r="E224">
         <v>70</v>
       </c>
-      <c r="F224" s="65">
+      <c r="F224">
         <v>32</v>
       </c>
-      <c r="G224" s="65">
+      <c r="G224">
         <v>63</v>
       </c>
-      <c r="H224" s="65">
+      <c r="H224">
         <v>32</v>
       </c>
-      <c r="I224" s="65">
+      <c r="I224">
         <v>47</v>
       </c>
-      <c r="J224" s="65">
+      <c r="J224">
         <v>36</v>
       </c>
-      <c r="K224" s="65">
+      <c r="K224">
         <v>69</v>
       </c>
-      <c r="L224" s="65">
+      <c r="L224">
         <v>42</v>
       </c>
-      <c r="M224" s="65">
+      <c r="M224">
         <v>44</v>
       </c>
-      <c r="N224" s="65">
+      <c r="N224">
         <v>41</v>
       </c>
-      <c r="O224" s="66">
+      <c r="O224" s="19">
         <f t="shared" si="38"/>
         <v>47</v>
       </c>
-      <c r="P224" s="66">
+      <c r="P224" s="19">
         <f t="shared" si="39"/>
         <v>12.2</v>
       </c>
@@ -33445,14 +33448,14 @@
         <f t="shared" ref="S224:S234" si="46">O224/A224</f>
         <v>1.1463414634146341</v>
       </c>
-      <c r="T224" s="65">
+      <c r="T224">
         <v>43</v>
       </c>
-      <c r="U224" s="65">
+      <c r="U224">
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A225" s="13">
         <v>32</v>
       </c>
@@ -33518,7 +33521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A226" s="13">
         <v>85</v>
       </c>
@@ -33584,7 +33587,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A227" s="13">
         <v>111</v>
       </c>
@@ -33649,8 +33652,10 @@
       <c r="U227">
         <v>94</v>
       </c>
-    </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W227" s="66"/>
+      <c r="X227" s="66"/>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A228" s="13">
         <v>163</v>
       </c>
@@ -33715,8 +33720,10 @@
       <c r="U228">
         <v>115</v>
       </c>
-    </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W228" s="66"/>
+      <c r="X228" s="66"/>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A229" s="13">
         <v>62</v>
       </c>
@@ -33781,8 +33788,10 @@
       <c r="U229">
         <v>34</v>
       </c>
-    </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W229" s="66"/>
+      <c r="X229" s="66"/>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A230" s="13">
         <v>51</v>
       </c>
@@ -33847,55 +33856,57 @@
       <c r="U230">
         <v>35</v>
       </c>
-    </row>
-    <row r="231" spans="1:21" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W230" s="66"/>
+      <c r="X230" s="66"/>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A231" s="13">
         <v>42</v>
       </c>
-      <c r="B231" s="64">
+      <c r="B231" s="21">
         <v>46056</v>
       </c>
-      <c r="C231" s="65">
+      <c r="C231">
         <v>46</v>
       </c>
-      <c r="D231" s="65">
+      <c r="D231">
         <v>45</v>
       </c>
-      <c r="E231" s="65">
+      <c r="E231">
         <v>56</v>
       </c>
-      <c r="F231" s="65">
+      <c r="F231">
         <v>37</v>
       </c>
-      <c r="G231" s="65">
+      <c r="G231">
         <v>50</v>
       </c>
-      <c r="H231" s="65">
+      <c r="H231">
         <v>50</v>
       </c>
-      <c r="I231" s="65">
+      <c r="I231">
         <v>49</v>
       </c>
-      <c r="J231" s="65">
+      <c r="J231">
         <v>36</v>
       </c>
-      <c r="K231" s="65">
+      <c r="K231">
         <v>48</v>
       </c>
-      <c r="L231" s="65">
+      <c r="L231">
         <v>46</v>
       </c>
-      <c r="M231" s="65">
+      <c r="M231">
         <v>53</v>
       </c>
-      <c r="N231" s="65">
+      <c r="N231">
         <v>45</v>
       </c>
-      <c r="O231" s="66">
+      <c r="O231" s="19">
         <f t="shared" si="38"/>
         <v>47</v>
       </c>
-      <c r="P231" s="66">
+      <c r="P231" s="19">
         <f t="shared" si="39"/>
         <v>5.7</v>
       </c>
@@ -33907,14 +33918,16 @@
         <f t="shared" si="46"/>
         <v>1.1190476190476191</v>
       </c>
-      <c r="T231" s="65">
+      <c r="T231">
         <v>53</v>
       </c>
-      <c r="U231" s="65">
+      <c r="U231">
         <v>40</v>
       </c>
-    </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W231" s="66"/>
+      <c r="X231" s="66"/>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A232" s="13">
         <v>38</v>
       </c>
@@ -33979,8 +33992,10 @@
       <c r="U232">
         <v>42</v>
       </c>
-    </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W232" s="66"/>
+      <c r="X232" s="66"/>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A233" s="13">
         <v>29</v>
       </c>
@@ -34045,8 +34060,10 @@
       <c r="U233">
         <v>47</v>
       </c>
-    </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W233" s="66"/>
+      <c r="X233" s="66"/>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A234" s="13">
         <v>140</v>
       </c>
@@ -34111,63 +34128,81 @@
       <c r="U234">
         <v>107</v>
       </c>
-    </row>
-    <row r="235" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B235" s="26">
+      <c r="W234" s="66"/>
+      <c r="X234" s="66"/>
+    </row>
+    <row r="235" spans="1:24" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="13">
+        <v>186</v>
+      </c>
+      <c r="B235" s="64">
         <v>46060</v>
       </c>
-      <c r="C235" s="27">
+      <c r="C235" s="63">
         <v>121</v>
       </c>
-      <c r="D235" s="27">
+      <c r="D235" s="63">
         <v>118</v>
       </c>
-      <c r="E235" s="27">
+      <c r="E235" s="63">
         <v>117</v>
       </c>
-      <c r="F235" s="27">
+      <c r="F235" s="63">
         <v>110</v>
       </c>
-      <c r="G235" s="27">
+      <c r="G235" s="63">
         <v>114</v>
       </c>
-      <c r="H235" s="27">
+      <c r="H235" s="63">
         <v>115</v>
       </c>
-      <c r="I235" s="27">
+      <c r="I235" s="63">
         <v>129</v>
       </c>
-      <c r="J235" s="27">
+      <c r="J235" s="63">
         <v>126</v>
       </c>
-      <c r="K235" s="27">
+      <c r="K235" s="63">
         <v>141</v>
       </c>
-      <c r="L235" s="27">
+      <c r="L235" s="63">
         <v>133</v>
       </c>
-      <c r="M235" s="27">
+      <c r="M235" s="63">
         <v>148</v>
       </c>
-      <c r="N235" s="27">
+      <c r="N235" s="63">
         <v>132</v>
       </c>
-      <c r="O235" s="28">
+      <c r="O235" s="65">
         <f t="shared" si="38"/>
         <v>126</v>
       </c>
-      <c r="P235" s="28">
+      <c r="P235" s="65">
         <f t="shared" si="39"/>
         <v>10.98</v>
       </c>
-      <c r="T235" s="27">
+      <c r="R235" s="25">
+        <f t="shared" ref="R235:R244" si="47">O235-A235</f>
+        <v>-60</v>
+      </c>
+      <c r="S235">
+        <f t="shared" ref="S235:S244" si="48">O235/A235</f>
+        <v>0.67741935483870963</v>
+      </c>
+      <c r="T235" s="63">
         <v>140</v>
       </c>
-      <c r="U235" s="27">
+      <c r="U235" s="63">
         <v>125</v>
       </c>
-    </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W235" s="66"/>
+      <c r="X235" s="66"/>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A236" s="13">
+        <v>0</v>
+      </c>
       <c r="B236" s="21">
         <v>46061</v>
       </c>
@@ -34215,14 +34250,27 @@
         <f t="shared" si="39"/>
         <v>11.36</v>
       </c>
+      <c r="R236" s="25">
+        <f t="shared" si="47"/>
+        <v>35</v>
+      </c>
+      <c r="S236">
+        <f>O236/(A236+1)</f>
+        <v>35</v>
+      </c>
       <c r="T236">
         <v>49</v>
       </c>
       <c r="U236">
         <v>28</v>
       </c>
-    </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W236" s="66"/>
+      <c r="X236" s="66"/>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A237" s="13">
+        <v>30</v>
+      </c>
       <c r="B237" s="21">
         <v>46062</v>
       </c>
@@ -34270,14 +34318,27 @@
         <f t="shared" si="39"/>
         <v>4.76</v>
       </c>
+      <c r="R237" s="25">
+        <f t="shared" si="47"/>
+        <v>14</v>
+      </c>
+      <c r="S237">
+        <f t="shared" si="48"/>
+        <v>1.4666666666666666</v>
+      </c>
       <c r="T237">
         <v>52</v>
       </c>
       <c r="U237">
         <v>42</v>
       </c>
-    </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W237" s="66"/>
+      <c r="X237" s="66"/>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A238" s="13">
+        <v>26</v>
+      </c>
       <c r="B238" s="21">
         <v>46063</v>
       </c>
@@ -34325,14 +34386,27 @@
         <f t="shared" si="39"/>
         <v>8.02</v>
       </c>
+      <c r="R238" s="25">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="S238">
+        <f t="shared" si="48"/>
+        <v>1.7692307692307692</v>
+      </c>
       <c r="T238">
         <v>52</v>
       </c>
       <c r="U238">
         <v>40</v>
       </c>
-    </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W238" s="66"/>
+      <c r="X238" s="66"/>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A239" s="13">
+        <v>59</v>
+      </c>
       <c r="B239" s="21">
         <v>46064</v>
       </c>
@@ -34380,14 +34454,27 @@
         <f t="shared" si="39"/>
         <v>4.8499999999999996</v>
       </c>
+      <c r="R239" s="25">
+        <f t="shared" si="47"/>
+        <v>-15</v>
+      </c>
+      <c r="S239">
+        <f t="shared" si="48"/>
+        <v>0.74576271186440679</v>
+      </c>
       <c r="T239">
         <v>49</v>
       </c>
       <c r="U239">
         <v>41</v>
       </c>
-    </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="W239" s="66"/>
+      <c r="X239" s="66"/>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A240" s="13">
+        <v>37</v>
+      </c>
       <c r="B240" s="21">
         <v>46065</v>
       </c>
@@ -34435,14 +34522,27 @@
         <f t="shared" si="39"/>
         <v>4.08</v>
       </c>
+      <c r="R240" s="25">
+        <f t="shared" si="47"/>
+        <v>10</v>
+      </c>
+      <c r="S240">
+        <f t="shared" si="48"/>
+        <v>1.2702702702702702</v>
+      </c>
       <c r="T240">
         <v>51</v>
       </c>
       <c r="U240">
         <v>45</v>
       </c>
-    </row>
-    <row r="241" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W240" s="66"/>
+      <c r="X240" s="66"/>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A241" s="13">
+        <v>199</v>
+      </c>
       <c r="B241" s="21">
         <v>46066</v>
       </c>
@@ -34490,14 +34590,27 @@
         <f t="shared" si="39"/>
         <v>9.36</v>
       </c>
+      <c r="R241" s="25">
+        <f t="shared" si="47"/>
+        <v>-111</v>
+      </c>
+      <c r="S241">
+        <f t="shared" si="48"/>
+        <v>0.44221105527638194</v>
+      </c>
       <c r="T241">
         <v>85</v>
       </c>
       <c r="U241">
         <v>85</v>
       </c>
-    </row>
-    <row r="242" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W241" s="66"/>
+      <c r="X241" s="66"/>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A242" s="13">
+        <v>283</v>
+      </c>
       <c r="B242" s="21">
         <v>46067</v>
       </c>
@@ -34545,14 +34658,27 @@
         <f t="shared" si="39"/>
         <v>30.86</v>
       </c>
+      <c r="R242" s="25">
+        <f t="shared" si="47"/>
+        <v>-93</v>
+      </c>
+      <c r="S242">
+        <f t="shared" si="48"/>
+        <v>0.67137809187279152</v>
+      </c>
       <c r="T242">
         <v>187</v>
       </c>
       <c r="U242">
         <v>179</v>
       </c>
-    </row>
-    <row r="243" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W242" s="66"/>
+      <c r="X242" s="66"/>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A243" s="13">
+        <v>91</v>
+      </c>
       <c r="B243" s="21">
         <v>46068</v>
       </c>
@@ -34600,14 +34726,27 @@
         <f t="shared" si="39"/>
         <v>4.17</v>
       </c>
+      <c r="R243" s="25">
+        <f t="shared" si="47"/>
+        <v>-47</v>
+      </c>
+      <c r="S243">
+        <f t="shared" si="48"/>
+        <v>0.48351648351648352</v>
+      </c>
       <c r="T243">
         <v>50</v>
       </c>
       <c r="U243">
         <v>44</v>
       </c>
-    </row>
-    <row r="244" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W243" s="66"/>
+      <c r="X243" s="66"/>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A244" s="13">
+        <v>35</v>
+      </c>
       <c r="B244" s="21">
         <v>46069</v>
       </c>
@@ -34655,162 +34794,178 @@
         <f t="shared" si="39"/>
         <v>8.1</v>
       </c>
+      <c r="R244" s="25">
+        <f t="shared" si="47"/>
+        <v>11</v>
+      </c>
+      <c r="S244">
+        <f t="shared" si="48"/>
+        <v>1.3142857142857143</v>
+      </c>
       <c r="T244">
         <v>54</v>
       </c>
       <c r="U244">
         <v>40</v>
       </c>
-    </row>
-    <row r="245" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B245" s="21">
+      <c r="W244" s="66"/>
+      <c r="X244" s="66"/>
+    </row>
+    <row r="245" spans="1:24" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="26">
         <v>46070</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="27">
+        <v>74</v>
+      </c>
+      <c r="D245" s="27">
+        <v>44</v>
+      </c>
+      <c r="E245" s="27">
+        <v>59</v>
+      </c>
+      <c r="F245" s="27">
+        <v>40</v>
+      </c>
+      <c r="G245" s="27">
+        <v>44</v>
+      </c>
+      <c r="H245" s="27">
+        <v>28</v>
+      </c>
+      <c r="I245" s="27">
+        <v>65</v>
+      </c>
+      <c r="J245" s="27">
+        <v>44</v>
+      </c>
+      <c r="K245" s="27">
+        <v>60</v>
+      </c>
+      <c r="L245" s="27">
         <v>46</v>
       </c>
-      <c r="D245">
-        <v>43</v>
-      </c>
-      <c r="E245">
+      <c r="M245" s="27">
         <v>61</v>
       </c>
-      <c r="F245">
-        <v>31</v>
-      </c>
-      <c r="G245">
-        <v>49</v>
-      </c>
-      <c r="H245">
-        <v>28</v>
-      </c>
-      <c r="I245">
+      <c r="N245" s="27">
+        <v>46</v>
+      </c>
+      <c r="O245" s="28">
+        <f>ROUND(AVERAGE(C245:N245,T245:U245),0)</f>
         <v>50</v>
       </c>
-      <c r="J245">
-        <v>39</v>
-      </c>
-      <c r="K245">
-        <v>48</v>
-      </c>
-      <c r="L245">
-        <v>45</v>
-      </c>
-      <c r="M245">
-        <v>53</v>
-      </c>
-      <c r="N245">
-        <v>42</v>
-      </c>
-      <c r="O245" s="19">
-        <f t="shared" si="38"/>
-        <v>45</v>
-      </c>
-      <c r="P245" s="19">
+      <c r="P245" s="28">
         <f t="shared" si="39"/>
-        <v>8.5</v>
-      </c>
-      <c r="T245">
-        <v>54</v>
-      </c>
-      <c r="U245">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="246" spans="2:21" x14ac:dyDescent="0.25">
+        <v>11.68</v>
+      </c>
+      <c r="T245" s="27">
+        <v>51</v>
+      </c>
+      <c r="U245" s="27">
+        <v>41</v>
+      </c>
+      <c r="W245" s="67"/>
+      <c r="X245" s="67"/>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B246" s="21">
         <v>46071</v>
       </c>
       <c r="C246">
+        <v>48</v>
+      </c>
+      <c r="D246">
+        <v>54</v>
+      </c>
+      <c r="E246">
+        <v>66</v>
+      </c>
+      <c r="F246">
+        <v>49</v>
+      </c>
+      <c r="G246">
+        <v>43</v>
+      </c>
+      <c r="H246">
+        <v>35</v>
+      </c>
+      <c r="I246">
         <v>47</v>
       </c>
-      <c r="D246">
-        <v>39</v>
-      </c>
-      <c r="E246">
-        <v>49</v>
-      </c>
-      <c r="F246">
-        <v>30</v>
-      </c>
-      <c r="G246">
-        <v>49</v>
-      </c>
-      <c r="H246">
-        <v>37</v>
-      </c>
-      <c r="I246">
-        <v>48</v>
-      </c>
       <c r="J246">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K246">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L246">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M246">
         <v>46</v>
       </c>
       <c r="N246">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="O246" s="19">
         <f t="shared" si="38"/>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="P246" s="19">
         <f t="shared" si="39"/>
-        <v>5.45</v>
+        <v>6.69</v>
       </c>
       <c r="T246">
+        <v>54</v>
+      </c>
+      <c r="U246">
         <v>47</v>
       </c>
-      <c r="U246">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="247" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W246" s="37">
+        <f>SUMPRODUCT(C246:N246,$C$264:$N$264)/SUM($C$264:$N$264)</f>
+        <v>49.474201870364396</v>
+      </c>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B247" s="21">
         <v>46072</v>
       </c>
       <c r="C247">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D247">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E247">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F247">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G247">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H247">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I247">
         <v>61</v>
       </c>
       <c r="J247">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K247">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L247">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M247">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="N247">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O247" s="19">
         <f t="shared" si="38"/>
@@ -34818,164 +34973,176 @@
       </c>
       <c r="P247" s="19">
         <f t="shared" si="39"/>
-        <v>4.75</v>
+        <v>5.56</v>
       </c>
       <c r="T247">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U247">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="248" spans="2:21" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="W247" s="37">
+        <f t="shared" ref="W247:W263" si="49">SUMPRODUCT(C247:N247,$C$264:$N$264)/SUM($C$264:$N$264)</f>
+        <v>53.171138342470172</v>
+      </c>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B248" s="21">
         <v>46073</v>
       </c>
       <c r="C248">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="D248">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E248">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="F248">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G248">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H248">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I248">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="J248">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K248">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="L248">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="M248">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="N248">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="O248" s="19">
         <f t="shared" si="38"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P248" s="19">
         <f t="shared" si="39"/>
-        <v>21.79</v>
+        <v>16</v>
       </c>
       <c r="T248">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="U248">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="249" spans="2:21" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="W248" s="37">
+        <f t="shared" si="49"/>
+        <v>91.361141567236373</v>
+      </c>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B249" s="21">
         <v>46074</v>
       </c>
       <c r="C249">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D249">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E249">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F249">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G249">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H249">
+        <v>106</v>
+      </c>
+      <c r="I249">
+        <v>120</v>
+      </c>
+      <c r="J249">
+        <v>139</v>
+      </c>
+      <c r="K249">
         <v>117</v>
       </c>
-      <c r="I249">
-        <v>128</v>
-      </c>
-      <c r="J249">
+      <c r="L249">
+        <v>133</v>
+      </c>
+      <c r="M249">
+        <v>85</v>
+      </c>
+      <c r="N249">
         <v>126</v>
-      </c>
-      <c r="K249">
-        <v>140</v>
-      </c>
-      <c r="L249">
-        <v>136</v>
-      </c>
-      <c r="M249">
-        <v>153</v>
-      </c>
-      <c r="N249">
-        <v>133</v>
       </c>
       <c r="O249" s="19">
         <f t="shared" si="38"/>
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="P249" s="19">
         <f t="shared" si="39"/>
-        <v>13.17</v>
+        <v>16.86</v>
       </c>
       <c r="T249">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="U249">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="250" spans="2:21" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="W249" s="37">
+        <f t="shared" si="49"/>
+        <v>115.69145436955819</v>
+      </c>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B250" s="21">
         <v>46075</v>
       </c>
       <c r="C250">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D250">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E250">
         <v>46</v>
       </c>
       <c r="F250">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G250">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H250">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I250">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J250">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K250">
         <v>47</v>
       </c>
       <c r="L250">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M250">
         <v>46</v>
       </c>
       <c r="N250">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O250" s="19">
         <f t="shared" si="38"/>
@@ -34983,76 +35150,84 @@
       </c>
       <c r="P250" s="19">
         <f t="shared" si="39"/>
-        <v>6.67</v>
+        <v>5.19</v>
       </c>
       <c r="T250">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="U250">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="251" spans="2:21" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W250" s="37">
+        <f t="shared" si="49"/>
+        <v>41.979297000967421</v>
+      </c>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B251" s="21">
         <v>46076</v>
       </c>
       <c r="C251">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D251">
+        <v>40</v>
+      </c>
+      <c r="E251">
+        <v>59</v>
+      </c>
+      <c r="F251">
+        <v>38</v>
+      </c>
+      <c r="G251">
+        <v>39</v>
+      </c>
+      <c r="H251">
+        <v>26</v>
+      </c>
+      <c r="I251">
+        <v>54</v>
+      </c>
+      <c r="J251">
         <v>41</v>
-      </c>
-      <c r="E251">
-        <v>48</v>
-      </c>
-      <c r="F251">
-        <v>36</v>
-      </c>
-      <c r="G251">
-        <v>50</v>
-      </c>
-      <c r="H251">
-        <v>28</v>
-      </c>
-      <c r="I251">
-        <v>45</v>
-      </c>
-      <c r="J251">
-        <v>38</v>
       </c>
       <c r="K251">
         <v>47</v>
       </c>
       <c r="L251">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M251">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N251">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O251" s="19">
         <f t="shared" si="38"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P251" s="19">
         <f t="shared" si="39"/>
-        <v>6.09</v>
+        <v>7.42</v>
       </c>
       <c r="T251">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U251">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="252" spans="2:21" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="W251" s="37">
+        <f t="shared" si="49"/>
+        <v>43.615640116091576</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B252" s="21">
         <v>46077</v>
       </c>
       <c r="C252">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D252">
         <v>42</v>
@@ -35061,48 +35236,52 @@
         <v>48</v>
       </c>
       <c r="F252">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G252">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H252">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I252">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J252">
+        <v>41</v>
+      </c>
+      <c r="K252">
+        <v>45</v>
+      </c>
+      <c r="L252">
         <v>44</v>
       </c>
-      <c r="K252">
-        <v>48</v>
-      </c>
-      <c r="L252">
-        <v>48</v>
-      </c>
       <c r="M252">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N252">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O252" s="19">
         <f t="shared" si="38"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P252" s="19">
         <f t="shared" si="39"/>
-        <v>6.3</v>
+        <v>8.34</v>
       </c>
       <c r="T252">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U252">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="253" spans="2:21" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="W252" s="37">
+        <f t="shared" si="49"/>
+        <v>45.863850370848112</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B253" s="21">
         <v>46078</v>
       </c>
@@ -35113,199 +35292,211 @@
         <v>41</v>
       </c>
       <c r="E253">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F253">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G253">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H253">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I253">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J253">
         <v>41</v>
       </c>
       <c r="K253">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L253">
         <v>43</v>
       </c>
       <c r="M253">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N253">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O253" s="19">
         <f t="shared" si="38"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P253" s="19">
         <f t="shared" si="39"/>
-        <v>5.0599999999999996</v>
+        <v>6.39</v>
       </c>
       <c r="T253">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U253">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="254" spans="2:21" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="W253" s="37">
+        <f t="shared" si="49"/>
+        <v>44.432537891002909</v>
+      </c>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B254" s="21">
         <v>46079</v>
       </c>
       <c r="C254">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D254">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E254">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F254">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G254">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H254">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I254">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J254">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K254">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L254">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M254">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="N254">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="O254" s="19">
         <f t="shared" si="38"/>
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="P254" s="19">
         <f t="shared" si="39"/>
-        <v>13.88</v>
+        <v>14.53</v>
       </c>
       <c r="T254">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="U254">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="255" spans="2:21" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="W254" s="37">
+        <f t="shared" si="49"/>
+        <v>74.048306997742657</v>
+      </c>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B255" s="21">
         <v>46080</v>
       </c>
       <c r="C255">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D255">
+        <v>74</v>
+      </c>
+      <c r="E255">
+        <v>113</v>
+      </c>
+      <c r="F255">
+        <v>68</v>
+      </c>
+      <c r="G255">
+        <v>70</v>
+      </c>
+      <c r="H255">
+        <v>54</v>
+      </c>
+      <c r="I255">
+        <v>121</v>
+      </c>
+      <c r="J255">
+        <v>71</v>
+      </c>
+      <c r="K255">
+        <v>82</v>
+      </c>
+      <c r="L255">
         <v>84</v>
       </c>
-      <c r="E255">
-        <v>82</v>
-      </c>
-      <c r="F255">
-        <v>59</v>
-      </c>
-      <c r="G255">
-        <v>75</v>
-      </c>
-      <c r="H255">
-        <v>58</v>
-      </c>
-      <c r="I255">
-        <v>72</v>
-      </c>
-      <c r="J255">
-        <v>72</v>
-      </c>
-      <c r="K255">
-        <v>124</v>
-      </c>
-      <c r="L255">
-        <v>81</v>
-      </c>
       <c r="M255">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="N255">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="O255" s="19">
         <f t="shared" si="38"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P255" s="19">
         <f t="shared" si="39"/>
-        <v>19.059999999999999</v>
+        <v>18.28</v>
       </c>
       <c r="T255">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="U255">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="256" spans="2:21" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="W255" s="37">
+        <f t="shared" si="49"/>
+        <v>84.701386649467906</v>
+      </c>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B256" s="21">
         <v>46081</v>
       </c>
       <c r="C256">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D256">
+        <v>115</v>
+      </c>
+      <c r="E256">
+        <v>136</v>
+      </c>
+      <c r="F256">
+        <v>119</v>
+      </c>
+      <c r="G256">
+        <v>95</v>
+      </c>
+      <c r="H256">
+        <v>98</v>
+      </c>
+      <c r="I256">
+        <v>147</v>
+      </c>
+      <c r="J256">
+        <v>127</v>
+      </c>
+      <c r="K256">
+        <v>149</v>
+      </c>
+      <c r="L256">
+        <v>116</v>
+      </c>
+      <c r="M256">
+        <v>135</v>
+      </c>
+      <c r="N256">
         <v>112</v>
-      </c>
-      <c r="E256">
-        <v>119</v>
-      </c>
-      <c r="F256">
-        <v>105</v>
-      </c>
-      <c r="G256">
-        <v>112</v>
-      </c>
-      <c r="H256">
-        <v>113</v>
-      </c>
-      <c r="I256">
-        <v>141</v>
-      </c>
-      <c r="J256">
-        <v>121</v>
-      </c>
-      <c r="K256">
-        <v>148</v>
-      </c>
-      <c r="L256">
-        <v>123</v>
-      </c>
-      <c r="M256">
-        <v>149</v>
-      </c>
-      <c r="N256">
-        <v>124</v>
       </c>
       <c r="O256" s="19">
         <f t="shared" si="38"/>
@@ -35313,161 +35504,173 @@
       </c>
       <c r="P256" s="19">
         <f t="shared" si="39"/>
-        <v>15.17</v>
+        <v>20.21</v>
       </c>
       <c r="T256">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="U256">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="257" spans="2:21" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="W256" s="37">
+        <f t="shared" si="49"/>
+        <v>125.63189293776202</v>
+      </c>
+    </row>
+    <row r="257" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B257" s="21">
         <v>46082</v>
       </c>
       <c r="C257">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D257">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E257">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F257">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G257">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H257">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I257">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J257">
         <v>35</v>
       </c>
       <c r="K257">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L257">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M257">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N257">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O257" s="19">
         <f t="shared" si="38"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P257" s="19">
         <f t="shared" si="39"/>
-        <v>8.75</v>
+        <v>7.99</v>
       </c>
       <c r="T257">
         <v>52</v>
       </c>
       <c r="U257">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="258" spans="2:21" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="W257" s="37">
+        <f t="shared" si="49"/>
+        <v>41.411931634956467</v>
+      </c>
+    </row>
+    <row r="258" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B258" s="21">
         <v>46083</v>
       </c>
       <c r="C258">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D258">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E258">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F258">
         <v>35</v>
       </c>
       <c r="G258">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H258">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I258">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J258">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K258">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="L258">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M258">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="N258">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O258" s="19">
         <f t="shared" si="38"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P258" s="19">
         <f t="shared" si="39"/>
-        <v>5.68</v>
+        <v>11.64</v>
       </c>
       <c r="T258">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="U258">
         <v>40</v>
       </c>
-    </row>
-    <row r="259" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W258" s="37">
+        <f t="shared" si="49"/>
+        <v>46.16933247339567</v>
+      </c>
+    </row>
+    <row r="259" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B259" s="21">
         <v>46084</v>
       </c>
       <c r="C259">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D259">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E259">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F259">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G259">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H259">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I259">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J259">
         <v>42</v>
       </c>
       <c r="K259">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L259">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M259">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N259">
         <v>45</v>
@@ -35478,181 +35681,197 @@
       </c>
       <c r="P259" s="19">
         <f t="shared" si="39"/>
-        <v>5.17</v>
+        <v>6.84</v>
       </c>
       <c r="T259">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U259">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="260" spans="2:21" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="W259" s="37">
+        <f t="shared" si="49"/>
+        <v>44.747887778136082</v>
+      </c>
+    </row>
+    <row r="260" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B260" s="21">
         <v>46085</v>
       </c>
       <c r="C260">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D260">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E260">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F260">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G260">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H260">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I260">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J260">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K260">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="L260">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M260">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="N260">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O260" s="19">
         <f t="shared" si="38"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P260" s="19">
         <f t="shared" si="39"/>
-        <v>6.08</v>
+        <v>8.17</v>
       </c>
       <c r="T260">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U260">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="261" spans="2:21" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="W260" s="37">
+        <f t="shared" si="49"/>
+        <v>51.340761044824248</v>
+      </c>
+    </row>
+    <row r="261" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B261" s="21">
         <v>46086</v>
       </c>
       <c r="C261">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D261">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E261">
+        <v>96</v>
+      </c>
+      <c r="F261">
+        <v>74</v>
+      </c>
+      <c r="G261">
+        <v>84</v>
+      </c>
+      <c r="H261">
         <v>58</v>
       </c>
-      <c r="F261">
-        <v>65</v>
-      </c>
-      <c r="G261">
-        <v>53</v>
-      </c>
-      <c r="H261">
-        <v>52</v>
-      </c>
       <c r="I261">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="J261">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K261">
         <v>76</v>
       </c>
       <c r="L261">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M261">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N261">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O261" s="19">
         <f t="shared" si="38"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="P261" s="19">
         <f t="shared" si="39"/>
-        <v>6.87</v>
+        <v>19.32</v>
       </c>
       <c r="T261">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="U261">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="262" spans="2:21" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="W261" s="37">
+        <f t="shared" si="49"/>
+        <v>78.019380844888744</v>
+      </c>
+    </row>
+    <row r="262" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B262" s="21">
         <v>46087</v>
       </c>
       <c r="C262">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D262">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E262">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F262">
+        <v>75</v>
+      </c>
+      <c r="G262">
+        <v>80</v>
+      </c>
+      <c r="H262">
+        <v>65</v>
+      </c>
+      <c r="I262">
+        <v>105</v>
+      </c>
+      <c r="J262">
         <v>71</v>
       </c>
-      <c r="G262">
-        <v>70</v>
-      </c>
-      <c r="H262">
-        <v>66</v>
-      </c>
-      <c r="I262">
-        <v>92</v>
-      </c>
-      <c r="J262">
+      <c r="K262">
+        <v>80</v>
+      </c>
+      <c r="L262">
+        <v>78</v>
+      </c>
+      <c r="M262">
+        <v>104</v>
+      </c>
+      <c r="N262">
+        <v>74</v>
+      </c>
+      <c r="O262" s="19">
+        <f t="shared" ref="O262:O263" si="50">ROUND(AVERAGE(C262:N262,T262:U262),0)</f>
+        <v>83</v>
+      </c>
+      <c r="P262" s="19">
+        <f t="shared" ref="P262:P263" si="51">ROUND(_xlfn.STDEV.P(C262:N262,T262:U262),2)</f>
+        <v>12.89</v>
+      </c>
+      <c r="T262">
+        <v>76</v>
+      </c>
+      <c r="U262">
         <v>77</v>
       </c>
-      <c r="K262">
-        <v>110</v>
-      </c>
-      <c r="L262">
-        <v>77</v>
-      </c>
-      <c r="M262">
-        <v>78</v>
-      </c>
-      <c r="N262">
-        <v>72</v>
-      </c>
-      <c r="O262" s="19">
-        <f t="shared" ref="O262:O263" si="47">ROUND(AVERAGE(C262:N262,T262:U262),0)</f>
-        <v>81</v>
-      </c>
-      <c r="P262" s="19">
-        <f t="shared" ref="P262:P263" si="48">ROUND(_xlfn.STDEV.P(C262:N262,T262:U262),2)</f>
-        <v>13.11</v>
-      </c>
-      <c r="T262">
-        <v>108</v>
-      </c>
-      <c r="U262">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="263" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W262" s="37">
+        <f t="shared" si="49"/>
+        <v>84.644985488552066</v>
+      </c>
+    </row>
+    <row r="263" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B263" s="21">
         <v>46088</v>
       </c>
@@ -35660,164 +35879,168 @@
         <v>160</v>
       </c>
       <c r="D263">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E263">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="F263">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G263">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H263">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="I263">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J263">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K263">
         <v>151</v>
       </c>
       <c r="L263">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M263">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="N263">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="O263" s="19">
-        <f t="shared" si="47"/>
-        <v>127</v>
+        <f t="shared" si="50"/>
+        <v>129</v>
       </c>
       <c r="P263" s="19">
-        <f t="shared" si="48"/>
-        <v>17.29</v>
+        <f t="shared" si="51"/>
+        <v>23.57</v>
       </c>
       <c r="T263">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="U263">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="264" spans="2:21" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="W263" s="37">
+        <f t="shared" si="49"/>
+        <v>126.38465011286679</v>
+      </c>
+    </row>
+    <row r="264" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B264" s="31" t="s">
         <v>40</v>
       </c>
       <c r="C264">
-        <v>27.02</v>
+        <v>31.34</v>
       </c>
       <c r="D264">
-        <v>29.96</v>
+        <v>27.36</v>
       </c>
       <c r="E264">
-        <v>27.3</v>
+        <v>24.16</v>
       </c>
       <c r="F264" s="14">
-        <v>23.15</v>
+        <v>25.42</v>
       </c>
       <c r="G264" s="14">
-        <v>31.25</v>
+        <v>22.55</v>
       </c>
       <c r="H264" s="14">
-        <v>25.04</v>
+        <v>24.03</v>
       </c>
       <c r="I264" s="14">
-        <v>29.31</v>
+        <v>25.17</v>
       </c>
       <c r="J264" s="14">
-        <v>27.16</v>
+        <v>24.65</v>
       </c>
       <c r="K264" s="14">
-        <v>25.4</v>
+        <v>21.01</v>
       </c>
       <c r="L264" s="14">
-        <v>26.61</v>
+        <v>28.94</v>
       </c>
       <c r="M264" s="14">
-        <v>27.88</v>
+        <v>26.77</v>
       </c>
       <c r="N264" s="15">
-        <v>28.66</v>
+        <v>28.7</v>
       </c>
       <c r="O264" s="32">
         <f>ROUND(AVERAGE(C264:N264,T264:U264),2)</f>
-        <v>27.53</v>
+        <v>25.87</v>
       </c>
       <c r="P264" s="32">
         <f>ROUND(_xlfn.STDEV.P(C264:N264,T264:U264),2)</f>
-        <v>2.0699999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="T264">
-        <v>29.61</v>
+        <v>26.68</v>
       </c>
       <c r="U264">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="265" spans="2:21" x14ac:dyDescent="0.25">
+        <v>25.46</v>
+      </c>
+    </row>
+    <row r="265" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B265" s="18" t="s">
         <v>41</v>
       </c>
       <c r="C265">
-        <v>25.96</v>
+        <v>25.37</v>
       </c>
       <c r="D265">
-        <v>26.8</v>
+        <v>27.82</v>
       </c>
       <c r="E265">
-        <v>27.9</v>
+        <v>28.38</v>
       </c>
       <c r="F265">
-        <v>32.49</v>
+        <v>29.6</v>
       </c>
       <c r="G265">
-        <v>27.12</v>
+        <v>31.56</v>
       </c>
       <c r="H265">
-        <v>27.38</v>
+        <v>37.090000000000003</v>
       </c>
       <c r="I265">
-        <v>25.18</v>
+        <v>27.82</v>
       </c>
       <c r="J265">
-        <v>25.23</v>
+        <v>28.25</v>
       </c>
       <c r="K265">
-        <v>27.45</v>
+        <v>28.92</v>
       </c>
       <c r="L265">
-        <v>26.54</v>
+        <v>26.4</v>
       </c>
       <c r="M265" s="14">
-        <v>25.98</v>
+        <v>28.03</v>
       </c>
       <c r="N265" s="14">
-        <v>24.94</v>
+        <v>27.67</v>
       </c>
       <c r="O265" s="32">
         <f>ROUND(AVERAGE(C265:N265,T265:U265),2)</f>
-        <v>26.84</v>
+        <v>28.81</v>
       </c>
       <c r="P265" s="32">
         <f>ROUND(_xlfn.STDEV.P(C265:N265,T265:U265),2)</f>
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="T265">
-        <v>25.96</v>
+        <v>27.33</v>
       </c>
       <c r="U265">
-        <v>26.78</v>
-      </c>
-    </row>
-    <row r="266" spans="2:21" x14ac:dyDescent="0.25">
+        <v>29.03</v>
+      </c>
+    </row>
+    <row r="266" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C266" s="54" t="s">
         <v>53</v>
       </c>
@@ -35847,7 +36070,7 @@
       </c>
       <c r="U266" s="54"/>
     </row>
-    <row r="267" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C267" t="s">
         <v>63</v>
       </c>
@@ -35891,54 +36114,54 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
         <v>65</v>
       </c>
       <c r="C268">
-        <v>69.369</v>
+        <v>86.980999999999995</v>
       </c>
       <c r="D268">
-        <v>72.186000000000007</v>
+        <v>85.673000000000002</v>
       </c>
       <c r="E268">
-        <v>105.223</v>
+        <v>113.746</v>
       </c>
       <c r="F268">
-        <v>93.605000000000004</v>
+        <v>100.096</v>
       </c>
       <c r="G268">
-        <v>22.337</v>
+        <v>27.535</v>
       </c>
       <c r="H268">
-        <v>24.212</v>
+        <v>16.765999999999998</v>
       </c>
       <c r="I268">
-        <v>103.099</v>
+        <v>121.79600000000001</v>
       </c>
       <c r="J268">
-        <v>128.64400000000001</v>
+        <v>142.374</v>
       </c>
       <c r="K268">
-        <v>86.679000000000002</v>
+        <v>103.759</v>
       </c>
       <c r="L268">
-        <v>114.809</v>
+        <v>119.176</v>
       </c>
       <c r="M268">
-        <v>184.167</v>
+        <v>222.09700000000001</v>
       </c>
       <c r="N268">
-        <v>193.672</v>
+        <v>213.37299999999999</v>
       </c>
       <c r="T268">
-        <v>197.327</v>
+        <v>230.65700000000001</v>
       </c>
       <c r="U268">
-        <v>196.69499999999999</v>
-      </c>
-    </row>
-    <row r="269" spans="2:21" x14ac:dyDescent="0.25">
+        <v>222.28700000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
         <v>67</v>
       </c>
@@ -35949,28 +36172,28 @@
       <c r="G269" s="33"/>
       <c r="H269" s="33"/>
       <c r="I269" s="53">
-        <v>0.73650000000000004</v>
+        <v>0.69730000000000003</v>
       </c>
       <c r="J269" s="53">
-        <v>0.77580000000000005</v>
+        <v>0.79630000000000001</v>
       </c>
       <c r="K269" s="53">
-        <v>0.71179999999999999</v>
+        <v>0.73029999999999995</v>
       </c>
       <c r="L269" s="53">
-        <v>0.84570000000000001</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="M269" s="53">
-        <v>0.75549999999999995</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="N269" s="53">
-        <v>0.83260000000000001</v>
+        <v>0.83360000000000001</v>
       </c>
       <c r="T269" s="53">
-        <v>0.69140000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="U269" s="53">
-        <v>0.67830000000000001</v>
+        <v>0.81779999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -35985,23 +36208,13 @@
     <mergeCell ref="K266:L266"/>
     <mergeCell ref="M266:N266"/>
   </mergeCells>
-  <conditionalFormatting sqref="C264:N264">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="lessThan">
-      <formula>20</formula>
-    </cfRule>
-    <cfRule type="aboveAverage" dxfId="10" priority="7"/>
-    <cfRule type="cellIs" dxfId="9" priority="28" operator="between">
-      <formula>$O$264-$P$264</formula>
-      <formula>"$O$58+$P$58"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C265:N265">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="C265:N265 T265:U265">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R79 R81:R234">
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="R3:R79 R81:R244">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -36010,15 +36223,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98:N234">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <conditionalFormatting sqref="C98:N244 T142:U244">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>ABS(C98-$A98)&lt;=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>ABS(C98-$A98)&lt;=15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C264:N264 T264:U264">
+    <cfRule type="cellIs" dxfId="3" priority="30" operator="between">
+      <formula>$O$264-$P$264</formula>
+      <formula>"$O$264+$P$264"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+      <formula>$O$264-$P$264</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+      <formula>$O$264+$P$264</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36028,7 +36253,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9BE2AF-C5F8-4B32-A88A-8E9C9CBC1046}">
-  <dimension ref="A1:U264"/>
+  <dimension ref="A1:W265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -48709,54 +48934,54 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:21" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="13">
         <v>41</v>
       </c>
-      <c r="B224" s="64">
+      <c r="B224" s="21">
         <v>46049</v>
       </c>
-      <c r="C224" s="65">
+      <c r="C224">
         <v>55</v>
       </c>
-      <c r="D224" s="65">
+      <c r="D224">
         <v>45</v>
       </c>
-      <c r="E224" s="65">
+      <c r="E224">
         <v>49</v>
       </c>
-      <c r="F224" s="65">
+      <c r="F224">
         <v>29</v>
       </c>
-      <c r="G224" s="65">
+      <c r="G224">
         <v>47</v>
       </c>
-      <c r="H224" s="65">
+      <c r="H224">
         <v>13</v>
       </c>
-      <c r="I224" s="65">
+      <c r="I224">
         <v>44</v>
       </c>
-      <c r="J224" s="65">
+      <c r="J224">
         <v>20</v>
       </c>
-      <c r="K224" s="65">
+      <c r="K224">
         <v>69</v>
       </c>
-      <c r="L224" s="65">
+      <c r="L224">
         <v>43</v>
       </c>
-      <c r="M224" s="65">
+      <c r="M224">
         <v>46</v>
       </c>
-      <c r="N224" s="65">
+      <c r="N224">
         <v>41</v>
       </c>
-      <c r="O224" s="66">
+      <c r="O224" s="19">
         <f t="shared" si="25"/>
         <v>41</v>
       </c>
-      <c r="P224" s="66">
+      <c r="P224" s="19">
         <f t="shared" si="26"/>
         <v>13.64</v>
       </c>
@@ -48768,10 +48993,10 @@
         <f t="shared" ref="S224:S230" si="32">O224/A224</f>
         <v>1</v>
       </c>
-      <c r="T224" s="65">
+      <c r="T224">
         <v>41</v>
       </c>
-      <c r="U224" s="65">
+      <c r="U224">
         <v>31</v>
       </c>
     </row>
@@ -49171,54 +49396,54 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:21" s="65" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="13">
         <v>42</v>
       </c>
-      <c r="B231" s="64">
+      <c r="B231" s="21">
         <v>46056</v>
       </c>
-      <c r="C231" s="65">
+      <c r="C231">
         <v>47</v>
       </c>
-      <c r="D231" s="65">
+      <c r="D231">
         <v>45</v>
       </c>
-      <c r="E231" s="65">
+      <c r="E231">
         <v>49</v>
       </c>
-      <c r="F231" s="65">
+      <c r="F231">
         <v>30</v>
       </c>
-      <c r="G231" s="65">
+      <c r="G231">
         <v>45</v>
       </c>
-      <c r="H231" s="65">
+      <c r="H231">
         <v>41</v>
       </c>
-      <c r="I231" s="65">
+      <c r="I231">
         <v>44</v>
       </c>
-      <c r="J231" s="65">
+      <c r="J231">
         <v>25</v>
       </c>
-      <c r="K231" s="65">
+      <c r="K231">
         <v>48</v>
       </c>
-      <c r="L231" s="65">
+      <c r="L231">
         <v>46</v>
       </c>
-      <c r="M231" s="65">
+      <c r="M231">
         <v>53</v>
       </c>
-      <c r="N231" s="65">
+      <c r="N231">
         <v>45</v>
       </c>
-      <c r="O231" s="66">
+      <c r="O231" s="19">
         <f t="shared" si="25"/>
         <v>43</v>
       </c>
-      <c r="P231" s="66">
+      <c r="P231" s="19">
         <f t="shared" si="26"/>
         <v>7.25</v>
       </c>
@@ -49230,10 +49455,10 @@
         <f t="shared" ref="S231:S234" si="34">O231/A231</f>
         <v>1.0238095238095237</v>
       </c>
-      <c r="T231" s="65">
+      <c r="T231">
         <v>45</v>
       </c>
-      <c r="U231" s="65">
+      <c r="U231">
         <v>37</v>
       </c>
     </row>
@@ -49435,62 +49660,76 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B235" s="26">
+    <row r="235" spans="1:21" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="13">
+        <v>186</v>
+      </c>
+      <c r="B235" s="64">
         <v>46060</v>
       </c>
-      <c r="C235" s="27">
+      <c r="C235" s="63">
         <v>121</v>
       </c>
-      <c r="D235" s="27">
+      <c r="D235" s="63">
         <v>121</v>
       </c>
-      <c r="E235" s="27">
+      <c r="E235" s="63">
         <v>115</v>
       </c>
-      <c r="F235" s="27">
+      <c r="F235" s="63">
         <v>111</v>
       </c>
-      <c r="G235" s="27">
+      <c r="G235" s="63">
         <v>155</v>
       </c>
-      <c r="H235" s="27">
+      <c r="H235" s="63">
         <v>145</v>
       </c>
-      <c r="I235" s="27">
+      <c r="I235" s="63">
         <v>130</v>
       </c>
-      <c r="J235" s="27">
+      <c r="J235" s="63">
         <v>112</v>
       </c>
-      <c r="K235" s="27">
+      <c r="K235" s="63">
         <v>141</v>
       </c>
-      <c r="L235" s="27">
+      <c r="L235" s="63">
         <v>133</v>
       </c>
-      <c r="M235" s="27">
+      <c r="M235" s="63">
         <v>150</v>
       </c>
-      <c r="N235" s="27">
+      <c r="N235" s="63">
         <v>135</v>
       </c>
-      <c r="O235" s="28">
+      <c r="O235" s="65">
         <f t="shared" si="25"/>
         <v>130</v>
       </c>
-      <c r="P235" s="28">
+      <c r="P235" s="65">
         <f t="shared" si="26"/>
         <v>14</v>
       </c>
-      <c r="T235" s="27">
+      <c r="R235" s="25">
+        <f t="shared" ref="R235:R244" si="35">O235-A235</f>
+        <v>-56</v>
+      </c>
+      <c r="S235">
+        <f t="shared" ref="S235:S244" si="36">O235/A235</f>
+        <v>0.69892473118279574</v>
+      </c>
+      <c r="T235" s="63">
         <v>117</v>
       </c>
-      <c r="U235" s="27">
+      <c r="U235" s="63">
         <v>140</v>
       </c>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A236" s="13">
+        <v>0</v>
+      </c>
       <c r="B236" s="21">
         <v>46061</v>
       </c>
@@ -49538,6 +49777,14 @@
         <f t="shared" si="26"/>
         <v>10.96</v>
       </c>
+      <c r="R236" s="25">
+        <f t="shared" si="35"/>
+        <v>35</v>
+      </c>
+      <c r="S236">
+        <f>O236/(A236+1)</f>
+        <v>35</v>
+      </c>
       <c r="T236">
         <v>44</v>
       </c>
@@ -49546,6 +49793,9 @@
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A237" s="13">
+        <v>30</v>
+      </c>
       <c r="B237" s="21">
         <v>46062</v>
       </c>
@@ -49593,6 +49843,14 @@
         <f t="shared" si="26"/>
         <v>4.91</v>
       </c>
+      <c r="R237" s="25">
+        <f t="shared" si="35"/>
+        <v>12</v>
+      </c>
+      <c r="S237">
+        <f t="shared" si="36"/>
+        <v>1.4</v>
+      </c>
       <c r="T237">
         <v>45</v>
       </c>
@@ -49601,6 +49859,9 @@
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A238" s="13">
+        <v>26</v>
+      </c>
       <c r="B238" s="21">
         <v>46063</v>
       </c>
@@ -49648,6 +49909,14 @@
         <f t="shared" si="26"/>
         <v>5.88</v>
       </c>
+      <c r="R238" s="25">
+        <f t="shared" si="35"/>
+        <v>16</v>
+      </c>
+      <c r="S238">
+        <f t="shared" si="36"/>
+        <v>1.6153846153846154</v>
+      </c>
       <c r="T238">
         <v>45</v>
       </c>
@@ -49656,6 +49925,9 @@
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A239" s="13">
+        <v>59</v>
+      </c>
       <c r="B239" s="21">
         <v>46064</v>
       </c>
@@ -49703,6 +49975,14 @@
         <f t="shared" si="26"/>
         <v>5.5</v>
       </c>
+      <c r="R239" s="25">
+        <f t="shared" si="35"/>
+        <v>-17</v>
+      </c>
+      <c r="S239">
+        <f t="shared" si="36"/>
+        <v>0.71186440677966101</v>
+      </c>
       <c r="T239">
         <v>48</v>
       </c>
@@ -49711,6 +49991,9 @@
       </c>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A240" s="13">
+        <v>37</v>
+      </c>
       <c r="B240" s="21">
         <v>46065</v>
       </c>
@@ -49758,6 +50041,14 @@
         <f t="shared" si="26"/>
         <v>6.03</v>
       </c>
+      <c r="R240" s="25">
+        <f t="shared" si="35"/>
+        <v>13</v>
+      </c>
+      <c r="S240">
+        <f t="shared" si="36"/>
+        <v>1.3513513513513513</v>
+      </c>
       <c r="T240">
         <v>54</v>
       </c>
@@ -49765,7 +50056,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="241" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A241" s="13">
+        <v>199</v>
+      </c>
       <c r="B241" s="21">
         <v>46066</v>
       </c>
@@ -49813,6 +50107,14 @@
         <f t="shared" si="26"/>
         <v>7.03</v>
       </c>
+      <c r="R241" s="25">
+        <f t="shared" si="35"/>
+        <v>-110</v>
+      </c>
+      <c r="S241">
+        <f t="shared" si="36"/>
+        <v>0.44723618090452261</v>
+      </c>
       <c r="T241">
         <v>89</v>
       </c>
@@ -49820,7 +50122,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="242" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A242" s="13">
+        <v>283</v>
+      </c>
       <c r="B242" s="21">
         <v>46067</v>
       </c>
@@ -49868,6 +50173,14 @@
         <f t="shared" si="26"/>
         <v>39.81</v>
       </c>
+      <c r="R242" s="25">
+        <f t="shared" si="35"/>
+        <v>-100</v>
+      </c>
+      <c r="S242">
+        <f t="shared" si="36"/>
+        <v>0.64664310954063609</v>
+      </c>
       <c r="T242">
         <v>163</v>
       </c>
@@ -49875,7 +50188,10 @@
         <v>204</v>
       </c>
     </row>
-    <row r="243" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A243" s="13">
+        <v>91</v>
+      </c>
       <c r="B243" s="21">
         <v>46068</v>
       </c>
@@ -49923,6 +50239,14 @@
         <f t="shared" si="26"/>
         <v>3.56</v>
       </c>
+      <c r="R243" s="25">
+        <f t="shared" si="35"/>
+        <v>-48</v>
+      </c>
+      <c r="S243">
+        <f t="shared" si="36"/>
+        <v>0.47252747252747251</v>
+      </c>
       <c r="T243">
         <v>44</v>
       </c>
@@ -49930,7 +50254,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="244" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A244" s="13">
+        <v>35</v>
+      </c>
       <c r="B244" s="21">
         <v>46069</v>
       </c>
@@ -49978,6 +50305,14 @@
         <f t="shared" si="26"/>
         <v>11.41</v>
       </c>
+      <c r="R244" s="25">
+        <f t="shared" si="35"/>
+        <v>7</v>
+      </c>
+      <c r="S244">
+        <f t="shared" si="36"/>
+        <v>1.2</v>
+      </c>
       <c r="T244">
         <v>50</v>
       </c>
@@ -49985,447 +50320,475 @@
         <v>36</v>
       </c>
     </row>
-    <row r="245" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B245" s="21">
+    <row r="245" spans="1:23" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="26">
         <v>46070</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="27">
+        <v>78</v>
+      </c>
+      <c r="D245" s="27">
+        <v>44</v>
+      </c>
+      <c r="E245" s="27">
+        <v>51</v>
+      </c>
+      <c r="F245" s="27">
+        <v>31</v>
+      </c>
+      <c r="G245" s="27">
+        <v>38</v>
+      </c>
+      <c r="H245" s="27">
+        <v>22</v>
+      </c>
+      <c r="I245" s="27">
+        <v>42</v>
+      </c>
+      <c r="J245" s="27">
+        <v>29</v>
+      </c>
+      <c r="K245" s="27">
+        <v>60</v>
+      </c>
+      <c r="L245" s="27">
+        <v>46</v>
+      </c>
+      <c r="M245" s="27">
+        <v>67</v>
+      </c>
+      <c r="N245" s="27">
+        <v>45</v>
+      </c>
+      <c r="O245" s="28">
+        <f t="shared" si="25"/>
+        <v>45</v>
+      </c>
+      <c r="P245" s="28">
+        <f t="shared" si="26"/>
+        <v>14.49</v>
+      </c>
+      <c r="T245" s="27">
+        <v>46</v>
+      </c>
+      <c r="U245" s="27">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B246" s="21">
+        <v>46071</v>
+      </c>
+      <c r="C246">
         <v>47</v>
       </c>
-      <c r="D245">
+      <c r="D246">
+        <v>54</v>
+      </c>
+      <c r="E246">
+        <v>60</v>
+      </c>
+      <c r="F246">
+        <v>45</v>
+      </c>
+      <c r="G246">
+        <v>48</v>
+      </c>
+      <c r="H246">
+        <v>46</v>
+      </c>
+      <c r="I246">
+        <v>69</v>
+      </c>
+      <c r="J246">
+        <v>52</v>
+      </c>
+      <c r="K246">
+        <v>54</v>
+      </c>
+      <c r="L246">
+        <v>51</v>
+      </c>
+      <c r="M246">
+        <v>45</v>
+      </c>
+      <c r="N246">
+        <v>48</v>
+      </c>
+      <c r="O246" s="19">
+        <f t="shared" si="25"/>
+        <v>52</v>
+      </c>
+      <c r="P246" s="19">
+        <f t="shared" si="26"/>
+        <v>6.34</v>
+      </c>
+      <c r="T246">
+        <v>53</v>
+      </c>
+      <c r="U246">
+        <v>55</v>
+      </c>
+      <c r="W246" s="37">
+        <f>SUMPRODUCT(C246:N246,$C$265:$N$265)/SUM($C$265:$N$265)</f>
+        <v>51.412318606900996</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B247" s="21">
+        <v>46072</v>
+      </c>
+      <c r="C247">
+        <v>48</v>
+      </c>
+      <c r="D247">
+        <v>52</v>
+      </c>
+      <c r="E247">
+        <v>59</v>
+      </c>
+      <c r="F247">
+        <v>47</v>
+      </c>
+      <c r="G247">
+        <v>60</v>
+      </c>
+      <c r="H247">
+        <v>55</v>
+      </c>
+      <c r="I247">
+        <v>59</v>
+      </c>
+      <c r="J247">
+        <v>51</v>
+      </c>
+      <c r="K247">
+        <v>52</v>
+      </c>
+      <c r="L247">
+        <v>49</v>
+      </c>
+      <c r="M247">
+        <v>57</v>
+      </c>
+      <c r="N247">
+        <v>49</v>
+      </c>
+      <c r="O247" s="19">
+        <f t="shared" si="25"/>
+        <v>53</v>
+      </c>
+      <c r="P247" s="19">
+        <f t="shared" si="26"/>
+        <v>4.18</v>
+      </c>
+      <c r="T247">
+        <v>52</v>
+      </c>
+      <c r="U247">
+        <v>51</v>
+      </c>
+      <c r="W247" s="37">
+        <f t="shared" ref="W247:W263" si="37">SUMPRODUCT(C247:N247,$C$265:$N$265)/SUM($C$265:$N$265)</f>
+        <v>52.908158658497257</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B248" s="21">
+        <v>46073</v>
+      </c>
+      <c r="C248">
+        <v>101</v>
+      </c>
+      <c r="D248">
+        <v>85</v>
+      </c>
+      <c r="E248">
+        <v>103</v>
+      </c>
+      <c r="F248">
+        <v>58</v>
+      </c>
+      <c r="G248">
+        <v>87</v>
+      </c>
+      <c r="H248">
+        <v>28</v>
+      </c>
+      <c r="I248">
+        <v>112</v>
+      </c>
+      <c r="J248">
+        <v>58</v>
+      </c>
+      <c r="K248">
+        <v>98</v>
+      </c>
+      <c r="L248">
+        <v>97</v>
+      </c>
+      <c r="M248">
+        <v>105</v>
+      </c>
+      <c r="N248">
+        <v>87</v>
+      </c>
+      <c r="O248" s="19">
+        <f t="shared" si="25"/>
+        <v>85</v>
+      </c>
+      <c r="P248" s="19">
+        <f t="shared" si="26"/>
+        <v>22.86</v>
+      </c>
+      <c r="T248">
+        <v>103</v>
+      </c>
+      <c r="U248">
+        <v>69</v>
+      </c>
+      <c r="W248" s="37">
+        <f t="shared" si="37"/>
+        <v>85.492163818123188</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B249" s="21">
+        <v>46074</v>
+      </c>
+      <c r="C249">
+        <v>88</v>
+      </c>
+      <c r="D249">
+        <v>131</v>
+      </c>
+      <c r="E249">
+        <v>99</v>
+      </c>
+      <c r="F249">
+        <v>110</v>
+      </c>
+      <c r="G249">
+        <v>107</v>
+      </c>
+      <c r="H249">
+        <v>111</v>
+      </c>
+      <c r="I249">
+        <v>101</v>
+      </c>
+      <c r="J249">
+        <v>121</v>
+      </c>
+      <c r="K249">
+        <v>117</v>
+      </c>
+      <c r="L249">
+        <v>133</v>
+      </c>
+      <c r="M249">
+        <v>73</v>
+      </c>
+      <c r="N249">
+        <v>132</v>
+      </c>
+      <c r="O249" s="19">
+        <f t="shared" si="25"/>
+        <v>110</v>
+      </c>
+      <c r="P249" s="19">
+        <f t="shared" si="26"/>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="T249">
+        <v>92</v>
+      </c>
+      <c r="U249">
+        <v>125</v>
+      </c>
+      <c r="W249" s="37">
+        <f t="shared" si="37"/>
+        <v>110.23837471783294</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B250" s="21">
+        <v>46075</v>
+      </c>
+      <c r="C250">
+        <v>45</v>
+      </c>
+      <c r="D250">
+        <v>40</v>
+      </c>
+      <c r="E250">
+        <v>41</v>
+      </c>
+      <c r="F250">
+        <v>35</v>
+      </c>
+      <c r="G250">
+        <v>40</v>
+      </c>
+      <c r="H250">
+        <v>34</v>
+      </c>
+      <c r="I250">
+        <v>60</v>
+      </c>
+      <c r="J250">
+        <v>37</v>
+      </c>
+      <c r="K250">
+        <v>47</v>
+      </c>
+      <c r="L250">
+        <v>42</v>
+      </c>
+      <c r="M250">
+        <v>45</v>
+      </c>
+      <c r="N250">
+        <v>41</v>
+      </c>
+      <c r="O250" s="19">
+        <f t="shared" si="25"/>
+        <v>42</v>
+      </c>
+      <c r="P250" s="19">
+        <f t="shared" si="26"/>
+        <v>6.21</v>
+      </c>
+      <c r="T250">
+        <v>45</v>
+      </c>
+      <c r="U250">
+        <v>38</v>
+      </c>
+      <c r="W250" s="37">
+        <f t="shared" si="37"/>
+        <v>42.278394066430174</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B251" s="21">
+        <v>46076</v>
+      </c>
+      <c r="C251">
+        <v>45</v>
+      </c>
+      <c r="D251">
+        <v>40</v>
+      </c>
+      <c r="E251">
+        <v>52</v>
+      </c>
+      <c r="F251">
+        <v>34</v>
+      </c>
+      <c r="G251">
+        <v>39</v>
+      </c>
+      <c r="H251">
+        <v>29</v>
+      </c>
+      <c r="I251">
+        <v>68</v>
+      </c>
+      <c r="J251">
+        <v>34</v>
+      </c>
+      <c r="K251">
+        <v>47</v>
+      </c>
+      <c r="L251">
+        <v>44</v>
+      </c>
+      <c r="M251">
+        <v>46</v>
+      </c>
+      <c r="N251">
         <v>43</v>
       </c>
-      <c r="E245">
-        <v>57</v>
-      </c>
-      <c r="F245">
-        <v>33</v>
-      </c>
-      <c r="G245">
-        <v>44</v>
-      </c>
-      <c r="H245">
-        <v>24</v>
-      </c>
-      <c r="I245">
-        <v>47</v>
-      </c>
-      <c r="J245">
-        <v>35</v>
-      </c>
-      <c r="K245">
-        <v>48</v>
-      </c>
-      <c r="L245">
-        <v>45</v>
-      </c>
-      <c r="M245">
-        <v>55</v>
-      </c>
-      <c r="N245">
-        <v>42</v>
-      </c>
-      <c r="O245" s="19">
+      <c r="O251" s="19">
         <f t="shared" si="25"/>
         <v>43</v>
       </c>
-      <c r="P245" s="19">
-        <f t="shared" si="26"/>
-        <v>8.85</v>
-      </c>
-      <c r="T245">
-        <v>48</v>
-      </c>
-      <c r="U245">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="246" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B246" s="21">
-        <v>46071</v>
-      </c>
-      <c r="C246">
-        <v>47</v>
-      </c>
-      <c r="D246">
-        <v>39</v>
-      </c>
-      <c r="E246">
-        <v>45</v>
-      </c>
-      <c r="F246">
-        <v>31</v>
-      </c>
-      <c r="G246">
-        <v>45</v>
-      </c>
-      <c r="H246">
-        <v>22</v>
-      </c>
-      <c r="I246">
-        <v>46</v>
-      </c>
-      <c r="J246">
-        <v>26</v>
-      </c>
-      <c r="K246">
-        <v>46</v>
-      </c>
-      <c r="L246">
-        <v>39</v>
-      </c>
-      <c r="M246">
-        <v>46</v>
-      </c>
-      <c r="N246">
-        <v>38</v>
-      </c>
-      <c r="O246" s="19">
-        <f t="shared" si="25"/>
-        <v>39</v>
-      </c>
-      <c r="P246" s="19">
-        <f t="shared" si="26"/>
-        <v>7.92</v>
-      </c>
-      <c r="T246">
-        <v>45</v>
-      </c>
-      <c r="U246">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="247" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B247" s="21">
-        <v>46072</v>
-      </c>
-      <c r="C247">
-        <v>50</v>
-      </c>
-      <c r="D247">
-        <v>53</v>
-      </c>
-      <c r="E247">
-        <v>49</v>
-      </c>
-      <c r="F247">
-        <v>60</v>
-      </c>
-      <c r="G247">
-        <v>71</v>
-      </c>
-      <c r="H247">
-        <v>67</v>
-      </c>
-      <c r="I247">
-        <v>55</v>
-      </c>
-      <c r="J247">
-        <v>60</v>
-      </c>
-      <c r="K247">
-        <v>48</v>
-      </c>
-      <c r="L247">
-        <v>53</v>
-      </c>
-      <c r="M247">
-        <v>47</v>
-      </c>
-      <c r="N247">
-        <v>58</v>
-      </c>
-      <c r="O247" s="19">
-        <f t="shared" si="25"/>
-        <v>56</v>
-      </c>
-      <c r="P247" s="19">
-        <f t="shared" si="26"/>
-        <v>7.56</v>
-      </c>
-      <c r="T247">
-        <v>67</v>
-      </c>
-      <c r="U247">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="248" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B248" s="21">
-        <v>46073</v>
-      </c>
-      <c r="C248">
-        <v>142</v>
-      </c>
-      <c r="D248">
-        <v>95</v>
-      </c>
-      <c r="E248">
-        <v>85</v>
-      </c>
-      <c r="F248">
-        <v>85</v>
-      </c>
-      <c r="G248">
-        <v>52</v>
-      </c>
-      <c r="H248">
-        <v>76</v>
-      </c>
-      <c r="I248">
-        <v>70</v>
-      </c>
-      <c r="J248">
-        <v>51</v>
-      </c>
-      <c r="K248">
-        <v>117</v>
-      </c>
-      <c r="L248">
-        <v>130</v>
-      </c>
-      <c r="M248">
-        <v>62</v>
-      </c>
-      <c r="N248">
-        <v>115</v>
-      </c>
-      <c r="O248" s="19">
-        <f t="shared" si="25"/>
-        <v>88</v>
-      </c>
-      <c r="P248" s="19">
-        <f t="shared" si="26"/>
-        <v>27.65</v>
-      </c>
-      <c r="T248">
-        <v>86</v>
-      </c>
-      <c r="U248">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="249" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B249" s="21">
-        <v>46074</v>
-      </c>
-      <c r="C249">
-        <v>104</v>
-      </c>
-      <c r="D249">
-        <v>121</v>
-      </c>
-      <c r="E249">
-        <v>115</v>
-      </c>
-      <c r="F249">
-        <v>114</v>
-      </c>
-      <c r="G249">
-        <v>164</v>
-      </c>
-      <c r="H249">
-        <v>149</v>
-      </c>
-      <c r="I249">
-        <v>132</v>
-      </c>
-      <c r="J249">
-        <v>115</v>
-      </c>
-      <c r="K249">
-        <v>140</v>
-      </c>
-      <c r="L249">
-        <v>136</v>
-      </c>
-      <c r="M249">
-        <v>155</v>
-      </c>
-      <c r="N249">
-        <v>136</v>
-      </c>
-      <c r="O249" s="19">
-        <f t="shared" si="25"/>
-        <v>131</v>
-      </c>
-      <c r="P249" s="19">
-        <f t="shared" si="26"/>
-        <v>16.89</v>
-      </c>
-      <c r="T249">
-        <v>117</v>
-      </c>
-      <c r="U249">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="250" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B250" s="21">
-        <v>46075</v>
-      </c>
-      <c r="C250">
-        <v>47</v>
-      </c>
-      <c r="D250">
-        <v>38</v>
-      </c>
-      <c r="E250">
-        <v>44</v>
-      </c>
-      <c r="F250">
-        <v>34</v>
-      </c>
-      <c r="G250">
-        <v>45</v>
-      </c>
-      <c r="H250">
-        <v>27</v>
-      </c>
-      <c r="I250">
-        <v>47</v>
-      </c>
-      <c r="J250">
-        <v>38</v>
-      </c>
-      <c r="K250">
-        <v>47</v>
-      </c>
-      <c r="L250">
-        <v>39</v>
-      </c>
-      <c r="M250">
-        <v>46</v>
-      </c>
-      <c r="N250">
-        <v>39</v>
-      </c>
-      <c r="O250" s="19">
-        <f t="shared" si="25"/>
-        <v>41</v>
-      </c>
-      <c r="P250" s="19">
-        <f t="shared" si="26"/>
-        <v>5.97</v>
-      </c>
-      <c r="T250">
-        <v>44</v>
-      </c>
-      <c r="U250">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="251" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B251" s="21">
-        <v>46076</v>
-      </c>
-      <c r="C251">
-        <v>48</v>
-      </c>
-      <c r="D251">
-        <v>41</v>
-      </c>
-      <c r="E251">
-        <v>45</v>
-      </c>
-      <c r="F251">
-        <v>39</v>
-      </c>
-      <c r="G251">
-        <v>48</v>
-      </c>
-      <c r="H251">
-        <v>27</v>
-      </c>
-      <c r="I251">
-        <v>45</v>
-      </c>
-      <c r="J251">
-        <v>38</v>
-      </c>
-      <c r="K251">
-        <v>47</v>
-      </c>
-      <c r="L251">
-        <v>41</v>
-      </c>
-      <c r="M251">
-        <v>47</v>
-      </c>
-      <c r="N251">
-        <v>38</v>
-      </c>
-      <c r="O251" s="19">
-        <f t="shared" si="25"/>
-        <v>41</v>
-      </c>
       <c r="P251" s="19">
         <f t="shared" si="26"/>
-        <v>6.43</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="T251">
         <v>45</v>
       </c>
       <c r="U251">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="252" spans="2:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="W251" s="37">
+        <f t="shared" si="37"/>
+        <v>43.462205740083839</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B252" s="21">
         <v>46077</v>
       </c>
       <c r="C252">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D252">
         <v>42</v>
       </c>
       <c r="E252">
+        <v>49</v>
+      </c>
+      <c r="F252">
+        <v>35</v>
+      </c>
+      <c r="G252">
+        <v>36</v>
+      </c>
+      <c r="H252">
+        <v>29</v>
+      </c>
+      <c r="I252">
+        <v>65</v>
+      </c>
+      <c r="J252">
+        <v>30</v>
+      </c>
+      <c r="K252">
         <v>45</v>
       </c>
-      <c r="F252">
-        <v>45</v>
-      </c>
-      <c r="G252">
+      <c r="L252">
+        <v>43</v>
+      </c>
+      <c r="M252">
         <v>49</v>
       </c>
-      <c r="H252">
-        <v>24</v>
-      </c>
-      <c r="I252">
-        <v>48</v>
-      </c>
-      <c r="J252">
-        <v>40</v>
-      </c>
-      <c r="K252">
-        <v>47</v>
-      </c>
-      <c r="L252">
-        <v>48</v>
-      </c>
-      <c r="M252">
-        <v>59</v>
-      </c>
       <c r="N252">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O252" s="19">
         <f t="shared" si="25"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P252" s="19">
         <f t="shared" si="26"/>
-        <v>7.36</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="T252">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="U252">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="253" spans="2:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="W252" s="37">
+        <f t="shared" si="37"/>
+        <v>44.244888745565937</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B253" s="21">
         <v>46078</v>
       </c>
@@ -50436,25 +50799,25 @@
         <v>41</v>
       </c>
       <c r="E253">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F253">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G253">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H253">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I253">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="J253">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K253">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L253">
         <v>43</v>
@@ -50463,337 +50826,361 @@
         <v>47</v>
       </c>
       <c r="N253">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O253" s="19">
         <f t="shared" si="25"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P253" s="19">
         <f t="shared" si="26"/>
-        <v>4.5</v>
+        <v>6.52</v>
       </c>
       <c r="T253">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="U253">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="254" spans="2:21" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="W253" s="37">
+        <f t="shared" si="37"/>
+        <v>44.673750403095774</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B254" s="21">
         <v>46079</v>
       </c>
       <c r="C254">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D254">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E254">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F254">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G254">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H254">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I254">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J254">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="K254">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L254">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M254">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="N254">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O254" s="19">
         <f t="shared" si="25"/>
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="P254" s="19">
         <f t="shared" si="26"/>
-        <v>18.170000000000002</v>
+        <v>25.78</v>
       </c>
       <c r="T254">
+        <v>130</v>
+      </c>
+      <c r="U254">
         <v>57</v>
       </c>
-      <c r="U254">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="255" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W254" s="37">
+        <f t="shared" si="37"/>
+        <v>67.064140599806507</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B255" s="21">
         <v>46080</v>
       </c>
       <c r="C255">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D255">
+        <v>74</v>
+      </c>
+      <c r="E255">
+        <v>100</v>
+      </c>
+      <c r="F255">
+        <v>46</v>
+      </c>
+      <c r="G255">
+        <v>78</v>
+      </c>
+      <c r="H255">
+        <v>27</v>
+      </c>
+      <c r="I255">
+        <v>115</v>
+      </c>
+      <c r="J255">
+        <v>46</v>
+      </c>
+      <c r="K255">
+        <v>82</v>
+      </c>
+      <c r="L255">
         <v>84</v>
       </c>
-      <c r="E255">
-        <v>84</v>
-      </c>
-      <c r="F255">
-        <v>54</v>
-      </c>
-      <c r="G255">
-        <v>72</v>
-      </c>
-      <c r="H255">
-        <v>62</v>
-      </c>
-      <c r="I255">
-        <v>60</v>
-      </c>
-      <c r="J255">
-        <v>49</v>
-      </c>
-      <c r="K255">
-        <v>124</v>
-      </c>
-      <c r="L255">
-        <v>81</v>
-      </c>
       <c r="M255">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="N255">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O255" s="19">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P255" s="19">
         <f t="shared" si="26"/>
-        <v>20.97</v>
+        <v>25.07</v>
       </c>
       <c r="T255">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="U255">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="256" spans="2:21" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="W255" s="37">
+        <f t="shared" si="37"/>
+        <v>78.188810061270544</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B256" s="21">
         <v>46081</v>
       </c>
       <c r="C256">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D256">
         <v>114</v>
       </c>
       <c r="E256">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="F256">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G256">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="H256">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="I256">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="J256">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="K256">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L256">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="M256">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="N256">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O256" s="19">
         <f t="shared" si="25"/>
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="P256" s="19">
         <f t="shared" si="26"/>
-        <v>14.37</v>
+        <v>16.71</v>
       </c>
       <c r="T256">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="U256">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="257" spans="2:21" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="W256" s="37">
+        <f t="shared" si="37"/>
+        <v>124.2759432441148</v>
+      </c>
+    </row>
+    <row r="257" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B257" s="21">
         <v>46082</v>
       </c>
       <c r="C257">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D257">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E257">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F257">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G257">
+        <v>38</v>
+      </c>
+      <c r="H257">
+        <v>9</v>
+      </c>
+      <c r="I257">
+        <v>35</v>
+      </c>
+      <c r="J257">
+        <v>20</v>
+      </c>
+      <c r="K257">
+        <v>54</v>
+      </c>
+      <c r="L257">
+        <v>40</v>
+      </c>
+      <c r="M257">
         <v>45</v>
       </c>
-      <c r="H257">
-        <v>25</v>
-      </c>
-      <c r="I257">
-        <v>44</v>
-      </c>
-      <c r="J257">
-        <v>16</v>
-      </c>
-      <c r="K257">
-        <v>56</v>
-      </c>
-      <c r="L257">
-        <v>39</v>
-      </c>
-      <c r="M257">
-        <v>47</v>
-      </c>
       <c r="N257">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="O257" s="19">
         <f t="shared" si="25"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P257" s="19">
         <f t="shared" si="26"/>
-        <v>11.31</v>
+        <v>11.8</v>
       </c>
       <c r="T257">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="U257">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="258" spans="2:21" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="W257" s="37">
+        <f t="shared" si="37"/>
+        <v>35.753208642373423</v>
+      </c>
+    </row>
+    <row r="258" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B258" s="21">
         <v>46083</v>
       </c>
       <c r="C258">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D258">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E258">
+        <v>50</v>
+      </c>
+      <c r="F258">
+        <v>30</v>
+      </c>
+      <c r="G258">
+        <v>36</v>
+      </c>
+      <c r="H258">
+        <v>18</v>
+      </c>
+      <c r="I258">
+        <v>52</v>
+      </c>
+      <c r="J258">
+        <v>25</v>
+      </c>
+      <c r="K258">
+        <v>74</v>
+      </c>
+      <c r="L258">
+        <v>43</v>
+      </c>
+      <c r="M258">
+        <v>51</v>
+      </c>
+      <c r="N258">
         <v>44</v>
-      </c>
-      <c r="F258">
-        <v>32</v>
-      </c>
-      <c r="G258">
-        <v>46</v>
-      </c>
-      <c r="H258">
-        <v>28</v>
-      </c>
-      <c r="I258">
-        <v>45</v>
-      </c>
-      <c r="J258">
-        <v>29</v>
-      </c>
-      <c r="K258">
-        <v>46</v>
-      </c>
-      <c r="L258">
-        <v>42</v>
-      </c>
-      <c r="M258">
-        <v>46</v>
-      </c>
-      <c r="N258">
-        <v>42</v>
       </c>
       <c r="O258" s="19">
         <f t="shared" si="25"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P258" s="19">
         <f t="shared" si="26"/>
-        <v>6.94</v>
+        <v>13.17</v>
       </c>
       <c r="T258">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U258">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="259" spans="2:21" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="W258" s="37">
+        <f t="shared" si="37"/>
+        <v>42.43153821347952</v>
+      </c>
+    </row>
+    <row r="259" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B259" s="21">
         <v>46084</v>
       </c>
       <c r="C259">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D259">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E259">
+        <v>53</v>
+      </c>
+      <c r="F259">
+        <v>36</v>
+      </c>
+      <c r="G259">
+        <v>37</v>
+      </c>
+      <c r="H259">
+        <v>23</v>
+      </c>
+      <c r="I259">
+        <v>60</v>
+      </c>
+      <c r="J259">
+        <v>31</v>
+      </c>
+      <c r="K259">
+        <v>49</v>
+      </c>
+      <c r="L259">
         <v>45</v>
       </c>
-      <c r="F259">
-        <v>41</v>
-      </c>
-      <c r="G259">
-        <v>51</v>
-      </c>
-      <c r="H259">
-        <v>29</v>
-      </c>
-      <c r="I259">
-        <v>47</v>
-      </c>
-      <c r="J259">
-        <v>40</v>
-      </c>
-      <c r="K259">
-        <v>46</v>
-      </c>
-      <c r="L259">
-        <v>47</v>
-      </c>
       <c r="M259">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N259">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O259" s="19">
         <f t="shared" si="25"/>
@@ -50801,54 +51188,58 @@
       </c>
       <c r="P259" s="19">
         <f t="shared" si="26"/>
-        <v>6.03</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="T259">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="U259">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="260" spans="2:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="W259" s="37">
+        <f t="shared" si="37"/>
+        <v>43.560561109319572</v>
+      </c>
+    </row>
+    <row r="260" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B260" s="21">
         <v>46085</v>
       </c>
       <c r="C260">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D260">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E260">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F260">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G260">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H260">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I260">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J260">
         <v>37</v>
       </c>
       <c r="K260">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L260">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M260">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="N260">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O260" s="19">
         <f t="shared" si="25"/>
@@ -50856,181 +51247,197 @@
       </c>
       <c r="P260" s="19">
         <f t="shared" si="26"/>
-        <v>8.25</v>
+        <v>12.24</v>
       </c>
       <c r="T260">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="U260">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="261" spans="2:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="W260" s="37">
+        <f t="shared" si="37"/>
+        <v>47.845662689455004</v>
+      </c>
+    </row>
+    <row r="261" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B261" s="21">
         <v>46086</v>
       </c>
       <c r="C261">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D261">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E261">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="F261">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G261">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H261">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I261">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="J261">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K261">
         <v>76</v>
       </c>
       <c r="L261">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M261">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N261">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O261" s="19">
         <f t="shared" si="25"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P261" s="19">
         <f t="shared" si="26"/>
-        <v>12.46</v>
+        <v>27.23</v>
       </c>
       <c r="T261">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U261">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="262" spans="2:21" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="W261" s="37">
+        <f t="shared" si="37"/>
+        <v>72.076910673976144</v>
+      </c>
+    </row>
+    <row r="262" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B262" s="21">
         <v>46087</v>
       </c>
       <c r="C262">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D262">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E262">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F262">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G262">
+        <v>84</v>
+      </c>
+      <c r="H262">
+        <v>49</v>
+      </c>
+      <c r="I262">
+        <v>103</v>
+      </c>
+      <c r="J262">
+        <v>50</v>
+      </c>
+      <c r="K262">
         <v>81</v>
       </c>
-      <c r="H262">
+      <c r="L262">
+        <v>78</v>
+      </c>
+      <c r="M262">
+        <v>101</v>
+      </c>
+      <c r="N262">
         <v>71</v>
       </c>
-      <c r="I262">
-        <v>77</v>
-      </c>
-      <c r="J262">
-        <v>66</v>
-      </c>
-      <c r="K262">
-        <v>110</v>
-      </c>
-      <c r="L262">
-        <v>77</v>
-      </c>
-      <c r="M262">
-        <v>69</v>
-      </c>
-      <c r="N262">
-        <v>73</v>
-      </c>
       <c r="O262" s="19">
-        <f t="shared" ref="O262:O263" si="35">ROUND(AVERAGE(C262:N262,T262,U262),0)</f>
-        <v>83</v>
+        <f t="shared" ref="O262:O263" si="38">ROUND(AVERAGE(C262:N262,T262,U262),0)</f>
+        <v>79</v>
       </c>
       <c r="P262" s="19">
-        <f t="shared" ref="P262:P263" si="36">ROUND(_xlfn.STDEV.P(C262:N262,T262,U262),2)</f>
-        <v>18.04</v>
+        <f t="shared" ref="P262:P263" si="39">ROUND(_xlfn.STDEV.P(C262:N262,T262,U262),2)</f>
+        <v>18.98</v>
       </c>
       <c r="T262">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="U262">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="263" spans="2:21" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="W262" s="37">
+        <f t="shared" si="37"/>
+        <v>80.859271202837803</v>
+      </c>
+    </row>
+    <row r="263" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B263" s="21">
         <v>46088</v>
       </c>
       <c r="C263">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D263">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E263">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F263">
+        <v>105</v>
+      </c>
+      <c r="G263">
+        <v>104</v>
+      </c>
+      <c r="H263">
+        <v>109</v>
+      </c>
+      <c r="I263">
         <v>115</v>
       </c>
-      <c r="G263">
-        <v>135</v>
-      </c>
-      <c r="H263">
-        <v>132</v>
-      </c>
-      <c r="I263">
-        <v>130</v>
-      </c>
       <c r="J263">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K263">
         <v>151</v>
       </c>
       <c r="L263">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M263">
+        <v>138</v>
+      </c>
+      <c r="N263">
+        <v>115</v>
+      </c>
+      <c r="O263" s="19">
+        <f t="shared" si="38"/>
+        <v>125</v>
+      </c>
+      <c r="P263" s="19">
+        <f t="shared" si="39"/>
+        <v>18.84</v>
+      </c>
+      <c r="T263">
         <v>151</v>
       </c>
-      <c r="N263">
-        <v>123</v>
-      </c>
-      <c r="O263" s="19">
-        <f t="shared" si="35"/>
-        <v>128</v>
-      </c>
-      <c r="P263" s="19">
-        <f t="shared" si="36"/>
-        <v>15.67</v>
-      </c>
-      <c r="T263">
-        <v>124</v>
-      </c>
       <c r="U263">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="264" spans="2:21" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="W263" s="37">
+        <f t="shared" si="37"/>
+        <v>124.45217671718801</v>
+      </c>
+    </row>
+    <row r="264" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B264" s="33"/>
       <c r="C264" s="60" t="s">
         <v>53</v>
@@ -51062,6 +51469,44 @@
         <v>66</v>
       </c>
       <c r="U264" s="54"/>
+    </row>
+    <row r="265" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C265">
+        <v>31.34</v>
+      </c>
+      <c r="D265">
+        <v>27.36</v>
+      </c>
+      <c r="E265">
+        <v>24.16</v>
+      </c>
+      <c r="F265" s="14">
+        <v>25.42</v>
+      </c>
+      <c r="G265" s="14">
+        <v>22.55</v>
+      </c>
+      <c r="H265" s="14">
+        <v>24.03</v>
+      </c>
+      <c r="I265" s="14">
+        <v>25.17</v>
+      </c>
+      <c r="J265" s="14">
+        <v>24.65</v>
+      </c>
+      <c r="K265" s="14">
+        <v>21.01</v>
+      </c>
+      <c r="L265" s="14">
+        <v>28.94</v>
+      </c>
+      <c r="M265" s="14">
+        <v>26.77</v>
+      </c>
+      <c r="N265" s="15">
+        <v>28.7</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -51075,8 +51520,8 @@
     <mergeCell ref="K264:L264"/>
     <mergeCell ref="M264:N264"/>
   </mergeCells>
-  <conditionalFormatting sqref="R3:R234">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="R3:R244">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -51085,15 +51530,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98:N234">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="C98:N244 T142:U244">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>ABS(C98-$A98)&lt;=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>ABS(C98-$A98)&lt;=15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C265:N265">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>$O$264-$P$264</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>$O$264+$P$264</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
+      <formula>$O$264-$P$264</formula>
+      <formula>"$O$264+$P$264"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -77136,10 +77593,10 @@
     <mergeCell ref="C1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:Y498">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>ABS(C24-$A24) &lt;= 10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>ABS(C24-$A24) &lt;= 15</formula>
     </cfRule>
   </conditionalFormatting>

--- a/restaurant_analytics/data/data.xlsx
+++ b/restaurant_analytics/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cardi\Documents\git-repo\swe_dev\restaurant_analytics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7754421-8C0D-4301-9CD9-8D4957DC7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6009E2D6-01D7-461F-AA44-0A1C05AEF656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="69">
   <si>
     <t>day</t>
   </si>
@@ -585,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -709,6 +709,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -718,23 +724,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
@@ -744,12 +748,21 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBA3A3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -801,6 +814,86 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBA3A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1190,7 +1283,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R745"/>
+  <dimension ref="A1:R758"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
@@ -19732,7 +19825,7 @@
         <v>199</v>
       </c>
       <c r="E695" s="8">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="F695" s="8">
         <v>0</v>
@@ -19741,7 +19834,7 @@
         <v>0</v>
       </c>
       <c r="H695" s="8">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="696" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19758,7 +19851,7 @@
         <v>283</v>
       </c>
       <c r="E696" s="8">
-        <v>36.9</v>
+        <v>41.2</v>
       </c>
       <c r="F696" s="8">
         <v>0</v>
@@ -19767,7 +19860,7 @@
         <v>0</v>
       </c>
       <c r="H696" s="8">
-        <v>8.1999999999999993</v>
+        <v>3.4</v>
       </c>
       <c r="I696" s="39" t="s">
         <v>34</v>
@@ -19787,16 +19880,16 @@
         <v>91</v>
       </c>
       <c r="E697" s="8">
-        <v>44.2</v>
+        <v>42.8</v>
       </c>
       <c r="F697" s="8">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G697" s="8">
         <v>0</v>
       </c>
       <c r="H697" s="8">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="698" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19813,7 +19906,7 @@
         <v>35</v>
       </c>
       <c r="E698" s="8">
-        <v>48.9</v>
+        <v>47.7</v>
       </c>
       <c r="F698" s="8">
         <v>0</v>
@@ -19822,7 +19915,7 @@
         <v>0</v>
       </c>
       <c r="H698" s="8">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="I698" s="39" t="s">
         <v>35</v>
@@ -19842,16 +19935,16 @@
         <v>79</v>
       </c>
       <c r="E699" s="8">
-        <v>48.4</v>
+        <v>50.2</v>
       </c>
       <c r="F699" s="8">
-        <v>5.0999999999999997E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G699" s="8">
         <v>0</v>
       </c>
       <c r="H699" s="8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="700" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19868,16 +19961,16 @@
         <v>29</v>
       </c>
       <c r="E700" s="8">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="F700" s="8">
-        <v>0.12</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G700" s="8">
         <v>0</v>
       </c>
       <c r="H700" s="8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="I700" s="39" t="s">
         <v>37</v>
@@ -19897,16 +19990,16 @@
         <v>38</v>
       </c>
       <c r="E701" s="8">
-        <v>45.3</v>
+        <v>47.5</v>
       </c>
       <c r="F701" s="8">
-        <v>0.02</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G701" s="8">
         <v>0</v>
       </c>
       <c r="H701" s="8">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="702" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19923,16 +20016,16 @@
         <v>101</v>
       </c>
       <c r="E702" s="8">
-        <v>38.299999999999997</v>
+        <v>35.4</v>
       </c>
       <c r="F702" s="8">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G702" s="8">
         <v>0</v>
       </c>
       <c r="H702" s="8">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="I702" s="39" t="s">
         <v>10</v>
@@ -19952,16 +20045,16 @@
         <v>183</v>
       </c>
       <c r="E703" s="8">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F703" s="8">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G703" s="8">
         <v>0</v>
       </c>
       <c r="H703" s="8">
-        <v>11.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="704" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19978,7 +20071,7 @@
         <v>66</v>
       </c>
       <c r="E704" s="8">
-        <v>28.4</v>
+        <v>24.4</v>
       </c>
       <c r="F704" s="8">
         <v>0</v>
@@ -19987,10 +20080,10 @@
         <v>0</v>
       </c>
       <c r="H704" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="705" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="5">
         <v>2</v>
       </c>
@@ -20004,7 +20097,7 @@
         <v>36</v>
       </c>
       <c r="E705" s="8">
-        <v>28.8</v>
+        <v>21.9</v>
       </c>
       <c r="F705" s="8">
         <v>0</v>
@@ -20013,10 +20106,10 @@
         <v>0</v>
       </c>
       <c r="H705" s="8">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="706" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="5">
         <v>3</v>
       </c>
@@ -20030,7 +20123,7 @@
         <v>45</v>
       </c>
       <c r="E706" s="8">
-        <v>31.8</v>
+        <v>25.7</v>
       </c>
       <c r="F706" s="8">
         <v>0</v>
@@ -20039,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="H706" s="8">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="707" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="5">
         <v>4</v>
       </c>
@@ -20056,7 +20149,7 @@
         <v>64</v>
       </c>
       <c r="E707" s="8">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="F707" s="8">
         <v>0</v>
@@ -20065,10 +20158,10 @@
         <v>0.36</v>
       </c>
       <c r="H707" s="8">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="708" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="708" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="5">
         <v>5</v>
       </c>
@@ -20082,7 +20175,7 @@
         <v>41</v>
       </c>
       <c r="E708" s="8">
-        <v>31.2</v>
+        <v>30.2</v>
       </c>
       <c r="F708" s="8">
         <v>0</v>
@@ -20091,10 +20184,10 @@
         <v>0</v>
       </c>
       <c r="H708" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="709" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="709" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="5">
         <v>6</v>
       </c>
@@ -20108,7 +20201,7 @@
         <v>90</v>
       </c>
       <c r="E709" s="8">
-        <v>46.3</v>
+        <v>43.2</v>
       </c>
       <c r="F709" s="8">
         <v>0</v>
@@ -20117,13 +20210,13 @@
         <v>0</v>
       </c>
       <c r="H709" s="8">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="I709" s="39" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="710" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="5">
         <v>7</v>
       </c>
@@ -20137,7 +20230,7 @@
         <v>137</v>
       </c>
       <c r="E710" s="8">
-        <v>33.5</v>
+        <v>39.9</v>
       </c>
       <c r="F710" s="8">
         <v>0</v>
@@ -20146,10 +20239,10 @@
         <v>0</v>
       </c>
       <c r="H710" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="711" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="711" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="5">
         <v>1</v>
       </c>
@@ -20163,7 +20256,7 @@
         <v>43</v>
       </c>
       <c r="E711" s="8">
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="F711" s="8">
         <v>0</v>
@@ -20172,10 +20265,10 @@
         <v>0</v>
       </c>
       <c r="H711" s="8">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="712" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="712" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="5">
         <v>2</v>
       </c>
@@ -20189,7 +20282,7 @@
         <v>39</v>
       </c>
       <c r="E712" s="8">
-        <v>33.5</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="F712" s="8">
         <v>0</v>
@@ -20198,10 +20291,10 @@
         <v>0</v>
       </c>
       <c r="H712" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="713" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="713" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="5">
         <v>3</v>
       </c>
@@ -20212,25 +20305,22 @@
         <v>46084</v>
       </c>
       <c r="D713" s="13">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E713" s="8">
-        <v>37.200000000000003</v>
+        <v>36.5</v>
       </c>
       <c r="F713" s="8">
-        <v>0</v>
+        <v>3.1E-2</v>
       </c>
       <c r="G713" s="8">
         <v>0</v>
       </c>
       <c r="H713" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="J713" s="8">
-        <v>6.8699999999999992</v>
-      </c>
-    </row>
-    <row r="714" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="714" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="5">
         <v>4</v>
       </c>
@@ -20241,10 +20331,10 @@
         <v>46085</v>
       </c>
       <c r="D714" s="13">
-        <v>39.5</v>
+        <v>21</v>
       </c>
       <c r="E714" s="8">
-        <v>43</v>
+        <v>37.9</v>
       </c>
       <c r="F714" s="8">
         <v>7.0000000000000007E-2</v>
@@ -20253,13 +20343,10 @@
         <v>0</v>
       </c>
       <c r="H714" s="8">
-        <v>6</v>
-      </c>
-      <c r="J714" s="8">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="715" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="715" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="5">
         <v>5</v>
       </c>
@@ -20270,25 +20357,22 @@
         <v>46086</v>
       </c>
       <c r="D715" s="13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E715" s="8">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="F715" s="8">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G715" s="8">
         <v>0</v>
       </c>
       <c r="H715" s="8">
-        <v>7</v>
-      </c>
-      <c r="J715" s="8">
-        <v>7.0350000000000001</v>
-      </c>
-    </row>
-    <row r="716" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="716" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="5">
         <v>6</v>
       </c>
@@ -20299,28 +20383,25 @@
         <v>46087</v>
       </c>
       <c r="D716" s="13">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="E716" s="8">
-        <v>62.5</v>
+        <v>54.5</v>
       </c>
       <c r="F716" s="8">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="G716" s="8">
         <v>0</v>
       </c>
       <c r="H716" s="8">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="I716" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="J716" s="8">
-        <v>16.864999999999998</v>
-      </c>
-    </row>
-    <row r="717" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="717" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="5">
         <v>7</v>
       </c>
@@ -20331,25 +20412,22 @@
         <v>46088</v>
       </c>
       <c r="D717" s="13">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E717" s="8">
-        <v>46.5</v>
+        <v>52.3</v>
       </c>
       <c r="F717" s="8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G717" s="8">
         <v>0</v>
       </c>
       <c r="H717" s="8">
-        <v>16</v>
-      </c>
-      <c r="J717" s="8">
-        <v>25.545000000000002</v>
-      </c>
-    </row>
-    <row r="718" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="718" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="5">
         <v>1</v>
       </c>
@@ -20360,10 +20438,10 @@
         <v>46089</v>
       </c>
       <c r="D718" s="13">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E718" s="8">
-        <v>54.5</v>
+        <v>48.6</v>
       </c>
       <c r="F718" s="8">
         <v>0</v>
@@ -20372,16 +20450,13 @@
         <v>0</v>
       </c>
       <c r="H718" s="8">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="I718" t="s">
         <v>61</v>
       </c>
-      <c r="J718" s="8">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="719" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="719" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="5">
         <v>2</v>
       </c>
@@ -20392,10 +20467,10 @@
         <v>46090</v>
       </c>
       <c r="D719" s="13">
-        <v>47.5</v>
+        <v>28</v>
       </c>
       <c r="E719" s="8">
-        <v>57.5</v>
+        <v>59.4</v>
       </c>
       <c r="F719" s="8">
         <v>0</v>
@@ -20404,13 +20479,10 @@
         <v>0</v>
       </c>
       <c r="H719" s="8">
-        <v>13</v>
-      </c>
-      <c r="J719" s="8">
-        <v>8.2149999999999999</v>
-      </c>
-    </row>
-    <row r="720" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="720" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="5">
         <v>3</v>
       </c>
@@ -20421,10 +20493,10 @@
         <v>46091</v>
       </c>
       <c r="D720" s="13">
-        <v>48.5</v>
+        <v>33</v>
       </c>
       <c r="E720" s="8">
-        <v>48.5</v>
+        <v>51.8</v>
       </c>
       <c r="F720" s="8">
         <v>1.1599999999999999</v>
@@ -20433,10 +20505,7 @@
         <v>0</v>
       </c>
       <c r="H720" s="8">
-        <v>16</v>
-      </c>
-      <c r="J720" s="8">
-        <v>7.5049999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="721" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20450,22 +20519,19 @@
         <v>46092</v>
       </c>
       <c r="D721" s="13">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E721" s="8">
-        <v>35</v>
+        <v>40.5</v>
       </c>
       <c r="F721" s="8">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="G721" s="8">
         <v>0</v>
       </c>
       <c r="H721" s="8">
-        <v>13</v>
-      </c>
-      <c r="J721" s="8">
-        <v>6.6649999999999991</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="722" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20479,10 +20545,10 @@
         <v>46093</v>
       </c>
       <c r="D722" s="13">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E722" s="8">
-        <v>36</v>
+        <v>39.9</v>
       </c>
       <c r="F722" s="8">
         <v>0</v>
@@ -20491,10 +20557,7 @@
         <v>0</v>
       </c>
       <c r="H722" s="8">
-        <v>5</v>
-      </c>
-      <c r="J722" s="8">
-        <v>9.5649999999999995</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="723" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20508,25 +20571,22 @@
         <v>46094</v>
       </c>
       <c r="D723" s="13">
-        <v>69.5</v>
+        <v>111</v>
       </c>
       <c r="E723" s="8">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="F723" s="8">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="G723" s="8">
         <v>0</v>
       </c>
       <c r="H723" s="8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I723" s="39" t="s">
         <v>10</v>
-      </c>
-      <c r="J723" s="8">
-        <v>11.945</v>
       </c>
     </row>
     <row r="724" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20540,10 +20600,10 @@
         <v>46095</v>
       </c>
       <c r="D724" s="13">
-        <v>131.5</v>
+        <v>135</v>
       </c>
       <c r="E724" s="8">
-        <v>31</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="F724" s="8">
         <v>0</v>
@@ -20552,10 +20612,7 @@
         <v>0</v>
       </c>
       <c r="H724" s="8">
-        <v>14</v>
-      </c>
-      <c r="J724" s="8">
-        <v>19.82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="725" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20569,22 +20626,19 @@
         <v>46096</v>
       </c>
       <c r="D725" s="13">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E725" s="8">
-        <v>33</v>
+        <v>38.1</v>
       </c>
       <c r="F725" s="8">
-        <v>0.03</v>
+        <v>1.42</v>
       </c>
       <c r="G725" s="8">
         <v>0.14000000000000001</v>
       </c>
       <c r="H725" s="8">
-        <v>1</v>
-      </c>
-      <c r="J725" s="8">
-        <v>15.17</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="726" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20598,10 +20652,10 @@
         <v>46097</v>
       </c>
       <c r="D726" s="13">
-        <v>46.5</v>
+        <v>43.5</v>
       </c>
       <c r="E726" s="8">
-        <v>33.5</v>
+        <v>30.4</v>
       </c>
       <c r="F726" s="8">
         <v>0</v>
@@ -20610,10 +20664,10 @@
         <v>0</v>
       </c>
       <c r="H726" s="8">
-        <v>8</v>
+        <v>13.3</v>
       </c>
       <c r="J726" s="8">
-        <v>9.0050000000000008</v>
+        <v>5.4749999999999996</v>
       </c>
     </row>
     <row r="727" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20627,25 +20681,25 @@
         <v>46098</v>
       </c>
       <c r="D727" s="13">
-        <v>31.5</v>
+        <v>35.5</v>
       </c>
       <c r="E727" s="8">
-        <v>35</v>
+        <v>29.5</v>
       </c>
       <c r="F727" s="8">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G727" s="8">
         <v>0</v>
       </c>
       <c r="H727" s="8">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="I727" s="39" t="s">
         <v>38</v>
       </c>
       <c r="J727" s="8">
-        <v>10.89</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="728" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20659,10 +20713,10 @@
         <v>46099</v>
       </c>
       <c r="D728" s="13">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E728" s="8">
-        <v>29</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="F728" s="8">
         <v>0</v>
@@ -20671,10 +20725,10 @@
         <v>0</v>
       </c>
       <c r="H728" s="8">
-        <v>6</v>
+        <v>10.3</v>
       </c>
       <c r="J728" s="8">
-        <v>9.3249999999999993</v>
+        <v>4.1550000000000002</v>
       </c>
     </row>
     <row r="729" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20688,22 +20742,22 @@
         <v>46100</v>
       </c>
       <c r="D729" s="13">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E729" s="8">
-        <v>35.5</v>
+        <v>38.5</v>
       </c>
       <c r="F729" s="8">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G729" s="8">
         <v>0</v>
       </c>
       <c r="H729" s="8">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="J729" s="8">
-        <v>11.83</v>
+        <v>6.7650000000000006</v>
       </c>
     </row>
     <row r="730" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20717,22 +20771,22 @@
         <v>46101</v>
       </c>
       <c r="D730" s="13">
-        <v>75.5</v>
+        <v>112</v>
       </c>
       <c r="E730" s="8">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F730" s="8">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="G730" s="8">
         <v>0</v>
       </c>
       <c r="H730" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J730" s="8">
-        <v>13.125</v>
+        <v>14.574999999999999</v>
       </c>
     </row>
     <row r="731" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20746,22 +20800,22 @@
         <v>46102</v>
       </c>
       <c r="D731" s="13">
-        <v>93.5</v>
+        <v>128.5</v>
       </c>
       <c r="E731" s="8">
-        <v>42.5</v>
+        <v>58</v>
       </c>
       <c r="F731" s="8">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G731" s="8">
         <v>0</v>
       </c>
       <c r="H731" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J731" s="8">
-        <v>16.335000000000001</v>
+        <v>13.215</v>
       </c>
     </row>
     <row r="732" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20775,22 +20829,22 @@
         <v>46103</v>
       </c>
       <c r="D732" s="13">
-        <v>45.5</v>
+        <v>44</v>
       </c>
       <c r="E732" s="8">
-        <v>37.5</v>
+        <v>43.5</v>
       </c>
       <c r="F732" s="8">
-        <v>0.34</v>
+        <v>0.02</v>
       </c>
       <c r="G732" s="8">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H732" s="8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J732" s="8">
-        <v>10.67</v>
+        <v>6.7200000000000006</v>
       </c>
     </row>
     <row r="733" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20804,10 +20858,10 @@
         <v>46104</v>
       </c>
       <c r="D733" s="13">
-        <v>40.5</v>
+        <v>47.5</v>
       </c>
       <c r="E733" s="8">
-        <v>31.5</v>
+        <v>34</v>
       </c>
       <c r="F733" s="8">
         <v>0</v>
@@ -20816,10 +20870,10 @@
         <v>0</v>
       </c>
       <c r="H733" s="8">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J733" s="8">
-        <v>10.02</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="734" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20833,10 +20887,10 @@
         <v>46105</v>
       </c>
       <c r="D734" s="13">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="E734" s="8">
-        <v>30</v>
+        <v>39.5</v>
       </c>
       <c r="F734" s="8">
         <v>0</v>
@@ -20845,10 +20899,10 @@
         <v>0</v>
       </c>
       <c r="H734" s="8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J734" s="8">
-        <v>7.6349999999999998</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="735" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20862,10 +20916,10 @@
         <v>46106</v>
       </c>
       <c r="D735" s="13">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E735" s="8">
-        <v>32</v>
+        <v>47.5</v>
       </c>
       <c r="F735" s="8">
         <v>0</v>
@@ -20874,10 +20928,10 @@
         <v>0</v>
       </c>
       <c r="H735" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J735" s="8">
-        <v>11.475</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="736" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20891,10 +20945,10 @@
         <v>46107</v>
       </c>
       <c r="D736" s="13">
-        <v>55.5</v>
+        <v>47</v>
       </c>
       <c r="E736" s="8">
-        <v>36.5</v>
+        <v>42.5</v>
       </c>
       <c r="F736" s="8">
         <v>0</v>
@@ -20903,10 +20957,10 @@
         <v>0</v>
       </c>
       <c r="H736" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J736" s="8">
-        <v>11.355</v>
+        <v>6.7850000000000001</v>
       </c>
     </row>
     <row r="737" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20920,10 +20974,10 @@
         <v>46108</v>
       </c>
       <c r="D737" s="13">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="E737" s="8">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="F737" s="8">
         <v>0</v>
@@ -20932,13 +20986,13 @@
         <v>0</v>
       </c>
       <c r="H737" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I737" s="39" t="s">
         <v>68</v>
       </c>
       <c r="J737" s="8">
-        <v>11.215</v>
+        <v>11.309999999999999</v>
       </c>
     </row>
     <row r="738" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20952,10 +21006,10 @@
         <v>46109</v>
       </c>
       <c r="D738" s="13">
-        <v>125.5</v>
+        <v>125</v>
       </c>
       <c r="E738" s="8">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F738" s="8">
         <v>0</v>
@@ -20964,10 +21018,10 @@
         <v>0</v>
       </c>
       <c r="H738" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J738" s="8">
-        <v>19.84</v>
+        <v>13.615</v>
       </c>
     </row>
     <row r="739" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20981,10 +21035,10 @@
         <v>46110</v>
       </c>
       <c r="D739" s="13">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="E739" s="8">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F739" s="8">
         <v>0</v>
@@ -20996,7 +21050,7 @@
         <v>6</v>
       </c>
       <c r="J739" s="8">
-        <v>7.73</v>
+        <v>9.4550000000000001</v>
       </c>
     </row>
     <row r="740" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21010,10 +21064,10 @@
         <v>46111</v>
       </c>
       <c r="D740" s="13">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E740" s="8">
-        <v>36.5</v>
+        <v>45.5</v>
       </c>
       <c r="F740" s="8">
         <v>0</v>
@@ -21022,10 +21076,10 @@
         <v>0</v>
       </c>
       <c r="H740" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J740" s="8">
-        <v>10.565000000000001</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="741" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21039,22 +21093,22 @@
         <v>46112</v>
       </c>
       <c r="D741" s="13">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="E741" s="8">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F741" s="8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G741" s="8">
         <v>0</v>
       </c>
       <c r="H741" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J741" s="8">
-        <v>13.21</v>
+        <v>10.275</v>
       </c>
     </row>
     <row r="742" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21068,10 +21122,10 @@
         <v>46113</v>
       </c>
       <c r="D742" s="13">
-        <v>44</v>
+        <v>50.5</v>
       </c>
       <c r="E742" s="8">
-        <v>40</v>
+        <v>49.5</v>
       </c>
       <c r="F742" s="8">
         <v>0</v>
@@ -21080,10 +21134,10 @@
         <v>0</v>
       </c>
       <c r="H742" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J742" s="8">
-        <v>9.48</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="743" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21097,10 +21151,10 @@
         <v>46114</v>
       </c>
       <c r="D743" s="13">
-        <v>73</v>
+        <v>77.5</v>
       </c>
       <c r="E743" s="8">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F743" s="8">
         <v>0.23</v>
@@ -21109,24 +21163,459 @@
         <v>0</v>
       </c>
       <c r="H743" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J743" s="8">
-        <v>14.77</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="744" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A744"/>
+      <c r="A744" s="5">
+        <v>6</v>
+      </c>
+      <c r="B744" s="5">
+        <v>743</v>
+      </c>
+      <c r="C744" s="50">
+        <v>46115</v>
+      </c>
+      <c r="D744" s="13">
+        <v>75</v>
+      </c>
+      <c r="E744" s="8">
+        <v>50</v>
+      </c>
+      <c r="F744" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G744" s="8">
+        <v>0</v>
+      </c>
+      <c r="H744" s="8">
+        <v>12</v>
+      </c>
+      <c r="I744" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="J744" s="8">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="745" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A745"/>
+      <c r="A745" s="5">
+        <v>7</v>
+      </c>
+      <c r="B745" s="5">
+        <v>744</v>
+      </c>
+      <c r="C745" s="50">
+        <v>46116</v>
+      </c>
+      <c r="D745" s="13">
+        <v>102.5</v>
+      </c>
+      <c r="E745" s="8">
+        <v>49.5</v>
+      </c>
+      <c r="F745" s="8">
+        <v>0.19</v>
+      </c>
+      <c r="G745" s="8">
+        <v>0</v>
+      </c>
+      <c r="H745" s="8">
+        <v>7</v>
+      </c>
+      <c r="J745" s="8">
+        <v>10.785</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A746" s="5">
+        <v>1</v>
+      </c>
+      <c r="B746" s="5">
+        <v>745</v>
+      </c>
+      <c r="C746" s="50">
+        <v>46117</v>
+      </c>
+      <c r="D746" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="E746" s="8">
+        <v>50.5</v>
+      </c>
+      <c r="F746" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G746" s="8">
+        <v>0</v>
+      </c>
+      <c r="H746" s="8">
+        <v>12</v>
+      </c>
+      <c r="I746" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="J746" s="8">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="5">
+        <v>2</v>
+      </c>
+      <c r="B747" s="5">
+        <v>746</v>
+      </c>
+      <c r="C747" s="50">
+        <v>46118</v>
+      </c>
+      <c r="D747" s="13">
+        <v>43</v>
+      </c>
+      <c r="E747" s="8">
+        <v>51</v>
+      </c>
+      <c r="F747" s="8">
+        <v>0</v>
+      </c>
+      <c r="G747" s="8">
+        <v>0</v>
+      </c>
+      <c r="H747" s="8">
+        <v>10</v>
+      </c>
+      <c r="J747" s="8">
+        <v>3.6749999999999998</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="5">
+        <v>3</v>
+      </c>
+      <c r="B748" s="5">
+        <v>747</v>
+      </c>
+      <c r="C748" s="50">
+        <v>46119</v>
+      </c>
+      <c r="D748" s="13">
+        <v>46.5</v>
+      </c>
+      <c r="E748" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="F748" s="8">
+        <v>0</v>
+      </c>
+      <c r="G748" s="8">
+        <v>0</v>
+      </c>
+      <c r="H748" s="8">
+        <v>10</v>
+      </c>
+      <c r="J748" s="8">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="5">
+        <v>4</v>
+      </c>
+      <c r="B749" s="5">
+        <v>748</v>
+      </c>
+      <c r="C749" s="50">
+        <v>46120</v>
+      </c>
+      <c r="D749" s="13">
+        <v>57</v>
+      </c>
+      <c r="E749" s="8">
+        <v>52</v>
+      </c>
+      <c r="F749" s="8">
+        <v>0.66</v>
+      </c>
+      <c r="G749" s="8">
+        <v>0</v>
+      </c>
+      <c r="H749" s="8">
+        <v>4</v>
+      </c>
+      <c r="J749" s="8">
+        <v>17.63</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="5">
+        <v>5</v>
+      </c>
+      <c r="B750" s="5">
+        <v>749</v>
+      </c>
+      <c r="C750" s="50">
+        <v>46121</v>
+      </c>
+      <c r="D750" s="13">
+        <v>56.5</v>
+      </c>
+      <c r="E750" s="8">
+        <v>52</v>
+      </c>
+      <c r="F750" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="G750" s="8">
+        <v>0</v>
+      </c>
+      <c r="H750" s="8">
+        <v>7</v>
+      </c>
+      <c r="J750" s="8">
+        <v>7.1400000000000006</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="5">
+        <v>6</v>
+      </c>
+      <c r="B751" s="5">
+        <v>750</v>
+      </c>
+      <c r="C751" s="50">
+        <v>46122</v>
+      </c>
+      <c r="D751" s="13">
+        <v>76</v>
+      </c>
+      <c r="E751" s="8">
+        <v>51</v>
+      </c>
+      <c r="F751" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="G751" s="8">
+        <v>0</v>
+      </c>
+      <c r="H751" s="8">
+        <v>8</v>
+      </c>
+      <c r="J751" s="8">
+        <v>7.5950000000000006</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="5">
+        <v>7</v>
+      </c>
+      <c r="B752" s="5">
+        <v>751</v>
+      </c>
+      <c r="C752" s="50">
+        <v>46123</v>
+      </c>
+      <c r="D752" s="13">
+        <v>138</v>
+      </c>
+      <c r="E752" s="8">
+        <v>47.5</v>
+      </c>
+      <c r="F752" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G752" s="8">
+        <v>0</v>
+      </c>
+      <c r="H752" s="8">
+        <v>15</v>
+      </c>
+      <c r="J752" s="8">
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A753" s="5">
+        <v>1</v>
+      </c>
+      <c r="B753" s="5">
+        <v>752</v>
+      </c>
+      <c r="C753" s="50">
+        <v>46124</v>
+      </c>
+      <c r="D753" s="13">
+        <v>45</v>
+      </c>
+      <c r="E753" s="8">
+        <v>46.5</v>
+      </c>
+      <c r="F753" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="G753" s="8">
+        <v>0</v>
+      </c>
+      <c r="H753" s="8">
+        <v>10</v>
+      </c>
+      <c r="J753" s="8">
+        <v>4.6950000000000003</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="5">
+        <v>2</v>
+      </c>
+      <c r="B754" s="5">
+        <v>753</v>
+      </c>
+      <c r="C754" s="50">
+        <v>46125</v>
+      </c>
+      <c r="D754" s="13">
+        <v>52.5</v>
+      </c>
+      <c r="E754" s="8">
+        <v>48.5</v>
+      </c>
+      <c r="F754" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G754" s="8">
+        <v>0</v>
+      </c>
+      <c r="H754" s="8">
+        <v>4</v>
+      </c>
+      <c r="J754" s="8">
+        <v>13.96</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="5">
+        <v>3</v>
+      </c>
+      <c r="B755" s="5">
+        <v>754</v>
+      </c>
+      <c r="C755" s="50">
+        <v>46126</v>
+      </c>
+      <c r="D755" s="13">
+        <v>51</v>
+      </c>
+      <c r="E755" s="8">
+        <v>53.5</v>
+      </c>
+      <c r="F755" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="G755" s="8">
+        <v>0</v>
+      </c>
+      <c r="H755" s="8">
+        <v>9</v>
+      </c>
+      <c r="J755" s="8">
+        <v>14.635</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="5">
+        <v>4</v>
+      </c>
+      <c r="B756" s="5">
+        <v>755</v>
+      </c>
+      <c r="C756" s="50">
+        <v>46127</v>
+      </c>
+      <c r="D756" s="13">
+        <v>49.5</v>
+      </c>
+      <c r="E756" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="F756" s="8">
+        <v>0</v>
+      </c>
+      <c r="G756" s="8">
+        <v>0</v>
+      </c>
+      <c r="H756" s="8">
+        <v>9</v>
+      </c>
+      <c r="J756" s="8">
+        <v>8.4049999999999994</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="5">
+        <v>5</v>
+      </c>
+      <c r="B757" s="5">
+        <v>756</v>
+      </c>
+      <c r="C757" s="50">
+        <v>46128</v>
+      </c>
+      <c r="D757" s="13">
+        <v>52</v>
+      </c>
+      <c r="E757" s="8">
+        <v>48.5</v>
+      </c>
+      <c r="F757" s="8">
+        <v>0.17</v>
+      </c>
+      <c r="G757" s="8">
+        <v>0</v>
+      </c>
+      <c r="H757" s="8">
+        <v>8</v>
+      </c>
+      <c r="J757" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="5">
+        <v>6</v>
+      </c>
+      <c r="B758" s="5">
+        <v>757</v>
+      </c>
+      <c r="C758" s="50">
+        <v>46129</v>
+      </c>
+      <c r="D758" s="13">
+        <v>112.5</v>
+      </c>
+      <c r="E758" s="8">
+        <v>46</v>
+      </c>
+      <c r="F758" s="8">
+        <v>0</v>
+      </c>
+      <c r="G758" s="8">
+        <v>0</v>
+      </c>
+      <c r="H758" s="8">
+        <v>10</v>
+      </c>
+      <c r="J758" s="8">
+        <v>12.469999999999999</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A743">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="A2:A758">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21137,7 +21626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8670AF5D-84FB-432F-8F14-677D63D19C50}">
-  <dimension ref="A1:X295"/>
+  <dimension ref="A1:X310"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -36483,63 +36972,77 @@
       </c>
       <c r="W258" s="36"/>
     </row>
-    <row r="259" spans="1:23" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B259" s="26">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A259" s="13">
+        <v>46</v>
+      </c>
+      <c r="B259" s="21">
         <v>46084</v>
       </c>
-      <c r="C259" s="27">
+      <c r="C259">
         <v>42</v>
       </c>
-      <c r="D259" s="27">
+      <c r="D259">
         <v>46</v>
       </c>
-      <c r="E259" s="27">
+      <c r="E259">
         <v>46</v>
       </c>
-      <c r="F259" s="27">
+      <c r="F259">
         <v>49</v>
       </c>
-      <c r="G259" s="27">
+      <c r="G259">
         <v>42</v>
       </c>
-      <c r="H259" s="27">
+      <c r="H259">
         <v>30</v>
       </c>
-      <c r="I259" s="27">
+      <c r="I259">
         <v>50</v>
       </c>
-      <c r="J259" s="27">
+      <c r="J259">
         <v>43</v>
       </c>
-      <c r="K259" s="27">
+      <c r="K259">
         <v>51</v>
       </c>
-      <c r="L259" s="27">
+      <c r="L259">
         <v>43</v>
       </c>
-      <c r="M259" s="27">
+      <c r="M259">
         <v>43</v>
       </c>
-      <c r="N259" s="27">
+      <c r="N259">
         <v>43</v>
       </c>
-      <c r="O259" s="64">
+      <c r="O259" s="19">
         <f t="shared" si="38"/>
         <v>45</v>
       </c>
-      <c r="P259" s="64">
+      <c r="P259" s="19">
         <f t="shared" si="39"/>
         <v>5.62</v>
       </c>
-      <c r="T259" s="27">
+      <c r="R259" s="25">
+        <f t="shared" ref="R259:R271" si="51">O259-A259</f>
+        <v>-1</v>
+      </c>
+      <c r="S259">
+        <f t="shared" ref="S259:S271" si="52">O259/A259</f>
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="T259">
         <v>55</v>
       </c>
-      <c r="U259" s="27">
+      <c r="U259">
         <v>47</v>
       </c>
-      <c r="W259" s="65"/>
+      <c r="W259" s="36"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A260" s="13">
+        <v>21</v>
+      </c>
       <c r="B260" s="21">
         <v>46085</v>
       </c>
@@ -36587,6 +37090,14 @@
         <f t="shared" si="39"/>
         <v>4.47</v>
       </c>
+      <c r="R260" s="25">
+        <f t="shared" si="51"/>
+        <v>21</v>
+      </c>
+      <c r="S260">
+        <f t="shared" si="52"/>
+        <v>2</v>
+      </c>
       <c r="T260">
         <v>48</v>
       </c>
@@ -36596,6 +37107,9 @@
       <c r="W260" s="36"/>
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A261" s="13">
+        <v>40</v>
+      </c>
       <c r="B261" s="21">
         <v>46086</v>
       </c>
@@ -36643,6 +37157,14 @@
         <f t="shared" si="39"/>
         <v>4.79</v>
       </c>
+      <c r="R261" s="25">
+        <f t="shared" si="51"/>
+        <v>7</v>
+      </c>
+      <c r="S261">
+        <f t="shared" si="52"/>
+        <v>1.175</v>
+      </c>
       <c r="T261">
         <v>50</v>
       </c>
@@ -36652,6 +37174,9 @@
       <c r="W261" s="36"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A262" s="13">
+        <v>120</v>
+      </c>
       <c r="B262" s="21">
         <v>46087</v>
       </c>
@@ -36692,12 +37217,20 @@
         <v>90</v>
       </c>
       <c r="O262" s="19">
-        <f t="shared" ref="O262:O263" si="51">ROUND(AVERAGE(C262:N262,T262:U262),0)</f>
+        <f t="shared" ref="O262:O263" si="53">ROUND(AVERAGE(C262:N262,T262:U262),0)</f>
         <v>88</v>
       </c>
       <c r="P262" s="19">
-        <f t="shared" ref="P262:P263" si="52">ROUND(_xlfn.STDEV.P(C262:N262,T262:U262),2)</f>
+        <f t="shared" ref="P262:P263" si="54">ROUND(_xlfn.STDEV.P(C262:N262,T262:U262),2)</f>
         <v>11.19</v>
+      </c>
+      <c r="R262" s="25">
+        <f t="shared" si="51"/>
+        <v>-32</v>
+      </c>
+      <c r="S262">
+        <f t="shared" si="52"/>
+        <v>0.73333333333333328</v>
       </c>
       <c r="T262">
         <v>112</v>
@@ -36708,6 +37241,9 @@
       <c r="W262" s="36"/>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A263" s="13">
+        <v>157</v>
+      </c>
       <c r="B263" s="21">
         <v>46088</v>
       </c>
@@ -36748,12 +37284,20 @@
         <v>147</v>
       </c>
       <c r="O263" s="19">
+        <f t="shared" si="53"/>
+        <v>156</v>
+      </c>
+      <c r="P263" s="19">
+        <f t="shared" si="54"/>
+        <v>17.190000000000001</v>
+      </c>
+      <c r="R263" s="25">
         <f t="shared" si="51"/>
-        <v>156</v>
-      </c>
-      <c r="P263" s="19">
+        <v>-1</v>
+      </c>
+      <c r="S263">
         <f t="shared" si="52"/>
-        <v>17.190000000000001</v>
+        <v>0.99363057324840764</v>
       </c>
       <c r="T263">
         <v>169</v>
@@ -36764,6 +37308,9 @@
       <c r="W263" s="36"/>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A264" s="13">
+        <v>54</v>
+      </c>
       <c r="B264" s="21">
         <v>46089</v>
       </c>
@@ -36804,12 +37351,20 @@
         <v>37</v>
       </c>
       <c r="O264" s="19">
-        <f t="shared" ref="O264" si="53">ROUND(AVERAGE(C264:N264,T264:U264),0)</f>
+        <f t="shared" ref="O264" si="55">ROUND(AVERAGE(C264:N264,T264:U264),0)</f>
         <v>42</v>
       </c>
       <c r="P264" s="19">
-        <f t="shared" ref="P264" si="54">ROUND(_xlfn.STDEV.P(C264:N264,T264:U264),2)</f>
+        <f t="shared" ref="P264" si="56">ROUND(_xlfn.STDEV.P(C264:N264,T264:U264),2)</f>
         <v>6.41</v>
+      </c>
+      <c r="R264" s="25">
+        <f t="shared" si="51"/>
+        <v>-12</v>
+      </c>
+      <c r="S264">
+        <f t="shared" si="52"/>
+        <v>0.77777777777777779</v>
       </c>
       <c r="T264">
         <v>46</v>
@@ -36819,6 +37374,9 @@
       </c>
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A265" s="13">
+        <v>28</v>
+      </c>
       <c r="B265" s="21">
         <v>46090</v>
       </c>
@@ -36859,12 +37417,20 @@
         <v>47</v>
       </c>
       <c r="O265" s="19">
-        <f t="shared" ref="O265:O289" si="55">ROUND(AVERAGE(C265:N265,T265:U265),0)</f>
+        <f t="shared" ref="O265:O289" si="57">ROUND(AVERAGE(C265:N265,T265:U265),0)</f>
         <v>50</v>
       </c>
       <c r="P265" s="19">
-        <f t="shared" ref="P265:P289" si="56">ROUND(_xlfn.STDEV.P(C265:N265,T265:U265),2)</f>
+        <f t="shared" ref="P265:P289" si="58">ROUND(_xlfn.STDEV.P(C265:N265,T265:U265),2)</f>
         <v>5.98</v>
+      </c>
+      <c r="R265" s="25">
+        <f t="shared" si="51"/>
+        <v>22</v>
+      </c>
+      <c r="S265">
+        <f t="shared" si="52"/>
+        <v>1.7857142857142858</v>
       </c>
       <c r="T265">
         <v>49</v>
@@ -36874,6 +37440,9 @@
       </c>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A266" s="13">
+        <v>33</v>
+      </c>
       <c r="B266" s="21">
         <v>46091</v>
       </c>
@@ -36914,12 +37483,20 @@
         <v>45</v>
       </c>
       <c r="O266" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>53</v>
       </c>
       <c r="P266" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>4.07</v>
+      </c>
+      <c r="R266" s="25">
+        <f t="shared" si="51"/>
+        <v>20</v>
+      </c>
+      <c r="S266">
+        <f t="shared" si="52"/>
+        <v>1.606060606060606</v>
       </c>
       <c r="T266">
         <v>54</v>
@@ -36929,6 +37506,9 @@
       </c>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A267" s="13">
+        <v>31</v>
+      </c>
       <c r="B267" s="21">
         <v>46092</v>
       </c>
@@ -36969,12 +37549,20 @@
         <v>42</v>
       </c>
       <c r="O267" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>45</v>
       </c>
       <c r="P267" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>3.29</v>
+      </c>
+      <c r="R267" s="25">
+        <f t="shared" si="51"/>
+        <v>14</v>
+      </c>
+      <c r="S267">
+        <f t="shared" si="52"/>
+        <v>1.4516129032258065</v>
       </c>
       <c r="T267">
         <v>50</v>
@@ -36984,6 +37572,9 @@
       </c>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A268" s="13">
+        <v>34</v>
+      </c>
       <c r="B268" s="21">
         <v>46093</v>
       </c>
@@ -37024,12 +37615,20 @@
         <v>40</v>
       </c>
       <c r="O268" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>47</v>
       </c>
       <c r="P268" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>7.2</v>
+      </c>
+      <c r="R268" s="25">
+        <f t="shared" si="51"/>
+        <v>13</v>
+      </c>
+      <c r="S268">
+        <f t="shared" si="52"/>
+        <v>1.3823529411764706</v>
       </c>
       <c r="T268">
         <v>59</v>
@@ -37039,6 +37638,9 @@
       </c>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A269" s="13">
+        <v>111</v>
+      </c>
       <c r="B269" s="21">
         <v>46094</v>
       </c>
@@ -37079,12 +37681,20 @@
         <v>72</v>
       </c>
       <c r="O269" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>75</v>
       </c>
       <c r="P269" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>7.13</v>
+      </c>
+      <c r="R269" s="25">
+        <f t="shared" si="51"/>
+        <v>-36</v>
+      </c>
+      <c r="S269">
+        <f t="shared" si="52"/>
+        <v>0.67567567567567566</v>
       </c>
       <c r="T269">
         <v>88</v>
@@ -37094,6 +37704,9 @@
       </c>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A270" s="13">
+        <v>135</v>
+      </c>
       <c r="B270" s="21">
         <v>46095</v>
       </c>
@@ -37134,12 +37747,20 @@
         <v>145</v>
       </c>
       <c r="O270" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>137</v>
       </c>
       <c r="P270" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>10.34</v>
+      </c>
+      <c r="R270" s="25">
+        <f t="shared" si="51"/>
+        <v>2</v>
+      </c>
+      <c r="S270">
+        <f t="shared" si="52"/>
+        <v>1.0148148148148148</v>
       </c>
       <c r="T270">
         <v>142</v>
@@ -37149,6 +37770,9 @@
       </c>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A271" s="13">
+        <v>32</v>
+      </c>
       <c r="B271" s="21">
         <v>46096</v>
       </c>
@@ -37189,12 +37813,20 @@
         <v>47</v>
       </c>
       <c r="O271" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>54</v>
       </c>
       <c r="P271" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>16.43</v>
+      </c>
+      <c r="R271" s="25">
+        <f t="shared" si="51"/>
+        <v>22</v>
+      </c>
+      <c r="S271">
+        <f t="shared" si="52"/>
+        <v>1.6875</v>
       </c>
       <c r="T271">
         <v>104</v>
@@ -37208,54 +37840,54 @@
         <v>46097</v>
       </c>
       <c r="C272">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D272">
+        <v>40</v>
+      </c>
+      <c r="E272">
+        <v>47</v>
+      </c>
+      <c r="F272">
+        <v>41</v>
+      </c>
+      <c r="G272">
+        <v>49</v>
+      </c>
+      <c r="H272">
+        <v>42</v>
+      </c>
+      <c r="I272">
         <v>48</v>
       </c>
-      <c r="E272">
-        <v>51</v>
-      </c>
-      <c r="F272">
+      <c r="J272">
+        <v>38</v>
+      </c>
+      <c r="K272">
         <v>48</v>
       </c>
-      <c r="G272">
-        <v>45</v>
-      </c>
-      <c r="H272">
-        <v>35</v>
-      </c>
-      <c r="I272">
-        <v>57</v>
-      </c>
-      <c r="J272">
+      <c r="L272">
+        <v>43</v>
+      </c>
+      <c r="M272">
         <v>44</v>
       </c>
-      <c r="K272">
-        <v>63</v>
-      </c>
-      <c r="L272">
-        <v>48</v>
-      </c>
-      <c r="M272">
-        <v>47</v>
-      </c>
       <c r="N272">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O272" s="19">
-        <f t="shared" si="55"/>
-        <v>49</v>
+        <f t="shared" si="57"/>
+        <v>43</v>
       </c>
       <c r="P272" s="19">
-        <f t="shared" si="56"/>
-        <v>6.96</v>
+        <f t="shared" si="58"/>
+        <v>3.7</v>
       </c>
       <c r="T272">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="U272">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="273" spans="2:21" x14ac:dyDescent="0.25">
@@ -37263,51 +37895,51 @@
         <v>46098</v>
       </c>
       <c r="C273">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D273">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E273">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F273">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G273">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H273">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I273">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J273">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K273">
         <v>44</v>
       </c>
       <c r="L273">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M273">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N273">
         <v>26</v>
       </c>
       <c r="O273" s="19">
-        <f t="shared" si="55"/>
-        <v>33</v>
+        <f t="shared" si="57"/>
+        <v>35</v>
       </c>
       <c r="P273" s="19">
-        <f t="shared" si="56"/>
-        <v>10.02</v>
+        <f t="shared" si="58"/>
+        <v>9.09</v>
       </c>
       <c r="T273">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="U273">
         <v>24</v>
@@ -37318,54 +37950,54 @@
         <v>46099</v>
       </c>
       <c r="C274">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D274">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E274">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F274">
+        <v>43</v>
+      </c>
+      <c r="G274">
+        <v>37</v>
+      </c>
+      <c r="H274">
+        <v>45</v>
+      </c>
+      <c r="I274">
+        <v>57</v>
+      </c>
+      <c r="J274">
+        <v>44</v>
+      </c>
+      <c r="K274">
         <v>47</v>
       </c>
-      <c r="G274">
-        <v>43</v>
-      </c>
-      <c r="H274">
-        <v>38</v>
-      </c>
-      <c r="I274">
-        <v>54</v>
-      </c>
-      <c r="J274">
-        <v>39</v>
-      </c>
-      <c r="K274">
-        <v>46</v>
-      </c>
       <c r="L274">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M274">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N274">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O274" s="19">
-        <f t="shared" si="55"/>
-        <v>46</v>
+        <f t="shared" si="57"/>
+        <v>45</v>
       </c>
       <c r="P274" s="19">
-        <f t="shared" si="56"/>
-        <v>7.84</v>
+        <f t="shared" si="58"/>
+        <v>4.37</v>
       </c>
       <c r="T274">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="U274">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="275" spans="2:21" x14ac:dyDescent="0.25">
@@ -37373,54 +38005,54 @@
         <v>46100</v>
       </c>
       <c r="C275">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D275">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E275">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F275">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G275">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H275">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I275">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J275">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K275">
         <v>55</v>
       </c>
       <c r="L275">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M275">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="N275">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O275" s="19">
-        <f t="shared" si="55"/>
-        <v>56</v>
+        <f t="shared" si="57"/>
+        <v>55</v>
       </c>
       <c r="P275" s="19">
-        <f t="shared" si="56"/>
-        <v>8.59</v>
+        <f t="shared" si="58"/>
+        <v>6.19</v>
       </c>
       <c r="T275">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="U275">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="276" spans="2:21" x14ac:dyDescent="0.25">
@@ -37428,54 +38060,54 @@
         <v>46101</v>
       </c>
       <c r="C276">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="D276">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E276">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="F276">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="G276">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="H276">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="I276">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="J276">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="K276">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="L276">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="M276">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="N276">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="O276" s="19">
-        <f t="shared" si="55"/>
-        <v>80</v>
+        <f t="shared" si="57"/>
+        <v>116</v>
       </c>
       <c r="P276" s="19">
-        <f t="shared" si="56"/>
-        <v>9.51</v>
+        <f t="shared" si="58"/>
+        <v>11.9</v>
       </c>
       <c r="T276">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="U276">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="277" spans="2:21" x14ac:dyDescent="0.25">
@@ -37483,54 +38115,54 @@
         <v>46102</v>
       </c>
       <c r="C277">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="D277">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E277">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="F277">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="G277">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="H277">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I277">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="J277">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="K277">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="L277">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="M277">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N277">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="O277" s="19">
-        <f t="shared" si="55"/>
-        <v>102</v>
+        <f t="shared" si="57"/>
+        <v>132</v>
       </c>
       <c r="P277" s="19">
-        <f t="shared" si="56"/>
-        <v>13</v>
+        <f t="shared" si="58"/>
+        <v>12.22</v>
       </c>
       <c r="T277">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="U277">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278" spans="2:21" x14ac:dyDescent="0.25">
@@ -37538,54 +38170,54 @@
         <v>46103</v>
       </c>
       <c r="C278">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D278">
+        <v>39</v>
+      </c>
+      <c r="E278">
+        <v>52</v>
+      </c>
+      <c r="F278">
+        <v>41</v>
+      </c>
+      <c r="G278">
+        <v>48</v>
+      </c>
+      <c r="H278">
+        <v>42</v>
+      </c>
+      <c r="I278">
         <v>47</v>
       </c>
-      <c r="E278">
-        <v>73</v>
-      </c>
-      <c r="F278">
+      <c r="J278">
+        <v>40</v>
+      </c>
+      <c r="K278">
+        <v>46</v>
+      </c>
+      <c r="L278">
+        <v>40</v>
+      </c>
+      <c r="M278">
+        <v>54</v>
+      </c>
+      <c r="N278">
+        <v>44</v>
+      </c>
+      <c r="O278" s="19">
+        <f t="shared" si="57"/>
         <v>45</v>
       </c>
-      <c r="G278">
-        <v>42</v>
-      </c>
-      <c r="H278">
-        <v>28</v>
-      </c>
-      <c r="I278">
-        <v>53</v>
-      </c>
-      <c r="J278">
-        <v>45</v>
-      </c>
-      <c r="K278">
-        <v>52</v>
-      </c>
-      <c r="L278">
-        <v>48</v>
-      </c>
-      <c r="M278">
-        <v>53</v>
-      </c>
-      <c r="N278">
-        <v>49</v>
-      </c>
-      <c r="O278" s="19">
-        <f t="shared" si="55"/>
-        <v>48</v>
-      </c>
       <c r="P278" s="19">
-        <f t="shared" si="56"/>
-        <v>9.69</v>
+        <f t="shared" si="58"/>
+        <v>4.96</v>
       </c>
       <c r="T278">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U278">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="279" spans="2:21" x14ac:dyDescent="0.25">
@@ -37596,51 +38228,51 @@
         <v>58</v>
       </c>
       <c r="D279">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E279">
+        <v>51</v>
+      </c>
+      <c r="F279">
+        <v>43</v>
+      </c>
+      <c r="G279">
+        <v>45</v>
+      </c>
+      <c r="H279">
+        <v>42</v>
+      </c>
+      <c r="I279">
+        <v>51</v>
+      </c>
+      <c r="J279">
+        <v>42</v>
+      </c>
+      <c r="K279">
+        <v>58</v>
+      </c>
+      <c r="L279">
         <v>50</v>
       </c>
-      <c r="F279">
-        <v>36</v>
-      </c>
-      <c r="G279">
-        <v>52</v>
-      </c>
-      <c r="H279">
-        <v>33</v>
-      </c>
-      <c r="I279">
+      <c r="M279">
+        <v>60</v>
+      </c>
+      <c r="N279">
         <v>46</v>
       </c>
-      <c r="J279">
-        <v>38</v>
-      </c>
-      <c r="K279">
-        <v>52</v>
-      </c>
-      <c r="L279">
-        <v>37</v>
-      </c>
-      <c r="M279">
-        <v>40</v>
-      </c>
-      <c r="N279">
-        <v>38</v>
-      </c>
       <c r="O279" s="19">
-        <f t="shared" si="55"/>
-        <v>43</v>
+        <f t="shared" si="57"/>
+        <v>50</v>
       </c>
       <c r="P279" s="19">
-        <f t="shared" si="56"/>
-        <v>7.44</v>
+        <f t="shared" si="58"/>
+        <v>6.23</v>
       </c>
       <c r="T279">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="U279">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="280" spans="2:21" x14ac:dyDescent="0.25">
@@ -37648,54 +38280,54 @@
         <v>46105</v>
       </c>
       <c r="C280">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D280">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E280">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F280">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G280">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H280">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I280">
         <v>47</v>
       </c>
       <c r="J280">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K280">
+        <v>48</v>
+      </c>
+      <c r="L280">
         <v>46</v>
       </c>
-      <c r="L280">
-        <v>40</v>
-      </c>
       <c r="M280">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N280">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O280" s="19">
-        <f t="shared" si="55"/>
-        <v>43</v>
+        <f t="shared" si="57"/>
+        <v>46</v>
       </c>
       <c r="P280" s="19">
-        <f t="shared" si="56"/>
-        <v>4.95</v>
+        <f t="shared" si="58"/>
+        <v>7.15</v>
       </c>
       <c r="T280">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="U280">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="281" spans="2:21" x14ac:dyDescent="0.25">
@@ -37703,54 +38335,54 @@
         <v>46106</v>
       </c>
       <c r="C281">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D281">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E281">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F281">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G281">
         <v>44</v>
       </c>
       <c r="H281">
+        <v>45</v>
+      </c>
+      <c r="I281">
+        <v>46</v>
+      </c>
+      <c r="J281">
+        <v>42</v>
+      </c>
+      <c r="K281">
+        <v>56</v>
+      </c>
+      <c r="L281">
         <v>41</v>
       </c>
-      <c r="I281">
-        <v>57</v>
-      </c>
-      <c r="J281">
-        <v>39</v>
-      </c>
-      <c r="K281">
+      <c r="M281">
+        <v>47</v>
+      </c>
+      <c r="N281">
+        <v>40</v>
+      </c>
+      <c r="O281" s="19">
+        <f t="shared" si="57"/>
+        <v>46</v>
+      </c>
+      <c r="P281" s="19">
+        <f t="shared" si="58"/>
+        <v>5.05</v>
+      </c>
+      <c r="T281">
         <v>49</v>
       </c>
-      <c r="L281">
-        <v>40</v>
-      </c>
-      <c r="M281">
+      <c r="U281">
         <v>41</v>
-      </c>
-      <c r="N281">
-        <v>39</v>
-      </c>
-      <c r="O281" s="19">
-        <f t="shared" si="55"/>
-        <v>48</v>
-      </c>
-      <c r="P281" s="19">
-        <f t="shared" si="56"/>
-        <v>9.6</v>
-      </c>
-      <c r="T281">
-        <v>62</v>
-      </c>
-      <c r="U281">
-        <v>43</v>
       </c>
     </row>
     <row r="282" spans="2:21" x14ac:dyDescent="0.25">
@@ -37758,54 +38390,54 @@
         <v>46107</v>
       </c>
       <c r="C282">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D282">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E282">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F282">
+        <v>51</v>
+      </c>
+      <c r="G282">
+        <v>45</v>
+      </c>
+      <c r="H282">
+        <v>58</v>
+      </c>
+      <c r="I282">
         <v>53</v>
-      </c>
-      <c r="G282">
-        <v>58</v>
-      </c>
-      <c r="H282">
-        <v>67</v>
-      </c>
-      <c r="I282">
-        <v>60</v>
       </c>
       <c r="J282">
         <v>49</v>
       </c>
       <c r="K282">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="L282">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M282">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N282">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O282" s="19">
-        <f t="shared" si="55"/>
-        <v>56</v>
+        <f t="shared" si="57"/>
+        <v>48</v>
       </c>
       <c r="P282" s="19">
-        <f t="shared" si="56"/>
-        <v>8.27</v>
+        <f t="shared" si="58"/>
+        <v>4.38</v>
       </c>
       <c r="T282">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="U282">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="283" spans="2:21" x14ac:dyDescent="0.25">
@@ -37813,54 +38445,54 @@
         <v>46108</v>
       </c>
       <c r="C283">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D283">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E283">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F283">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G283">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H283">
+        <v>82</v>
+      </c>
+      <c r="I283">
+        <v>112</v>
+      </c>
+      <c r="J283">
         <v>81</v>
       </c>
-      <c r="I283">
-        <v>83</v>
-      </c>
-      <c r="J283">
-        <v>65</v>
-      </c>
       <c r="K283">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="L283">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M283">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="N283">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O283" s="19">
-        <f t="shared" si="55"/>
-        <v>76</v>
+        <f t="shared" si="57"/>
+        <v>88</v>
       </c>
       <c r="P283" s="19">
-        <f t="shared" si="56"/>
-        <v>5.45</v>
+        <f t="shared" si="58"/>
+        <v>10</v>
       </c>
       <c r="T283">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="U283">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="284" spans="2:21" x14ac:dyDescent="0.25">
@@ -37868,54 +38500,54 @@
         <v>46109</v>
       </c>
       <c r="C284">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D284">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E284">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F284">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G284">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H284">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I284">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="J284">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K284">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="L284">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M284">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N284">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="O284" s="19">
-        <f t="shared" si="55"/>
-        <v>132</v>
+        <f t="shared" si="57"/>
+        <v>128</v>
       </c>
       <c r="P284" s="19">
-        <f t="shared" si="56"/>
-        <v>13.52</v>
+        <f t="shared" si="58"/>
+        <v>11.24</v>
       </c>
       <c r="T284">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="U284">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="285" spans="2:21" x14ac:dyDescent="0.25">
@@ -37923,54 +38555,54 @@
         <v>46110</v>
       </c>
       <c r="C285">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D285">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E285">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F285">
         <v>51</v>
       </c>
       <c r="G285">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H285">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I285">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J285">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K285">
+        <v>55</v>
+      </c>
+      <c r="L285">
+        <v>53</v>
+      </c>
+      <c r="M285">
         <v>57</v>
       </c>
-      <c r="L285">
-        <v>46</v>
-      </c>
-      <c r="M285">
+      <c r="N285">
+        <v>51</v>
+      </c>
+      <c r="O285" s="19">
+        <f t="shared" si="57"/>
+        <v>53</v>
+      </c>
+      <c r="P285" s="19">
+        <f t="shared" si="58"/>
+        <v>5.23</v>
+      </c>
+      <c r="T285">
+        <v>66</v>
+      </c>
+      <c r="U285">
         <v>50</v>
-      </c>
-      <c r="N285">
-        <v>47</v>
-      </c>
-      <c r="O285" s="19">
-        <f t="shared" si="55"/>
-        <v>48</v>
-      </c>
-      <c r="P285" s="19">
-        <f t="shared" si="56"/>
-        <v>5.33</v>
-      </c>
-      <c r="T285">
-        <v>50</v>
-      </c>
-      <c r="U285">
-        <v>48</v>
       </c>
     </row>
     <row r="286" spans="2:21" x14ac:dyDescent="0.25">
@@ -37978,54 +38610,54 @@
         <v>46111</v>
       </c>
       <c r="C286">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D286">
+        <v>40</v>
+      </c>
+      <c r="E286">
         <v>48</v>
       </c>
-      <c r="E286">
-        <v>57</v>
-      </c>
       <c r="F286">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G286">
+        <v>46</v>
+      </c>
+      <c r="H286">
+        <v>44</v>
+      </c>
+      <c r="I286">
+        <v>46</v>
+      </c>
+      <c r="J286">
+        <v>41</v>
+      </c>
+      <c r="K286">
+        <v>47</v>
+      </c>
+      <c r="L286">
+        <v>40</v>
+      </c>
+      <c r="M286">
         <v>45</v>
       </c>
-      <c r="H286">
-        <v>36</v>
-      </c>
-      <c r="I286">
-        <v>60</v>
-      </c>
-      <c r="J286">
-        <v>45</v>
-      </c>
-      <c r="K286">
-        <v>70</v>
-      </c>
-      <c r="L286">
-        <v>49</v>
-      </c>
-      <c r="M286">
-        <v>49</v>
-      </c>
       <c r="N286">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O286" s="19">
-        <f t="shared" si="55"/>
-        <v>51</v>
+        <f t="shared" si="57"/>
+        <v>43</v>
       </c>
       <c r="P286" s="19">
-        <f t="shared" si="56"/>
-        <v>8.15</v>
+        <f t="shared" si="58"/>
+        <v>3.27</v>
       </c>
       <c r="T286">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="U286">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="287" spans="2:21" x14ac:dyDescent="0.25">
@@ -38033,54 +38665,54 @@
         <v>46112</v>
       </c>
       <c r="C287">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D287">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E287">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F287">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G287">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H287">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I287">
         <v>68</v>
       </c>
       <c r="J287">
+        <v>41</v>
+      </c>
+      <c r="K287">
+        <v>51</v>
+      </c>
+      <c r="L287">
+        <v>46</v>
+      </c>
+      <c r="M287">
+        <v>64</v>
+      </c>
+      <c r="N287">
         <v>42</v>
       </c>
-      <c r="K287">
-        <v>70</v>
-      </c>
-      <c r="L287">
-        <v>48</v>
-      </c>
-      <c r="M287">
-        <v>47</v>
-      </c>
-      <c r="N287">
-        <v>44</v>
-      </c>
       <c r="O287" s="19">
-        <f t="shared" si="55"/>
-        <v>53</v>
+        <f t="shared" si="57"/>
+        <v>49</v>
       </c>
       <c r="P287" s="19">
-        <f t="shared" si="56"/>
-        <v>11.02</v>
+        <f t="shared" si="58"/>
+        <v>9.23</v>
       </c>
       <c r="T287">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="U287">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="288" spans="2:21" x14ac:dyDescent="0.25">
@@ -38088,54 +38720,54 @@
         <v>46113</v>
       </c>
       <c r="C288">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D288">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E288">
+        <v>59</v>
+      </c>
+      <c r="F288">
+        <v>53</v>
+      </c>
+      <c r="G288">
+        <v>60</v>
+      </c>
+      <c r="H288">
+        <v>53</v>
+      </c>
+      <c r="I288">
         <v>58</v>
       </c>
-      <c r="F288">
-        <v>45</v>
-      </c>
-      <c r="G288">
-        <v>44</v>
-      </c>
-      <c r="H288">
-        <v>43</v>
-      </c>
-      <c r="I288">
-        <v>55</v>
-      </c>
       <c r="J288">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K288">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L288">
         <v>43</v>
       </c>
       <c r="M288">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N288">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O288" s="19">
-        <f t="shared" si="55"/>
-        <v>46</v>
+        <f t="shared" si="57"/>
+        <v>51</v>
       </c>
       <c r="P288" s="19">
-        <f t="shared" si="56"/>
-        <v>6.37</v>
+        <f t="shared" si="58"/>
+        <v>5.12</v>
       </c>
       <c r="T288">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="U288">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="289" spans="2:21" x14ac:dyDescent="0.25">
@@ -38143,363 +38775,1188 @@
         <v>46114</v>
       </c>
       <c r="C289">
+        <v>106</v>
+      </c>
+      <c r="D289">
+        <v>65</v>
+      </c>
+      <c r="E289">
+        <v>91</v>
+      </c>
+      <c r="F289">
+        <v>75</v>
+      </c>
+      <c r="G289">
         <v>77</v>
       </c>
-      <c r="D289">
+      <c r="H289">
+        <v>57</v>
+      </c>
+      <c r="I289">
+        <v>80</v>
+      </c>
+      <c r="J289">
+        <v>67</v>
+      </c>
+      <c r="K289">
+        <v>112</v>
+      </c>
+      <c r="L289">
         <v>78</v>
       </c>
-      <c r="E289">
-        <v>93</v>
-      </c>
-      <c r="F289">
+      <c r="M289">
+        <v>82</v>
+      </c>
+      <c r="N289">
         <v>69</v>
       </c>
-      <c r="G289">
-        <v>84</v>
-      </c>
-      <c r="H289">
+      <c r="O289" s="19">
+        <f t="shared" si="57"/>
+        <v>80</v>
+      </c>
+      <c r="P289" s="19">
+        <f t="shared" si="58"/>
+        <v>15.06</v>
+      </c>
+      <c r="T289">
+        <v>90</v>
+      </c>
+      <c r="U289">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="290" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B290" s="21">
+        <v>46115</v>
+      </c>
+      <c r="C290">
+        <v>90</v>
+      </c>
+      <c r="D290">
+        <v>62</v>
+      </c>
+      <c r="E290">
+        <v>94</v>
+      </c>
+      <c r="F290">
+        <v>77</v>
+      </c>
+      <c r="G290">
+        <v>65</v>
+      </c>
+      <c r="H290">
+        <v>71</v>
+      </c>
+      <c r="I290">
+        <v>86</v>
+      </c>
+      <c r="J290">
+        <v>72</v>
+      </c>
+      <c r="K290">
+        <v>96</v>
+      </c>
+      <c r="L290">
+        <v>92</v>
+      </c>
+      <c r="M290">
+        <v>92</v>
+      </c>
+      <c r="N290">
+        <v>65</v>
+      </c>
+      <c r="O290" s="19">
+        <f t="shared" ref="O290:O304" si="59">ROUND(AVERAGE(C290:N290,T290:U290),0)</f>
+        <v>80</v>
+      </c>
+      <c r="P290" s="19">
+        <f t="shared" ref="P290:P304" si="60">ROUND(_xlfn.STDEV.P(C290:N290,T290:U290),2)</f>
+        <v>12.17</v>
+      </c>
+      <c r="T290">
+        <v>90</v>
+      </c>
+      <c r="U290">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B291" s="21">
+        <v>46116</v>
+      </c>
+      <c r="C291">
+        <v>106</v>
+      </c>
+      <c r="D291">
+        <v>103</v>
+      </c>
+      <c r="E291">
+        <v>100</v>
+      </c>
+      <c r="F291">
+        <v>118</v>
+      </c>
+      <c r="G291">
+        <v>95</v>
+      </c>
+      <c r="H291">
+        <v>127</v>
+      </c>
+      <c r="I291">
+        <v>94</v>
+      </c>
+      <c r="J291">
+        <v>111</v>
+      </c>
+      <c r="K291">
+        <v>116</v>
+      </c>
+      <c r="L291">
+        <v>115</v>
+      </c>
+      <c r="M291">
+        <v>90</v>
+      </c>
+      <c r="N291">
+        <v>112</v>
+      </c>
+      <c r="O291" s="19">
+        <f t="shared" si="59"/>
+        <v>106</v>
+      </c>
+      <c r="P291" s="19">
+        <f t="shared" si="60"/>
+        <v>10.36</v>
+      </c>
+      <c r="T291">
+        <v>96</v>
+      </c>
+      <c r="U291">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="292" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B292" s="21">
+        <v>46117</v>
+      </c>
+      <c r="C292">
+        <v>43</v>
+      </c>
+      <c r="D292">
+        <v>30</v>
+      </c>
+      <c r="E292">
+        <v>47</v>
+      </c>
+      <c r="F292">
+        <v>28</v>
+      </c>
+      <c r="G292">
+        <v>38</v>
+      </c>
+      <c r="H292">
+        <v>24</v>
+      </c>
+      <c r="I292">
+        <v>46</v>
+      </c>
+      <c r="J292">
+        <v>28</v>
+      </c>
+      <c r="K292">
+        <v>45</v>
+      </c>
+      <c r="L292">
+        <v>31</v>
+      </c>
+      <c r="M292">
+        <v>37</v>
+      </c>
+      <c r="N292">
+        <v>30</v>
+      </c>
+      <c r="O292" s="19">
+        <f t="shared" si="59"/>
+        <v>35</v>
+      </c>
+      <c r="P292" s="19">
+        <f t="shared" si="60"/>
+        <v>7.38</v>
+      </c>
+      <c r="T292">
+        <v>35</v>
+      </c>
+      <c r="U292">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="293" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B293" s="21">
+        <v>46118</v>
+      </c>
+      <c r="C293">
+        <v>46</v>
+      </c>
+      <c r="D293">
+        <v>44</v>
+      </c>
+      <c r="E293">
+        <v>50</v>
+      </c>
+      <c r="F293">
+        <v>45</v>
+      </c>
+      <c r="G293">
+        <v>47</v>
+      </c>
+      <c r="H293">
+        <v>44</v>
+      </c>
+      <c r="I293">
+        <v>46</v>
+      </c>
+      <c r="J293">
+        <v>44</v>
+      </c>
+      <c r="K293">
+        <v>47</v>
+      </c>
+      <c r="L293">
+        <v>45</v>
+      </c>
+      <c r="M293">
+        <v>44</v>
+      </c>
+      <c r="N293">
+        <v>43</v>
+      </c>
+      <c r="O293" s="19">
+        <f t="shared" si="59"/>
+        <v>45</v>
+      </c>
+      <c r="P293" s="19">
+        <f t="shared" si="60"/>
+        <v>1.83</v>
+      </c>
+      <c r="T293">
+        <v>46</v>
+      </c>
+      <c r="U293">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="294" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B294" s="21">
+        <v>46119</v>
+      </c>
+      <c r="C294">
+        <v>49</v>
+      </c>
+      <c r="D294">
+        <v>44</v>
+      </c>
+      <c r="E294">
+        <v>56</v>
+      </c>
+      <c r="F294">
+        <v>45</v>
+      </c>
+      <c r="G294">
+        <v>49</v>
+      </c>
+      <c r="H294">
+        <v>43</v>
+      </c>
+      <c r="I294">
+        <v>48</v>
+      </c>
+      <c r="J294">
+        <v>45</v>
+      </c>
+      <c r="K294">
+        <v>47</v>
+      </c>
+      <c r="L294">
+        <v>48</v>
+      </c>
+      <c r="M294">
+        <v>63</v>
+      </c>
+      <c r="N294">
+        <v>45</v>
+      </c>
+      <c r="O294" s="19">
+        <f t="shared" si="59"/>
+        <v>49</v>
+      </c>
+      <c r="P294" s="19">
+        <f t="shared" si="60"/>
+        <v>5.46</v>
+      </c>
+      <c r="T294">
+        <v>54</v>
+      </c>
+      <c r="U294">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="295" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B295" s="21">
+        <v>46120</v>
+      </c>
+      <c r="C295">
+        <v>51</v>
+      </c>
+      <c r="D295">
+        <v>42</v>
+      </c>
+      <c r="E295">
+        <v>69</v>
+      </c>
+      <c r="F295">
+        <v>42</v>
+      </c>
+      <c r="G295">
+        <v>50</v>
+      </c>
+      <c r="H295">
+        <v>48</v>
+      </c>
+      <c r="I295">
+        <v>70</v>
+      </c>
+      <c r="J295">
+        <v>35</v>
+      </c>
+      <c r="K295">
+        <v>96</v>
+      </c>
+      <c r="L295">
+        <v>48</v>
+      </c>
+      <c r="M295">
+        <v>83</v>
+      </c>
+      <c r="N295">
+        <v>42</v>
+      </c>
+      <c r="O295" s="19">
+        <f t="shared" si="59"/>
+        <v>56</v>
+      </c>
+      <c r="P295" s="19">
+        <f t="shared" si="60"/>
+        <v>17.27</v>
+      </c>
+      <c r="T295">
+        <v>68</v>
+      </c>
+      <c r="U295">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="296" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B296" s="21">
+        <v>46121</v>
+      </c>
+      <c r="C296">
+        <v>72</v>
+      </c>
+      <c r="D296">
+        <v>47</v>
+      </c>
+      <c r="E296">
+        <v>58</v>
+      </c>
+      <c r="F296">
+        <v>54</v>
+      </c>
+      <c r="G296">
+        <v>51</v>
+      </c>
+      <c r="H296">
+        <v>57</v>
+      </c>
+      <c r="I296">
+        <v>63</v>
+      </c>
+      <c r="J296">
+        <v>52</v>
+      </c>
+      <c r="K296">
+        <v>66</v>
+      </c>
+      <c r="L296">
+        <v>52</v>
+      </c>
+      <c r="M296">
+        <v>61</v>
+      </c>
+      <c r="N296">
+        <v>51</v>
+      </c>
+      <c r="O296" s="19">
+        <f t="shared" si="59"/>
+        <v>57</v>
+      </c>
+      <c r="P296" s="19">
+        <f t="shared" si="60"/>
+        <v>6.7</v>
+      </c>
+      <c r="T296">
+        <v>59</v>
+      </c>
+      <c r="U296">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="297" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B297" s="21">
+        <v>46122</v>
+      </c>
+      <c r="C297">
+        <v>65</v>
+      </c>
+      <c r="D297">
+        <v>79</v>
+      </c>
+      <c r="E297">
+        <v>78</v>
+      </c>
+      <c r="F297">
+        <v>85</v>
+      </c>
+      <c r="G297">
+        <v>68</v>
+      </c>
+      <c r="H297">
+        <v>89</v>
+      </c>
+      <c r="I297">
+        <v>76</v>
+      </c>
+      <c r="J297">
+        <v>82</v>
+      </c>
+      <c r="K297">
+        <v>71</v>
+      </c>
+      <c r="L297">
+        <v>88</v>
+      </c>
+      <c r="M297">
+        <v>85</v>
+      </c>
+      <c r="N297">
+        <v>86</v>
+      </c>
+      <c r="O297" s="19">
+        <f t="shared" si="59"/>
+        <v>79</v>
+      </c>
+      <c r="P297" s="19">
+        <f t="shared" si="60"/>
+        <v>7.12</v>
+      </c>
+      <c r="T297">
+        <v>78</v>
+      </c>
+      <c r="U297">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="298" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B298" s="21">
+        <v>46123</v>
+      </c>
+      <c r="C298">
+        <v>158</v>
+      </c>
+      <c r="D298">
+        <v>131</v>
+      </c>
+      <c r="E298">
+        <v>142</v>
+      </c>
+      <c r="F298">
+        <v>150</v>
+      </c>
+      <c r="G298">
+        <v>132</v>
+      </c>
+      <c r="H298">
+        <v>132</v>
+      </c>
+      <c r="I298">
+        <v>141</v>
+      </c>
+      <c r="J298">
+        <v>136</v>
+      </c>
+      <c r="K298">
+        <v>158</v>
+      </c>
+      <c r="L298">
+        <v>152</v>
+      </c>
+      <c r="M298">
+        <v>168</v>
+      </c>
+      <c r="N298">
+        <v>138</v>
+      </c>
+      <c r="O298" s="19">
+        <f t="shared" si="59"/>
+        <v>145</v>
+      </c>
+      <c r="P298" s="19">
+        <f t="shared" si="60"/>
+        <v>11.04</v>
+      </c>
+      <c r="T298">
+        <v>149</v>
+      </c>
+      <c r="U298">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="299" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B299" s="21">
+        <v>46124</v>
+      </c>
+      <c r="C299">
+        <v>46</v>
+      </c>
+      <c r="D299">
+        <v>44</v>
+      </c>
+      <c r="E299">
+        <v>48</v>
+      </c>
+      <c r="F299">
+        <v>46</v>
+      </c>
+      <c r="G299">
+        <v>49</v>
+      </c>
+      <c r="H299">
+        <v>45</v>
+      </c>
+      <c r="I299">
+        <v>46</v>
+      </c>
+      <c r="J299">
+        <v>44</v>
+      </c>
+      <c r="K299">
+        <v>47</v>
+      </c>
+      <c r="L299">
+        <v>48</v>
+      </c>
+      <c r="M299">
+        <v>57</v>
+      </c>
+      <c r="N299">
+        <v>44</v>
+      </c>
+      <c r="O299" s="19">
+        <f t="shared" si="59"/>
+        <v>47</v>
+      </c>
+      <c r="P299" s="19">
+        <f t="shared" si="60"/>
+        <v>3.33</v>
+      </c>
+      <c r="T299">
+        <v>46</v>
+      </c>
+      <c r="U299">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="300" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B300" s="21">
+        <v>46125</v>
+      </c>
+      <c r="C300">
+        <v>70</v>
+      </c>
+      <c r="D300">
+        <v>50</v>
+      </c>
+      <c r="E300">
+        <v>61</v>
+      </c>
+      <c r="F300">
+        <v>50</v>
+      </c>
+      <c r="G300">
+        <v>62</v>
+      </c>
+      <c r="H300">
+        <v>41</v>
+      </c>
+      <c r="I300">
+        <v>61</v>
+      </c>
+      <c r="J300">
+        <v>46</v>
+      </c>
+      <c r="K300">
+        <v>72</v>
+      </c>
+      <c r="L300">
+        <v>50</v>
+      </c>
+      <c r="M300">
+        <v>62</v>
+      </c>
+      <c r="N300">
+        <v>53</v>
+      </c>
+      <c r="O300" s="19">
+        <f t="shared" si="59"/>
+        <v>57</v>
+      </c>
+      <c r="P300" s="19">
+        <f t="shared" si="60"/>
+        <v>9.24</v>
+      </c>
+      <c r="T300">
+        <v>69</v>
+      </c>
+      <c r="U300">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="301" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B301" s="21">
+        <v>46126</v>
+      </c>
+      <c r="C301">
+        <v>76</v>
+      </c>
+      <c r="D301">
+        <v>44</v>
+      </c>
+      <c r="E301">
+        <v>68</v>
+      </c>
+      <c r="F301">
+        <v>42</v>
+      </c>
+      <c r="G301">
+        <v>51</v>
+      </c>
+      <c r="H301">
+        <v>38</v>
+      </c>
+      <c r="I301">
+        <v>66</v>
+      </c>
+      <c r="J301">
+        <v>43</v>
+      </c>
+      <c r="K301">
+        <v>63</v>
+      </c>
+      <c r="L301">
+        <v>49</v>
+      </c>
+      <c r="M301">
+        <v>73</v>
+      </c>
+      <c r="N301">
+        <v>44</v>
+      </c>
+      <c r="O301" s="19">
+        <f t="shared" si="59"/>
+        <v>54</v>
+      </c>
+      <c r="P301" s="19">
+        <f t="shared" si="60"/>
+        <v>12.41</v>
+      </c>
+      <c r="T301">
+        <v>60</v>
+      </c>
+      <c r="U301">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="302" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B302" s="21">
+        <v>46127</v>
+      </c>
+      <c r="C302">
+        <v>60</v>
+      </c>
+      <c r="D302">
+        <v>48</v>
+      </c>
+      <c r="E302">
+        <v>57</v>
+      </c>
+      <c r="F302">
+        <v>49</v>
+      </c>
+      <c r="G302">
+        <v>51</v>
+      </c>
+      <c r="H302">
+        <v>47</v>
+      </c>
+      <c r="I302">
+        <v>58</v>
+      </c>
+      <c r="J302">
+        <v>49</v>
+      </c>
+      <c r="K302">
+        <v>54</v>
+      </c>
+      <c r="L302">
+        <v>54</v>
+      </c>
+      <c r="M302">
+        <v>60</v>
+      </c>
+      <c r="N302">
+        <v>49</v>
+      </c>
+      <c r="O302" s="19">
+        <f t="shared" si="59"/>
+        <v>53</v>
+      </c>
+      <c r="P302" s="19">
+        <f t="shared" si="60"/>
+        <v>4.46</v>
+      </c>
+      <c r="T302">
+        <v>57</v>
+      </c>
+      <c r="U302">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="303" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B303" s="21">
+        <v>46128</v>
+      </c>
+      <c r="C303">
+        <v>56</v>
+      </c>
+      <c r="D303">
+        <v>47</v>
+      </c>
+      <c r="E303">
+        <v>58</v>
+      </c>
+      <c r="F303">
+        <v>54</v>
+      </c>
+      <c r="G303">
+        <v>49</v>
+      </c>
+      <c r="H303">
+        <v>58</v>
+      </c>
+      <c r="I303">
+        <v>54</v>
+      </c>
+      <c r="J303">
+        <v>51</v>
+      </c>
+      <c r="K303">
+        <v>57</v>
+      </c>
+      <c r="L303">
+        <v>51</v>
+      </c>
+      <c r="M303">
+        <v>56</v>
+      </c>
+      <c r="N303">
+        <v>49</v>
+      </c>
+      <c r="O303" s="19">
+        <f t="shared" si="59"/>
+        <v>53</v>
+      </c>
+      <c r="P303" s="19">
+        <f t="shared" si="60"/>
+        <v>3.49</v>
+      </c>
+      <c r="T303">
+        <v>53</v>
+      </c>
+      <c r="U303">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="304" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B304" s="21">
+        <v>46129</v>
+      </c>
+      <c r="C304">
+        <v>125</v>
+      </c>
+      <c r="D304">
+        <v>109</v>
+      </c>
+      <c r="E304">
+        <v>123</v>
+      </c>
+      <c r="F304">
+        <v>114</v>
+      </c>
+      <c r="G304">
+        <v>97</v>
+      </c>
+      <c r="H304">
+        <v>105</v>
+      </c>
+      <c r="I304">
+        <v>127</v>
+      </c>
+      <c r="J304">
+        <v>108</v>
+      </c>
+      <c r="K304">
+        <v>120</v>
+      </c>
+      <c r="L304">
+        <v>125</v>
+      </c>
+      <c r="M304">
+        <v>123</v>
+      </c>
+      <c r="N304">
+        <v>113</v>
+      </c>
+      <c r="O304" s="19">
+        <f t="shared" si="59"/>
+        <v>116</v>
+      </c>
+      <c r="P304" s="19">
+        <f t="shared" si="60"/>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="T304">
+        <v>125</v>
+      </c>
+      <c r="U304">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="305" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B305" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C305">
+        <v>29.34</v>
+      </c>
+      <c r="D305">
+        <v>30.21</v>
+      </c>
+      <c r="E305">
+        <v>24.61</v>
+      </c>
+      <c r="F305" s="14">
+        <v>27.28</v>
+      </c>
+      <c r="G305" s="14">
+        <v>22.28</v>
+      </c>
+      <c r="H305" s="14">
+        <v>23.15</v>
+      </c>
+      <c r="I305" s="14">
+        <v>28.87</v>
+      </c>
+      <c r="J305" s="14">
+        <v>28.82</v>
+      </c>
+      <c r="K305" s="14">
+        <v>26.2</v>
+      </c>
+      <c r="L305" s="14">
+        <v>28.06</v>
+      </c>
+      <c r="M305" s="14">
+        <v>28.45</v>
+      </c>
+      <c r="N305" s="15">
+        <v>30.56</v>
+      </c>
+      <c r="O305" s="31">
+        <f>ROUND(AVERAGE(C305:N305,T305:U305),2)</f>
+        <v>27.05</v>
+      </c>
+      <c r="P305" s="31">
+        <f>ROUND(_xlfn.STDEV.P(C305:N305,T305:U305),2)</f>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="T305">
+        <v>24.56</v>
+      </c>
+      <c r="U305">
+        <v>26.35</v>
+      </c>
+    </row>
+    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B306" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C306">
+        <v>26.27</v>
+      </c>
+      <c r="D306">
+        <v>26.22</v>
+      </c>
+      <c r="E306">
+        <v>29.18</v>
+      </c>
+      <c r="F306">
+        <v>25.22</v>
+      </c>
+      <c r="G306">
+        <v>32.25</v>
+      </c>
+      <c r="H306">
+        <v>29.23</v>
+      </c>
+      <c r="I306">
+        <v>24.57</v>
+      </c>
+      <c r="J306">
+        <v>24.75</v>
+      </c>
+      <c r="K306">
+        <v>26.81</v>
+      </c>
+      <c r="L306">
+        <v>24.03</v>
+      </c>
+      <c r="M306" s="14">
+        <v>23.43</v>
+      </c>
+      <c r="N306" s="14">
+        <v>23.13</v>
+      </c>
+      <c r="O306" s="31">
+        <f>ROUND(AVERAGE(C306:N306,T306:U306),2)</f>
+        <v>26.4</v>
+      </c>
+      <c r="P306" s="31">
+        <f>ROUND(_xlfn.STDEV.P(C306:N306,T306:U306),2)</f>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T306">
+        <v>27.27</v>
+      </c>
+      <c r="U306">
+        <v>27.18</v>
+      </c>
+    </row>
+    <row r="307" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C307" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="D307" s="53"/>
+      <c r="E307" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F307" s="53"/>
+      <c r="G307" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="H307" s="53"/>
+      <c r="I307" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="J307" s="53"/>
+      <c r="K307" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="L307" s="58"/>
+      <c r="M307" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="N307" s="58"/>
+      <c r="T307" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="U307" s="53"/>
+    </row>
+    <row r="308" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C308" t="s">
+        <v>63</v>
+      </c>
+      <c r="D308" t="s">
         <v>64</v>
       </c>
-      <c r="I289">
-        <v>90</v>
-      </c>
-      <c r="J289">
+      <c r="E308" t="s">
         <v>63</v>
       </c>
-      <c r="K289">
-        <v>78</v>
-      </c>
-      <c r="L289">
-        <v>69</v>
-      </c>
-      <c r="M289">
+      <c r="F308" t="s">
+        <v>64</v>
+      </c>
+      <c r="G308" t="s">
+        <v>63</v>
+      </c>
+      <c r="H308" t="s">
+        <v>64</v>
+      </c>
+      <c r="I308" t="s">
+        <v>63</v>
+      </c>
+      <c r="J308" t="s">
+        <v>64</v>
+      </c>
+      <c r="K308" t="s">
+        <v>63</v>
+      </c>
+      <c r="L308" t="s">
+        <v>64</v>
+      </c>
+      <c r="M308" t="s">
+        <v>63</v>
+      </c>
+      <c r="N308" t="s">
+        <v>64</v>
+      </c>
+      <c r="T308" t="s">
+        <v>63</v>
+      </c>
+      <c r="U308" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="309" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>65</v>
+      </c>
+      <c r="C309">
+        <v>72.426000000000002</v>
+      </c>
+      <c r="D309">
+        <v>76.203999999999994</v>
+      </c>
+      <c r="E309">
+        <v>106.777</v>
+      </c>
+      <c r="F309">
+        <v>95.346999999999994</v>
+      </c>
+      <c r="G309">
+        <v>26.42</v>
+      </c>
+      <c r="H309">
+        <v>15.21</v>
+      </c>
+      <c r="I309">
+        <v>110.955</v>
+      </c>
+      <c r="J309">
+        <v>125.211</v>
+      </c>
+      <c r="K309">
+        <v>86.977999999999994</v>
+      </c>
+      <c r="L309">
+        <v>104.254</v>
+      </c>
+      <c r="M309">
+        <v>196.98699999999999</v>
+      </c>
+      <c r="N309">
+        <v>175.36099999999999</v>
+      </c>
+      <c r="T309">
+        <v>212.42099999999999</v>
+      </c>
+      <c r="U309">
+        <v>218.84200000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
         <v>67</v>
       </c>
-      <c r="N289">
-        <v>68</v>
-      </c>
-      <c r="O289" s="19">
-        <f t="shared" si="55"/>
-        <v>76</v>
-      </c>
-      <c r="P289" s="19">
-        <f t="shared" si="56"/>
-        <v>10.39</v>
-      </c>
-      <c r="T289">
-        <v>95</v>
-      </c>
-      <c r="U289">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="290" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B290" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C290">
-        <v>24.12</v>
-      </c>
-      <c r="D290">
-        <v>25</v>
-      </c>
-      <c r="E290">
-        <v>25.76</v>
-      </c>
-      <c r="F290" s="14">
-        <v>24.05</v>
-      </c>
-      <c r="G290" s="14">
-        <v>26.18</v>
-      </c>
-      <c r="H290" s="14">
-        <v>23.24</v>
-      </c>
-      <c r="I290" s="14">
-        <v>25.65</v>
-      </c>
-      <c r="J290" s="14">
-        <v>25.38</v>
-      </c>
-      <c r="K290" s="14">
-        <v>24.64</v>
-      </c>
-      <c r="L290" s="14">
-        <v>29.12</v>
-      </c>
-      <c r="M290" s="14">
-        <v>25.44</v>
-      </c>
-      <c r="N290" s="15">
-        <v>29.25</v>
-      </c>
-      <c r="O290" s="31">
-        <f>ROUND(AVERAGE(C290:N290,T290:U290),2)</f>
-        <v>25.61</v>
-      </c>
-      <c r="P290" s="31">
-        <f>ROUND(_xlfn.STDEV.P(C290:N290,T290:U290),2)</f>
-        <v>1.76</v>
-      </c>
-      <c r="T290">
-        <v>23.66</v>
-      </c>
-      <c r="U290">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B291" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C291">
-        <v>27.05</v>
-      </c>
-      <c r="D291">
-        <v>25.12</v>
-      </c>
-      <c r="E291">
-        <v>28.76</v>
-      </c>
-      <c r="F291">
-        <v>27.97</v>
-      </c>
-      <c r="G291">
-        <v>28.62</v>
-      </c>
-      <c r="H291">
-        <v>27.55</v>
-      </c>
-      <c r="I291">
-        <v>27.53</v>
-      </c>
-      <c r="J291">
-        <v>23.71</v>
-      </c>
-      <c r="K291">
-        <v>28.02</v>
-      </c>
-      <c r="L291">
-        <v>23.81</v>
-      </c>
-      <c r="M291" s="14">
-        <v>27.97</v>
-      </c>
-      <c r="N291" s="14">
-        <v>24.93</v>
-      </c>
-      <c r="O291" s="31">
-        <f>ROUND(AVERAGE(C291:N291,T291:U291),2)</f>
-        <v>26.88</v>
-      </c>
-      <c r="P291" s="31">
-        <f>ROUND(_xlfn.STDEV.P(C291:N291,T291:U291),2)</f>
-        <v>2.17</v>
-      </c>
-      <c r="T291">
-        <v>31.31</v>
-      </c>
-      <c r="U291">
-        <v>23.95</v>
-      </c>
-    </row>
-    <row r="292" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C292" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="D292" s="53"/>
-      <c r="E292" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="F292" s="53"/>
-      <c r="G292" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="H292" s="53"/>
-      <c r="I292" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="J292" s="53"/>
-      <c r="K292" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="L292" s="58"/>
-      <c r="M292" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="N292" s="58"/>
-      <c r="T292" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="U292" s="53"/>
-    </row>
-    <row r="293" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C293" t="s">
-        <v>63</v>
-      </c>
-      <c r="D293" t="s">
-        <v>64</v>
-      </c>
-      <c r="E293" t="s">
-        <v>63</v>
-      </c>
-      <c r="F293" t="s">
-        <v>64</v>
-      </c>
-      <c r="G293" t="s">
-        <v>63</v>
-      </c>
-      <c r="H293" t="s">
-        <v>64</v>
-      </c>
-      <c r="I293" t="s">
-        <v>63</v>
-      </c>
-      <c r="J293" t="s">
-        <v>64</v>
-      </c>
-      <c r="K293" t="s">
-        <v>63</v>
-      </c>
-      <c r="L293" t="s">
-        <v>64</v>
-      </c>
-      <c r="M293" t="s">
-        <v>63</v>
-      </c>
-      <c r="N293" t="s">
-        <v>64</v>
-      </c>
-      <c r="T293" t="s">
-        <v>63</v>
-      </c>
-      <c r="U293" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="294" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B294" t="s">
-        <v>65</v>
-      </c>
-      <c r="C294">
-        <v>82.424000000000007</v>
-      </c>
-      <c r="D294">
-        <v>82.721000000000004</v>
-      </c>
-      <c r="E294">
-        <v>98.254999999999995</v>
-      </c>
-      <c r="F294">
-        <v>96.980999999999995</v>
-      </c>
-      <c r="G294">
-        <v>25.186</v>
-      </c>
-      <c r="H294">
-        <v>14.311</v>
-      </c>
-      <c r="I294">
-        <v>158.57400000000001</v>
-      </c>
-      <c r="J294">
-        <v>131.16200000000001</v>
-      </c>
-      <c r="K294">
-        <v>97.951999999999998</v>
-      </c>
-      <c r="L294">
-        <v>98.364000000000004</v>
-      </c>
-      <c r="M294">
-        <v>191.887</v>
-      </c>
-      <c r="N294">
-        <v>183.61500000000001</v>
-      </c>
-      <c r="T294">
-        <v>226.39</v>
-      </c>
-      <c r="U294">
-        <v>197.57900000000001</v>
-      </c>
-    </row>
-    <row r="295" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B295" t="s">
-        <v>67</v>
-      </c>
-      <c r="C295" s="32"/>
-      <c r="D295" s="32"/>
-      <c r="E295" s="32"/>
-      <c r="F295" s="32"/>
-      <c r="G295" s="32"/>
-      <c r="H295" s="32"/>
-      <c r="I295" s="52">
-        <v>0.7722</v>
-      </c>
-      <c r="J295" s="52">
-        <v>0.8115</v>
-      </c>
-      <c r="K295" s="52">
-        <v>0.70320000000000005</v>
-      </c>
-      <c r="L295" s="52">
-        <v>0.7117</v>
-      </c>
-      <c r="M295" s="52">
-        <v>0.83540000000000003</v>
-      </c>
-      <c r="N295" s="52">
-        <v>0.70599999999999996</v>
-      </c>
-      <c r="T295" s="52">
-        <v>0.85650000000000004</v>
-      </c>
-      <c r="U295" s="52">
-        <v>0.73839999999999995</v>
+      <c r="C310" s="32"/>
+      <c r="D310" s="32"/>
+      <c r="E310" s="32"/>
+      <c r="F310" s="32"/>
+      <c r="G310" s="32"/>
+      <c r="H310" s="32"/>
+      <c r="I310" s="52">
+        <v>0.70440000000000003</v>
+      </c>
+      <c r="J310" s="52">
+        <v>0.73480000000000001</v>
+      </c>
+      <c r="K310" s="52">
+        <v>0.69479999999999997</v>
+      </c>
+      <c r="L310" s="52">
+        <v>0.86460000000000004</v>
+      </c>
+      <c r="M310" s="52">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="N310" s="52">
+        <v>0.68920000000000003</v>
+      </c>
+      <c r="T310" s="52">
+        <v>0.8135</v>
+      </c>
+      <c r="U310" s="52">
+        <v>0.83289999999999997</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="T292:U292"/>
+    <mergeCell ref="T307:U307"/>
     <mergeCell ref="C1:N1"/>
     <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C292:D292"/>
-    <mergeCell ref="I292:J292"/>
-    <mergeCell ref="G292:H292"/>
-    <mergeCell ref="E292:F292"/>
-    <mergeCell ref="K292:L292"/>
-    <mergeCell ref="M292:N292"/>
+    <mergeCell ref="C307:D307"/>
+    <mergeCell ref="I307:J307"/>
+    <mergeCell ref="G307:H307"/>
+    <mergeCell ref="E307:F307"/>
+    <mergeCell ref="K307:L307"/>
+    <mergeCell ref="M307:N307"/>
   </mergeCells>
-  <conditionalFormatting sqref="C98:N258 T142:U258">
-    <cfRule type="expression" dxfId="14" priority="3">
+  <conditionalFormatting sqref="C98:N271 T142:U271">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>ABS(C98-$A98)&lt;=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="24" priority="4">
       <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="23" priority="11">
       <formula>ABS(C98-$A98)&lt;=15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C290:N290 T290:U290">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
-      <formula>$O$290-$P$290</formula>
+  <conditionalFormatting sqref="C305:N305 T305:U305">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="lessThan">
+      <formula>$O$305-$P$305</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
-      <formula>$O$290+$P$290</formula>
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+      <formula>$O$305+$P$305</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="30" operator="between">
-      <formula>$O$290-$P$290</formula>
+    <cfRule type="cellIs" dxfId="20" priority="30" operator="between">
+      <formula>$O$305-$P$305</formula>
       <formula>"$O$264+$P$264"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C291:N291 T291:U291">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="C306:N306 T306:U306">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThan">
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R79 R81:R258">
+  <conditionalFormatting sqref="R3:R79 R81:R271">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -38516,7 +39973,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9BE2AF-C5F8-4B32-A88A-8E9C9CBC1046}">
-  <dimension ref="A1:W291"/>
+  <dimension ref="A1:W306"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -38703,11 +40160,11 @@
         <v>15.17</v>
       </c>
       <c r="R6" s="25">
-        <f t="shared" ref="R6:R69" si="4">O6-A6</f>
+        <f t="shared" ref="R6:R68" si="4">O6-A6</f>
         <v>9</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:S69" si="5">O6/A6</f>
+        <f t="shared" ref="S6:S68" si="5">O6/A6</f>
         <v>1.1607142857142858</v>
       </c>
     </row>
@@ -42062,14 +43519,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R69" s="25" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S69" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R69" s="25"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="13">
@@ -42086,14 +43536,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R70" s="25" t="e">
-        <f t="shared" ref="R70:R104" si="8">O70-A70</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S70" t="e">
-        <f t="shared" ref="S70:S104" si="9">O70/A70</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R70" s="25"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
@@ -42110,14 +43553,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R71" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S71" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R71" s="25"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
@@ -42134,14 +43570,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R72" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S72" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R72" s="25"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="13">
@@ -42158,14 +43587,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R73" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S73" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R73" s="25"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="13">
@@ -42182,14 +43604,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R74" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S74" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R74" s="25"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="13">
@@ -42237,11 +43652,11 @@
         <v>10.42</v>
       </c>
       <c r="R75" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="R75:R104" si="8">O75-A75</f>
         <v>-1</v>
       </c>
       <c r="S75">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="S75:S104" si="9">O75/A75</f>
         <v>0.98529411764705888</v>
       </c>
     </row>
@@ -43088,14 +44503,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R95" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S95" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R95" s="25"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="13">
@@ -43112,14 +44520,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R96" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S96" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R96" s="25"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="13">
@@ -43136,14 +44537,7 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R97" s="25" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S97" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R97" s="25"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
@@ -53520,63 +54914,77 @@
       </c>
       <c r="W258" s="36"/>
     </row>
-    <row r="259" spans="1:23" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B259" s="26">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A259" s="13">
+        <v>46</v>
+      </c>
+      <c r="B259" s="21">
         <v>46084</v>
       </c>
-      <c r="C259" s="27">
+      <c r="C259">
         <v>43</v>
       </c>
-      <c r="D259" s="27">
+      <c r="D259">
         <v>48</v>
       </c>
-      <c r="E259" s="27">
+      <c r="E259">
         <v>46</v>
       </c>
-      <c r="F259" s="27">
+      <c r="F259">
         <v>38</v>
       </c>
-      <c r="G259" s="27">
+      <c r="G259">
         <v>43</v>
       </c>
-      <c r="H259" s="27">
+      <c r="H259">
         <v>30</v>
       </c>
-      <c r="I259" s="27">
+      <c r="I259">
         <v>48</v>
       </c>
-      <c r="J259" s="27">
+      <c r="J259">
         <v>20</v>
       </c>
-      <c r="K259" s="27">
+      <c r="K259">
         <v>51</v>
       </c>
-      <c r="L259" s="27">
+      <c r="L259">
         <v>43</v>
       </c>
-      <c r="M259" s="27">
+      <c r="M259">
         <v>42</v>
       </c>
-      <c r="N259" s="27">
+      <c r="N259">
         <v>43</v>
       </c>
-      <c r="O259" s="64">
+      <c r="O259" s="19">
         <f t="shared" si="25"/>
         <v>41</v>
       </c>
-      <c r="P259" s="64">
+      <c r="P259" s="19">
         <f t="shared" si="26"/>
         <v>8.1199999999999992</v>
       </c>
-      <c r="T259" s="27">
+      <c r="R259" s="25">
+        <f t="shared" ref="R259:R271" si="39">O259-A259</f>
+        <v>-5</v>
+      </c>
+      <c r="S259">
+        <f t="shared" ref="S259:S271" si="40">O259/A259</f>
+        <v>0.89130434782608692</v>
+      </c>
+      <c r="T259">
         <v>48</v>
       </c>
-      <c r="U259" s="27">
+      <c r="U259">
         <v>33</v>
       </c>
-      <c r="W259" s="65"/>
+      <c r="W259" s="36"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A260" s="13">
+        <v>21</v>
+      </c>
       <c r="B260" s="21">
         <v>46085</v>
       </c>
@@ -53624,6 +55032,14 @@
         <f t="shared" si="26"/>
         <v>8.73</v>
       </c>
+      <c r="R260" s="25">
+        <f t="shared" si="39"/>
+        <v>16</v>
+      </c>
+      <c r="S260">
+        <f t="shared" si="40"/>
+        <v>1.7619047619047619</v>
+      </c>
       <c r="T260">
         <v>46</v>
       </c>
@@ -53633,6 +55049,9 @@
       <c r="W260" s="36"/>
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A261" s="13">
+        <v>40</v>
+      </c>
       <c r="B261" s="21">
         <v>46086</v>
       </c>
@@ -53680,6 +55099,14 @@
         <f t="shared" si="26"/>
         <v>9.2799999999999994</v>
       </c>
+      <c r="R261" s="25">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="S261">
+        <f t="shared" si="40"/>
+        <v>1.125</v>
+      </c>
       <c r="T261">
         <v>52</v>
       </c>
@@ -53689,6 +55116,9 @@
       <c r="W261" s="36"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A262" s="13">
+        <v>120</v>
+      </c>
       <c r="B262" s="21">
         <v>46087</v>
       </c>
@@ -53729,12 +55159,20 @@
         <v>91</v>
       </c>
       <c r="O262" s="19">
-        <f t="shared" ref="O262:O263" si="39">ROUND(AVERAGE(C262:N262,T262,U262),0)</f>
+        <f t="shared" ref="O262:O263" si="41">ROUND(AVERAGE(C262:N262,T262,U262),0)</f>
         <v>76</v>
       </c>
       <c r="P262" s="19">
-        <f t="shared" ref="P262:P263" si="40">ROUND(_xlfn.STDEV.P(C262:N262,T262,U262),2)</f>
+        <f t="shared" ref="P262:P263" si="42">ROUND(_xlfn.STDEV.P(C262:N262,T262,U262),2)</f>
         <v>22.54</v>
+      </c>
+      <c r="R262" s="25">
+        <f t="shared" si="39"/>
+        <v>-44</v>
+      </c>
+      <c r="S262">
+        <f t="shared" si="40"/>
+        <v>0.6333333333333333</v>
       </c>
       <c r="T262">
         <v>93</v>
@@ -53745,6 +55183,9 @@
       <c r="W262" s="36"/>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A263" s="13">
+        <v>157</v>
+      </c>
       <c r="B263" s="21">
         <v>46088</v>
       </c>
@@ -53785,12 +55226,20 @@
         <v>149</v>
       </c>
       <c r="O263" s="19">
+        <f t="shared" si="41"/>
+        <v>144</v>
+      </c>
+      <c r="P263" s="19">
+        <f t="shared" si="42"/>
+        <v>33.9</v>
+      </c>
+      <c r="R263" s="25">
         <f t="shared" si="39"/>
-        <v>144</v>
-      </c>
-      <c r="P263" s="19">
+        <v>-13</v>
+      </c>
+      <c r="S263">
         <f t="shared" si="40"/>
-        <v>33.9</v>
+        <v>0.91719745222929938</v>
       </c>
       <c r="T263">
         <v>165</v>
@@ -53801,6 +55250,9 @@
       <c r="W263" s="36"/>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A264" s="13">
+        <v>54</v>
+      </c>
       <c r="B264" s="21">
         <v>46089</v>
       </c>
@@ -53841,12 +55293,20 @@
         <v>38</v>
       </c>
       <c r="O264" s="19">
-        <f t="shared" ref="O264:O289" si="41">ROUND(AVERAGE(C264:N264,T264,U264),0)</f>
+        <f t="shared" ref="O264:O289" si="43">ROUND(AVERAGE(C264:N264,T264,U264),0)</f>
         <v>38</v>
       </c>
       <c r="P264" s="19">
-        <f t="shared" ref="P264:P289" si="42">ROUND(_xlfn.STDEV.P(C264:N264,T264,U264),2)</f>
+        <f t="shared" ref="P264:P289" si="44">ROUND(_xlfn.STDEV.P(C264:N264,T264,U264),2)</f>
         <v>10.09</v>
+      </c>
+      <c r="R264" s="25">
+        <f t="shared" si="39"/>
+        <v>-16</v>
+      </c>
+      <c r="S264">
+        <f t="shared" si="40"/>
+        <v>0.70370370370370372</v>
       </c>
       <c r="T264">
         <v>46</v>
@@ -53856,6 +55316,9 @@
       </c>
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A265" s="13">
+        <v>28</v>
+      </c>
       <c r="B265" s="21">
         <v>46090</v>
       </c>
@@ -53896,12 +55359,20 @@
         <v>47</v>
       </c>
       <c r="O265" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>45</v>
       </c>
       <c r="P265" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>10.45</v>
+      </c>
+      <c r="R265" s="25">
+        <f t="shared" si="39"/>
+        <v>17</v>
+      </c>
+      <c r="S265">
+        <f t="shared" si="40"/>
+        <v>1.6071428571428572</v>
       </c>
       <c r="T265">
         <v>47</v>
@@ -53911,6 +55382,9 @@
       </c>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A266" s="13">
+        <v>33</v>
+      </c>
       <c r="B266" s="21">
         <v>46091</v>
       </c>
@@ -53951,12 +55425,20 @@
         <v>43</v>
       </c>
       <c r="O266" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>44</v>
       </c>
       <c r="P266" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>10.94</v>
+      </c>
+      <c r="R266" s="25">
+        <f t="shared" si="39"/>
+        <v>11</v>
+      </c>
+      <c r="S266">
+        <f t="shared" si="40"/>
+        <v>1.3333333333333333</v>
       </c>
       <c r="T266">
         <v>47</v>
@@ -53966,6 +55448,9 @@
       </c>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A267" s="13">
+        <v>31</v>
+      </c>
       <c r="B267" s="21">
         <v>46092</v>
       </c>
@@ -54006,12 +55491,20 @@
         <v>42</v>
       </c>
       <c r="O267" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>41</v>
       </c>
       <c r="P267" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>10.039999999999999</v>
+      </c>
+      <c r="R267" s="25">
+        <f t="shared" si="39"/>
+        <v>10</v>
+      </c>
+      <c r="S267">
+        <f t="shared" si="40"/>
+        <v>1.3225806451612903</v>
       </c>
       <c r="T267">
         <v>46</v>
@@ -54021,6 +55514,9 @@
       </c>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A268" s="13">
+        <v>34</v>
+      </c>
       <c r="B268" s="21">
         <v>46093</v>
       </c>
@@ -54061,12 +55557,20 @@
         <v>40</v>
       </c>
       <c r="O268" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>47</v>
       </c>
       <c r="P268" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>11.93</v>
+      </c>
+      <c r="R268" s="25">
+        <f t="shared" si="39"/>
+        <v>13</v>
+      </c>
+      <c r="S268">
+        <f t="shared" si="40"/>
+        <v>1.3823529411764706</v>
       </c>
       <c r="T268">
         <v>56</v>
@@ -54076,6 +55580,9 @@
       </c>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A269" s="13">
+        <v>111</v>
+      </c>
       <c r="B269" s="21">
         <v>46094</v>
       </c>
@@ -54116,12 +55623,20 @@
         <v>71</v>
       </c>
       <c r="O269" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>64</v>
       </c>
       <c r="P269" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>16.760000000000002</v>
+      </c>
+      <c r="R269" s="25">
+        <f t="shared" si="39"/>
+        <v>-47</v>
+      </c>
+      <c r="S269">
+        <f t="shared" si="40"/>
+        <v>0.57657657657657657</v>
       </c>
       <c r="T269">
         <v>76</v>
@@ -54131,6 +55646,9 @@
       </c>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A270" s="13">
+        <v>135</v>
+      </c>
       <c r="B270" s="21">
         <v>46095</v>
       </c>
@@ -54171,12 +55689,20 @@
         <v>146</v>
       </c>
       <c r="O270" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>126</v>
       </c>
       <c r="P270" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>29.3</v>
+      </c>
+      <c r="R270" s="25">
+        <f t="shared" si="39"/>
+        <v>-9</v>
+      </c>
+      <c r="S270">
+        <f t="shared" si="40"/>
+        <v>0.93333333333333335</v>
       </c>
       <c r="T270">
         <v>132</v>
@@ -54186,6 +55712,9 @@
       </c>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A271" s="13">
+        <v>32</v>
+      </c>
       <c r="B271" s="21">
         <v>46096</v>
       </c>
@@ -54226,12 +55755,20 @@
         <v>46</v>
       </c>
       <c r="O271" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>44</v>
       </c>
       <c r="P271" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>13.91</v>
+      </c>
+      <c r="R271" s="25">
+        <f t="shared" si="39"/>
+        <v>12</v>
+      </c>
+      <c r="S271">
+        <f t="shared" si="40"/>
+        <v>1.375</v>
       </c>
       <c r="T271">
         <v>69</v>
@@ -54245,54 +55782,54 @@
         <v>46097</v>
       </c>
       <c r="C272">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D272">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E272">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F272">
+        <v>42</v>
+      </c>
+      <c r="G272">
+        <v>39</v>
+      </c>
+      <c r="H272">
+        <v>67</v>
+      </c>
+      <c r="I272">
+        <v>41</v>
+      </c>
+      <c r="J272">
         <v>36</v>
       </c>
-      <c r="G272">
-        <v>40</v>
-      </c>
-      <c r="H272">
-        <v>23</v>
-      </c>
-      <c r="I272">
-        <v>46</v>
-      </c>
-      <c r="J272">
-        <v>22</v>
-      </c>
       <c r="K272">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="L272">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M272">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N272">
+        <v>41</v>
+      </c>
+      <c r="O272" s="19">
+        <f t="shared" si="43"/>
         <v>44</v>
       </c>
-      <c r="O272" s="19">
-        <f t="shared" si="41"/>
-        <v>44</v>
-      </c>
       <c r="P272" s="19">
-        <f t="shared" si="42"/>
-        <v>11.05</v>
+        <f t="shared" si="44"/>
+        <v>7.25</v>
       </c>
       <c r="T272">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U272">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="273" spans="2:21" x14ac:dyDescent="0.25">
@@ -54300,54 +55837,54 @@
         <v>46098</v>
       </c>
       <c r="C273">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D273">
+        <v>28</v>
+      </c>
+      <c r="E273">
+        <v>43</v>
+      </c>
+      <c r="F273">
         <v>27</v>
       </c>
-      <c r="E273">
-        <v>42</v>
-      </c>
-      <c r="F273">
-        <v>16</v>
-      </c>
       <c r="G273">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H273">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I273">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J273">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K273">
         <v>44</v>
       </c>
       <c r="L273">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M273">
+        <v>41</v>
+      </c>
+      <c r="N273">
         <v>28</v>
       </c>
-      <c r="N273">
+      <c r="O273" s="19">
+        <f t="shared" si="43"/>
+        <v>36</v>
+      </c>
+      <c r="P273" s="19">
+        <f t="shared" si="44"/>
+        <v>7.75</v>
+      </c>
+      <c r="T273">
+        <v>43</v>
+      </c>
+      <c r="U273">
         <v>27</v>
-      </c>
-      <c r="O273" s="19">
-        <f t="shared" si="41"/>
-        <v>30</v>
-      </c>
-      <c r="P273" s="19">
-        <f t="shared" si="42"/>
-        <v>11.76</v>
-      </c>
-      <c r="T273">
-        <v>46</v>
-      </c>
-      <c r="U273">
-        <v>24</v>
       </c>
     </row>
     <row r="274" spans="2:21" x14ac:dyDescent="0.25">
@@ -54355,54 +55892,54 @@
         <v>46099</v>
       </c>
       <c r="C274">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D274">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E274">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F274">
+        <v>43</v>
+      </c>
+      <c r="G274">
+        <v>40</v>
+      </c>
+      <c r="H274">
+        <v>33</v>
+      </c>
+      <c r="I274">
+        <v>48</v>
+      </c>
+      <c r="J274">
+        <v>41</v>
+      </c>
+      <c r="K274">
         <v>47</v>
       </c>
-      <c r="G274">
-        <v>38</v>
-      </c>
-      <c r="H274">
-        <v>40</v>
-      </c>
-      <c r="I274">
-        <v>66</v>
-      </c>
-      <c r="J274">
-        <v>19</v>
-      </c>
-      <c r="K274">
-        <v>46</v>
-      </c>
       <c r="L274">
+        <v>45</v>
+      </c>
+      <c r="M274">
+        <v>44</v>
+      </c>
+      <c r="N274">
+        <v>41</v>
+      </c>
+      <c r="O274" s="19">
+        <f t="shared" si="43"/>
+        <v>43</v>
+      </c>
+      <c r="P274" s="19">
+        <f t="shared" si="44"/>
+        <v>3.94</v>
+      </c>
+      <c r="T274">
+        <v>41</v>
+      </c>
+      <c r="U274">
         <v>37</v>
-      </c>
-      <c r="M274">
-        <v>41</v>
-      </c>
-      <c r="N274">
-        <v>40</v>
-      </c>
-      <c r="O274" s="19">
-        <f t="shared" si="41"/>
-        <v>44</v>
-      </c>
-      <c r="P274" s="19">
-        <f t="shared" si="42"/>
-        <v>10.81</v>
-      </c>
-      <c r="T274">
-        <v>55</v>
-      </c>
-      <c r="U274">
-        <v>44</v>
       </c>
     </row>
     <row r="275" spans="2:21" x14ac:dyDescent="0.25">
@@ -54410,54 +55947,54 @@
         <v>46100</v>
       </c>
       <c r="C275">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D275">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E275">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F275">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G275">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="H275">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I275">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="J275">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="K275">
         <v>55</v>
       </c>
       <c r="L275">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M275">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="N275">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O275" s="19">
-        <f t="shared" si="41"/>
-        <v>56</v>
+        <f t="shared" si="43"/>
+        <v>53</v>
       </c>
       <c r="P275" s="19">
-        <f t="shared" si="42"/>
-        <v>15.07</v>
+        <f t="shared" si="44"/>
+        <v>7.34</v>
       </c>
       <c r="T275">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="U275">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="276" spans="2:21" x14ac:dyDescent="0.25">
@@ -54465,54 +56002,54 @@
         <v>46101</v>
       </c>
       <c r="C276">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="D276">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E276">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F276">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G276">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="H276">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="I276">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="J276">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="K276">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="L276">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="M276">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="N276">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="O276" s="19">
-        <f t="shared" si="41"/>
-        <v>71</v>
+        <f t="shared" si="43"/>
+        <v>108</v>
       </c>
       <c r="P276" s="19">
-        <f t="shared" si="42"/>
-        <v>16.739999999999998</v>
+        <f t="shared" si="44"/>
+        <v>17.25</v>
       </c>
       <c r="T276">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="U276">
-        <v>65</v>
+        <v>104</v>
       </c>
     </row>
     <row r="277" spans="2:21" x14ac:dyDescent="0.25">
@@ -54520,54 +56057,54 @@
         <v>46102</v>
       </c>
       <c r="C277">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="D277">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="E277">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="F277">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="G277">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="H277">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="I277">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="J277">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="K277">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="L277">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="M277">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N277">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O277" s="19">
-        <f t="shared" si="41"/>
-        <v>85</v>
+        <f t="shared" si="43"/>
+        <v>125</v>
       </c>
       <c r="P277" s="19">
-        <f t="shared" si="42"/>
-        <v>19.670000000000002</v>
+        <f t="shared" si="44"/>
+        <v>14.21</v>
       </c>
       <c r="T277">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="U277">
-        <v>91</v>
+        <v>136</v>
       </c>
     </row>
     <row r="278" spans="2:21" x14ac:dyDescent="0.25">
@@ -54575,54 +56112,54 @@
         <v>46103</v>
       </c>
       <c r="C278">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D278">
+        <v>39</v>
+      </c>
+      <c r="E278">
         <v>49</v>
       </c>
-      <c r="E278">
-        <v>67</v>
-      </c>
       <c r="F278">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G278">
         <v>39</v>
       </c>
       <c r="H278">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I278">
+        <v>41</v>
+      </c>
+      <c r="J278">
+        <v>27</v>
+      </c>
+      <c r="K278">
         <v>46</v>
       </c>
-      <c r="J278">
-        <v>22</v>
-      </c>
-      <c r="K278">
-        <v>52</v>
-      </c>
       <c r="L278">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="M278">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N278">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O278" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>43</v>
       </c>
       <c r="P278" s="19">
-        <f t="shared" si="42"/>
-        <v>11.65</v>
+        <f t="shared" si="44"/>
+        <v>8.48</v>
       </c>
       <c r="T278">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U278">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="279" spans="2:21" x14ac:dyDescent="0.25">
@@ -54630,54 +56167,54 @@
         <v>46104</v>
       </c>
       <c r="C279">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D279">
+        <v>45</v>
+      </c>
+      <c r="E279">
+        <v>48</v>
+      </c>
+      <c r="F279">
+        <v>38</v>
+      </c>
+      <c r="G279">
+        <v>40</v>
+      </c>
+      <c r="H279">
+        <v>21</v>
+      </c>
+      <c r="I279">
         <v>42</v>
       </c>
-      <c r="E279">
+      <c r="J279">
+        <v>31</v>
+      </c>
+      <c r="K279">
+        <v>58</v>
+      </c>
+      <c r="L279">
+        <v>50</v>
+      </c>
+      <c r="M279">
+        <v>60</v>
+      </c>
+      <c r="N279">
         <v>46</v>
       </c>
-      <c r="F279">
-        <v>25</v>
-      </c>
-      <c r="G279">
-        <v>38</v>
-      </c>
-      <c r="H279">
-        <v>9</v>
-      </c>
-      <c r="I279">
-        <v>44</v>
-      </c>
-      <c r="J279">
-        <v>19</v>
-      </c>
-      <c r="K279">
-        <v>51</v>
-      </c>
-      <c r="L279">
-        <v>37</v>
-      </c>
-      <c r="M279">
-        <v>41</v>
-      </c>
-      <c r="N279">
-        <v>38</v>
-      </c>
       <c r="O279" s="19">
-        <f t="shared" si="41"/>
-        <v>38</v>
+        <f t="shared" si="43"/>
+        <v>45</v>
       </c>
       <c r="P279" s="19">
-        <f t="shared" si="42"/>
-        <v>12.6</v>
+        <f t="shared" si="44"/>
+        <v>10.73</v>
       </c>
       <c r="T279">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U279">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="280" spans="2:21" x14ac:dyDescent="0.25">
@@ -54685,54 +56222,54 @@
         <v>46105</v>
       </c>
       <c r="C280">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D280">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E280">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F280">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G280">
+        <v>31</v>
+      </c>
+      <c r="H280">
+        <v>15</v>
+      </c>
+      <c r="I280">
+        <v>42</v>
+      </c>
+      <c r="J280">
+        <v>22</v>
+      </c>
+      <c r="K280">
+        <v>48</v>
+      </c>
+      <c r="L280">
+        <v>46</v>
+      </c>
+      <c r="M280">
+        <v>31</v>
+      </c>
+      <c r="N280">
+        <v>46</v>
+      </c>
+      <c r="O280" s="19">
+        <f t="shared" si="43"/>
         <v>39</v>
       </c>
-      <c r="H280">
-        <v>13</v>
-      </c>
-      <c r="I280">
-        <v>47</v>
-      </c>
-      <c r="J280">
-        <v>19</v>
-      </c>
-      <c r="K280">
-        <v>47</v>
-      </c>
-      <c r="L280">
-        <v>40</v>
-      </c>
-      <c r="M280">
-        <v>40</v>
-      </c>
-      <c r="N280">
-        <v>40</v>
-      </c>
-      <c r="O280" s="19">
-        <f t="shared" si="41"/>
-        <v>38</v>
-      </c>
       <c r="P280" s="19">
-        <f t="shared" si="42"/>
-        <v>10.32</v>
+        <f t="shared" si="44"/>
+        <v>11.07</v>
       </c>
       <c r="T280">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="U280">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="281" spans="2:21" x14ac:dyDescent="0.25">
@@ -54740,54 +56277,54 @@
         <v>46106</v>
       </c>
       <c r="C281">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D281">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E281">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F281">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G281">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H281">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I281">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="J281">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K281">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L281">
         <v>40</v>
       </c>
       <c r="M281">
+        <v>47</v>
+      </c>
+      <c r="N281">
         <v>41</v>
       </c>
-      <c r="N281">
+      <c r="O281" s="19">
+        <f t="shared" si="43"/>
         <v>40</v>
       </c>
-      <c r="O281" s="19">
-        <f t="shared" si="41"/>
-        <v>46</v>
-      </c>
       <c r="P281" s="19">
-        <f t="shared" si="42"/>
-        <v>13.35</v>
+        <f t="shared" si="44"/>
+        <v>11.45</v>
       </c>
       <c r="T281">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U281">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="282" spans="2:21" x14ac:dyDescent="0.25">
@@ -54795,54 +56332,54 @@
         <v>46107</v>
       </c>
       <c r="C282">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D282">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E282">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F282">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G282">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="H282">
+        <v>28</v>
+      </c>
+      <c r="I282">
+        <v>71</v>
+      </c>
+      <c r="J282">
+        <v>43</v>
+      </c>
+      <c r="K282">
+        <v>47</v>
+      </c>
+      <c r="L282">
+        <v>42</v>
+      </c>
+      <c r="M282">
         <v>50</v>
       </c>
-      <c r="I282">
-        <v>70</v>
-      </c>
-      <c r="J282">
-        <v>21</v>
-      </c>
-      <c r="K282">
-        <v>56</v>
-      </c>
-      <c r="L282">
-        <v>49</v>
-      </c>
-      <c r="M282">
+      <c r="N282">
+        <v>43</v>
+      </c>
+      <c r="O282" s="19">
+        <f t="shared" si="43"/>
+        <v>46</v>
+      </c>
+      <c r="P282" s="19">
+        <f t="shared" si="44"/>
+        <v>9.19</v>
+      </c>
+      <c r="T282">
+        <v>59</v>
+      </c>
+      <c r="U282">
         <v>45</v>
-      </c>
-      <c r="N282">
-        <v>47</v>
-      </c>
-      <c r="O282" s="19">
-        <f t="shared" si="41"/>
-        <v>55</v>
-      </c>
-      <c r="P282" s="19">
-        <f t="shared" si="42"/>
-        <v>14.44</v>
-      </c>
-      <c r="T282">
-        <v>71</v>
-      </c>
-      <c r="U282">
-        <v>55</v>
       </c>
     </row>
     <row r="283" spans="2:21" x14ac:dyDescent="0.25">
@@ -54850,54 +56387,54 @@
         <v>46108</v>
       </c>
       <c r="C283">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D283">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E283">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F283">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G283">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H283">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I283">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J283">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="K283">
+        <v>98</v>
+      </c>
+      <c r="L283">
+        <v>84</v>
+      </c>
+      <c r="M283">
+        <v>88</v>
+      </c>
+      <c r="N283">
+        <v>81</v>
+      </c>
+      <c r="O283" s="19">
+        <f t="shared" si="43"/>
+        <v>87</v>
+      </c>
+      <c r="P283" s="19">
+        <f t="shared" si="44"/>
+        <v>12.62</v>
+      </c>
+      <c r="T283">
+        <v>88</v>
+      </c>
+      <c r="U283">
         <v>79</v>
-      </c>
-      <c r="L283">
-        <v>78</v>
-      </c>
-      <c r="M283">
-        <v>74</v>
-      </c>
-      <c r="N283">
-        <v>71</v>
-      </c>
-      <c r="O283" s="19">
-        <f t="shared" si="41"/>
-        <v>74</v>
-      </c>
-      <c r="P283" s="19">
-        <f t="shared" si="42"/>
-        <v>16.98</v>
-      </c>
-      <c r="T283">
-        <v>73</v>
-      </c>
-      <c r="U283">
-        <v>75</v>
       </c>
     </row>
     <row r="284" spans="2:21" x14ac:dyDescent="0.25">
@@ -54905,54 +56442,54 @@
         <v>46109</v>
       </c>
       <c r="C284">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D284">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E284">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="F284">
+        <v>113</v>
+      </c>
+      <c r="G284">
+        <v>108</v>
+      </c>
+      <c r="H284">
+        <v>110</v>
+      </c>
+      <c r="I284">
+        <v>138</v>
+      </c>
+      <c r="J284">
+        <v>128</v>
+      </c>
+      <c r="K284">
+        <v>157</v>
+      </c>
+      <c r="L284">
+        <v>120</v>
+      </c>
+      <c r="M284">
+        <v>123</v>
+      </c>
+      <c r="N284">
         <v>118</v>
       </c>
-      <c r="G284">
-        <v>117</v>
-      </c>
-      <c r="H284">
-        <v>87</v>
-      </c>
-      <c r="I284">
-        <v>128</v>
-      </c>
-      <c r="J284">
-        <v>39</v>
-      </c>
-      <c r="K284">
-        <v>148</v>
-      </c>
-      <c r="L284">
-        <v>126</v>
-      </c>
-      <c r="M284">
-        <v>119</v>
-      </c>
-      <c r="N284">
+      <c r="O284" s="19">
+        <f t="shared" si="43"/>
         <v>122</v>
       </c>
-      <c r="O284" s="19">
-        <f t="shared" si="41"/>
-        <v>119</v>
-      </c>
       <c r="P284" s="19">
-        <f t="shared" si="42"/>
-        <v>26.16</v>
+        <f t="shared" si="44"/>
+        <v>15.99</v>
       </c>
       <c r="T284">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="U284">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="285" spans="2:21" x14ac:dyDescent="0.25">
@@ -54960,54 +56497,54 @@
         <v>46110</v>
       </c>
       <c r="C285">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D285">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E285">
         <v>49</v>
       </c>
       <c r="F285">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G285">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H285">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I285">
+        <v>42</v>
+      </c>
+      <c r="J285">
+        <v>30</v>
+      </c>
+      <c r="K285">
+        <v>55</v>
+      </c>
+      <c r="L285">
+        <v>53</v>
+      </c>
+      <c r="M285">
+        <v>55</v>
+      </c>
+      <c r="N285">
+        <v>50</v>
+      </c>
+      <c r="O285" s="19">
+        <f t="shared" si="43"/>
         <v>46</v>
       </c>
-      <c r="J285">
-        <v>21</v>
-      </c>
-      <c r="K285">
-        <v>57</v>
-      </c>
-      <c r="L285">
-        <v>46</v>
-      </c>
-      <c r="M285">
-        <v>48</v>
-      </c>
-      <c r="N285">
-        <v>46</v>
-      </c>
-      <c r="O285" s="19">
-        <f t="shared" si="41"/>
-        <v>43</v>
-      </c>
       <c r="P285" s="19">
-        <f t="shared" si="42"/>
-        <v>10.130000000000001</v>
+        <f t="shared" si="44"/>
+        <v>13.68</v>
       </c>
       <c r="T285">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="U285">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="286" spans="2:21" x14ac:dyDescent="0.25">
@@ -55015,54 +56552,54 @@
         <v>46111</v>
       </c>
       <c r="C286">
+        <v>45</v>
+      </c>
+      <c r="D286">
+        <v>40</v>
+      </c>
+      <c r="E286">
+        <v>48</v>
+      </c>
+      <c r="F286">
+        <v>38</v>
+      </c>
+      <c r="G286">
+        <v>40</v>
+      </c>
+      <c r="H286">
         <v>60</v>
       </c>
-      <c r="D286">
-        <v>49</v>
-      </c>
-      <c r="E286">
-        <v>55</v>
-      </c>
-      <c r="F286">
-        <v>36</v>
-      </c>
-      <c r="G286">
+      <c r="I286">
+        <v>41</v>
+      </c>
+      <c r="J286">
+        <v>43</v>
+      </c>
+      <c r="K286">
+        <v>47</v>
+      </c>
+      <c r="L286">
         <v>39</v>
       </c>
-      <c r="H286">
-        <v>19</v>
-      </c>
-      <c r="I286">
-        <v>48</v>
-      </c>
-      <c r="J286">
-        <v>22</v>
-      </c>
-      <c r="K286">
-        <v>70</v>
-      </c>
-      <c r="L286">
-        <v>49</v>
-      </c>
       <c r="M286">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N286">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O286" s="19">
-        <f t="shared" si="41"/>
-        <v>45</v>
+        <f t="shared" si="43"/>
+        <v>43</v>
       </c>
       <c r="P286" s="19">
-        <f t="shared" si="42"/>
-        <v>12.98</v>
+        <f t="shared" si="44"/>
+        <v>6.06</v>
       </c>
       <c r="T286">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="U286">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="287" spans="2:21" x14ac:dyDescent="0.25">
@@ -55070,54 +56607,54 @@
         <v>46112</v>
       </c>
       <c r="C287">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D287">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E287">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F287">
+        <v>38</v>
+      </c>
+      <c r="G287">
+        <v>39</v>
+      </c>
+      <c r="H287">
+        <v>20</v>
+      </c>
+      <c r="I287">
+        <v>49</v>
+      </c>
+      <c r="J287">
+        <v>30</v>
+      </c>
+      <c r="K287">
+        <v>51</v>
+      </c>
+      <c r="L287">
+        <v>46</v>
+      </c>
+      <c r="M287">
+        <v>66</v>
+      </c>
+      <c r="N287">
+        <v>42</v>
+      </c>
+      <c r="O287" s="19">
+        <f t="shared" si="43"/>
+        <v>44</v>
+      </c>
+      <c r="P287" s="19">
+        <f t="shared" si="44"/>
+        <v>11.32</v>
+      </c>
+      <c r="T287">
+        <v>49</v>
+      </c>
+      <c r="U287">
         <v>34</v>
-      </c>
-      <c r="G287">
-        <v>38</v>
-      </c>
-      <c r="H287">
-        <v>19</v>
-      </c>
-      <c r="I287">
-        <v>57</v>
-      </c>
-      <c r="J287">
-        <v>21</v>
-      </c>
-      <c r="K287">
-        <v>70</v>
-      </c>
-      <c r="L287">
-        <v>48</v>
-      </c>
-      <c r="M287">
-        <v>45</v>
-      </c>
-      <c r="N287">
-        <v>44</v>
-      </c>
-      <c r="O287" s="19">
-        <f t="shared" si="41"/>
-        <v>47</v>
-      </c>
-      <c r="P287" s="19">
-        <f t="shared" si="42"/>
-        <v>15.4</v>
-      </c>
-      <c r="T287">
-        <v>57</v>
-      </c>
-      <c r="U287">
-        <v>40</v>
       </c>
     </row>
     <row r="288" spans="2:21" x14ac:dyDescent="0.25">
@@ -55125,225 +56662,1061 @@
         <v>46113</v>
       </c>
       <c r="C288">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D288">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E288">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F288">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G288">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H288">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="I288">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J288">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K288">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L288">
         <v>43</v>
       </c>
       <c r="M288">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="N288">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="O288" s="19">
-        <f t="shared" si="41"/>
-        <v>42</v>
+        <f t="shared" si="43"/>
+        <v>50</v>
       </c>
       <c r="P288" s="19">
-        <f t="shared" si="42"/>
-        <v>12.59</v>
+        <f t="shared" si="44"/>
+        <v>7.58</v>
       </c>
       <c r="T288">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="U288">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="289" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="289" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B289" s="21">
         <v>46114</v>
       </c>
       <c r="C289">
+        <v>108</v>
+      </c>
+      <c r="D289">
+        <v>66</v>
+      </c>
+      <c r="E289">
         <v>78</v>
       </c>
-      <c r="D289">
-        <v>79</v>
-      </c>
-      <c r="E289">
-        <v>80</v>
-      </c>
       <c r="F289">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G289">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H289">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I289">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="J289">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="K289">
+        <v>112</v>
+      </c>
+      <c r="L289">
         <v>78</v>
       </c>
-      <c r="L289">
-        <v>69</v>
-      </c>
       <c r="M289">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="N289">
         <v>69</v>
       </c>
       <c r="O289" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
+        <v>75</v>
+      </c>
+      <c r="P289" s="19">
+        <f t="shared" si="44"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="T289">
+        <v>85</v>
+      </c>
+      <c r="U289">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="290" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B290" s="21">
+        <v>46115</v>
+      </c>
+      <c r="C290">
+        <v>92</v>
+      </c>
+      <c r="D290">
+        <v>65</v>
+      </c>
+      <c r="E290">
+        <v>85</v>
+      </c>
+      <c r="F290">
+        <v>60</v>
+      </c>
+      <c r="G290">
+        <v>59</v>
+      </c>
+      <c r="H290">
+        <v>48</v>
+      </c>
+      <c r="I290">
+        <v>60</v>
+      </c>
+      <c r="J290">
+        <v>48</v>
+      </c>
+      <c r="K290">
+        <v>96</v>
+      </c>
+      <c r="L290">
+        <v>92</v>
+      </c>
+      <c r="M290">
+        <v>91</v>
+      </c>
+      <c r="N290">
+        <v>66</v>
+      </c>
+      <c r="O290" s="19">
+        <f t="shared" ref="O290:O304" si="45">ROUND(AVERAGE(C290:N290,T290,U290),0)</f>
         <v>70</v>
       </c>
-      <c r="P289" s="19">
-        <f t="shared" si="42"/>
-        <v>19.149999999999999</v>
-      </c>
-      <c r="T289">
-        <v>86</v>
-      </c>
-      <c r="U289">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="290" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B290" s="32"/>
-      <c r="C290" s="59" t="s">
+      <c r="P290" s="19">
+        <f t="shared" ref="P290:P304" si="46">ROUND(_xlfn.STDEV.P(C290:N290,T290,U290),2)</f>
+        <v>16.829999999999998</v>
+      </c>
+      <c r="T290">
+        <v>69</v>
+      </c>
+      <c r="U290">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B291" s="21">
+        <v>46116</v>
+      </c>
+      <c r="C291">
+        <v>109</v>
+      </c>
+      <c r="D291">
+        <v>107</v>
+      </c>
+      <c r="E291">
+        <v>84</v>
+      </c>
+      <c r="F291">
+        <v>93</v>
+      </c>
+      <c r="G291">
+        <v>88</v>
+      </c>
+      <c r="H291">
+        <v>92</v>
+      </c>
+      <c r="I291">
+        <v>101</v>
+      </c>
+      <c r="J291">
+        <v>97</v>
+      </c>
+      <c r="K291">
+        <v>116</v>
+      </c>
+      <c r="L291">
+        <v>115</v>
+      </c>
+      <c r="M291">
+        <v>92</v>
+      </c>
+      <c r="N291">
+        <v>110</v>
+      </c>
+      <c r="O291" s="19">
+        <f t="shared" si="45"/>
+        <v>99</v>
+      </c>
+      <c r="P291" s="19">
+        <f t="shared" si="46"/>
+        <v>11.21</v>
+      </c>
+      <c r="T291">
+        <v>78</v>
+      </c>
+      <c r="U291">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="292" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B292" s="21">
+        <v>46117</v>
+      </c>
+      <c r="C292">
+        <v>44</v>
+      </c>
+      <c r="D292">
+        <v>30</v>
+      </c>
+      <c r="E292">
+        <v>43</v>
+      </c>
+      <c r="F292">
+        <v>17</v>
+      </c>
+      <c r="G292">
+        <v>37</v>
+      </c>
+      <c r="H292">
+        <v>9</v>
+      </c>
+      <c r="I292">
+        <v>40</v>
+      </c>
+      <c r="J292">
+        <v>18</v>
+      </c>
+      <c r="K292">
+        <v>45</v>
+      </c>
+      <c r="L292">
+        <v>31</v>
+      </c>
+      <c r="M292">
+        <v>37</v>
+      </c>
+      <c r="N292">
+        <v>32</v>
+      </c>
+      <c r="O292" s="19">
+        <f t="shared" si="45"/>
+        <v>32</v>
+      </c>
+      <c r="P292" s="19">
+        <f t="shared" si="46"/>
+        <v>10.58</v>
+      </c>
+      <c r="T292">
+        <v>34</v>
+      </c>
+      <c r="U292">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="293" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B293" s="21">
+        <v>46118</v>
+      </c>
+      <c r="C293">
+        <v>46</v>
+      </c>
+      <c r="D293">
+        <v>44</v>
+      </c>
+      <c r="E293">
+        <v>50</v>
+      </c>
+      <c r="F293">
+        <v>38</v>
+      </c>
+      <c r="G293">
+        <v>41</v>
+      </c>
+      <c r="H293">
+        <v>30</v>
+      </c>
+      <c r="I293">
+        <v>41</v>
+      </c>
+      <c r="J293">
+        <v>33</v>
+      </c>
+      <c r="K293">
+        <v>47</v>
+      </c>
+      <c r="L293">
+        <v>45</v>
+      </c>
+      <c r="M293">
+        <v>44</v>
+      </c>
+      <c r="N293">
+        <v>44</v>
+      </c>
+      <c r="O293" s="19">
+        <f t="shared" si="45"/>
+        <v>41</v>
+      </c>
+      <c r="P293" s="19">
+        <f t="shared" si="46"/>
+        <v>5.52</v>
+      </c>
+      <c r="T293">
+        <v>41</v>
+      </c>
+      <c r="U293">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="294" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B294" s="21">
+        <v>46119</v>
+      </c>
+      <c r="C294">
+        <v>49</v>
+      </c>
+      <c r="D294">
+        <v>45</v>
+      </c>
+      <c r="E294">
+        <v>60</v>
+      </c>
+      <c r="F294">
+        <v>34</v>
+      </c>
+      <c r="G294">
+        <v>42</v>
+      </c>
+      <c r="H294">
+        <v>21</v>
+      </c>
+      <c r="I294">
+        <v>43</v>
+      </c>
+      <c r="J294">
+        <v>27</v>
+      </c>
+      <c r="K294">
+        <v>47</v>
+      </c>
+      <c r="L294">
+        <v>48</v>
+      </c>
+      <c r="M294">
+        <v>64</v>
+      </c>
+      <c r="N294">
+        <v>46</v>
+      </c>
+      <c r="O294" s="19">
+        <f t="shared" si="45"/>
+        <v>44</v>
+      </c>
+      <c r="P294" s="19">
+        <f t="shared" si="46"/>
+        <v>11.24</v>
+      </c>
+      <c r="T294">
+        <v>50</v>
+      </c>
+      <c r="U294">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="295" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B295" s="21">
+        <v>46120</v>
+      </c>
+      <c r="C295">
+        <v>50</v>
+      </c>
+      <c r="D295">
+        <v>42</v>
+      </c>
+      <c r="E295">
+        <v>61</v>
+      </c>
+      <c r="F295">
+        <v>44</v>
+      </c>
+      <c r="G295">
+        <v>41</v>
+      </c>
+      <c r="H295">
+        <v>72</v>
+      </c>
+      <c r="I295">
+        <v>65</v>
+      </c>
+      <c r="J295">
+        <v>32</v>
+      </c>
+      <c r="K295">
+        <v>96</v>
+      </c>
+      <c r="L295">
+        <v>48</v>
+      </c>
+      <c r="M295">
+        <v>89</v>
+      </c>
+      <c r="N295">
+        <v>45</v>
+      </c>
+      <c r="O295" s="19">
+        <f t="shared" si="45"/>
+        <v>58</v>
+      </c>
+      <c r="P295" s="19">
+        <f t="shared" si="46"/>
+        <v>17.989999999999998</v>
+      </c>
+      <c r="T295">
+        <v>68</v>
+      </c>
+      <c r="U295">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="296" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B296" s="21">
+        <v>46121</v>
+      </c>
+      <c r="C296">
+        <v>74</v>
+      </c>
+      <c r="D296">
+        <v>48</v>
+      </c>
+      <c r="E296">
+        <v>51</v>
+      </c>
+      <c r="F296">
+        <v>46</v>
+      </c>
+      <c r="G296">
+        <v>51</v>
+      </c>
+      <c r="H296">
+        <v>48</v>
+      </c>
+      <c r="I296">
+        <v>63</v>
+      </c>
+      <c r="J296">
+        <v>56</v>
+      </c>
+      <c r="K296">
+        <v>66</v>
+      </c>
+      <c r="L296">
+        <v>52</v>
+      </c>
+      <c r="M296">
+        <v>59</v>
+      </c>
+      <c r="N296">
+        <v>51</v>
+      </c>
+      <c r="O296" s="19">
+        <f t="shared" si="45"/>
+        <v>56</v>
+      </c>
+      <c r="P296" s="19">
+        <f t="shared" si="46"/>
+        <v>7.58</v>
+      </c>
+      <c r="T296">
+        <v>58</v>
+      </c>
+      <c r="U296">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="297" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B297" s="21">
+        <v>46122</v>
+      </c>
+      <c r="C297">
+        <v>64</v>
+      </c>
+      <c r="D297">
+        <v>81</v>
+      </c>
+      <c r="E297">
+        <v>69</v>
+      </c>
+      <c r="F297">
+        <v>71</v>
+      </c>
+      <c r="G297">
+        <v>66</v>
+      </c>
+      <c r="H297">
+        <v>59</v>
+      </c>
+      <c r="I297">
+        <v>72</v>
+      </c>
+      <c r="J297">
+        <v>64</v>
+      </c>
+      <c r="K297">
+        <v>71</v>
+      </c>
+      <c r="L297">
+        <v>87</v>
+      </c>
+      <c r="M297">
+        <v>79</v>
+      </c>
+      <c r="N297">
+        <v>83</v>
+      </c>
+      <c r="O297" s="19">
+        <f t="shared" si="45"/>
+        <v>73</v>
+      </c>
+      <c r="P297" s="19">
+        <f t="shared" si="46"/>
+        <v>8.07</v>
+      </c>
+      <c r="T297">
+        <v>71</v>
+      </c>
+      <c r="U297">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="298" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B298" s="21">
+        <v>46123</v>
+      </c>
+      <c r="C298">
+        <v>159</v>
+      </c>
+      <c r="D298">
+        <v>134</v>
+      </c>
+      <c r="E298">
+        <v>136</v>
+      </c>
+      <c r="F298">
+        <v>134</v>
+      </c>
+      <c r="G298">
+        <v>106</v>
+      </c>
+      <c r="H298">
+        <v>92</v>
+      </c>
+      <c r="I298">
+        <v>101</v>
+      </c>
+      <c r="J298">
+        <v>120</v>
+      </c>
+      <c r="K298">
+        <v>157</v>
+      </c>
+      <c r="L298">
+        <v>152</v>
+      </c>
+      <c r="M298">
+        <v>167</v>
+      </c>
+      <c r="N298">
+        <v>135</v>
+      </c>
+      <c r="O298" s="19">
+        <f t="shared" si="45"/>
+        <v>131</v>
+      </c>
+      <c r="P298" s="19">
+        <f t="shared" si="46"/>
+        <v>21.66</v>
+      </c>
+      <c r="T298">
+        <v>122</v>
+      </c>
+      <c r="U298">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="299" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B299" s="21">
+        <v>46124</v>
+      </c>
+      <c r="C299">
+        <v>46</v>
+      </c>
+      <c r="D299">
+        <v>44</v>
+      </c>
+      <c r="E299">
+        <v>47</v>
+      </c>
+      <c r="F299">
+        <v>41</v>
+      </c>
+      <c r="G299">
+        <v>41</v>
+      </c>
+      <c r="H299">
+        <v>28</v>
+      </c>
+      <c r="I299">
+        <v>41</v>
+      </c>
+      <c r="J299">
+        <v>41</v>
+      </c>
+      <c r="K299">
+        <v>47</v>
+      </c>
+      <c r="L299">
+        <v>48</v>
+      </c>
+      <c r="M299">
+        <v>56</v>
+      </c>
+      <c r="N299">
+        <v>44</v>
+      </c>
+      <c r="O299" s="19">
+        <f t="shared" si="45"/>
+        <v>43</v>
+      </c>
+      <c r="P299" s="19">
+        <f t="shared" si="46"/>
+        <v>6.06</v>
+      </c>
+      <c r="T299">
+        <v>43</v>
+      </c>
+      <c r="U299">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="300" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B300" s="21">
+        <v>46125</v>
+      </c>
+      <c r="C300">
+        <v>71</v>
+      </c>
+      <c r="D300">
+        <v>51</v>
+      </c>
+      <c r="E300">
+        <v>50</v>
+      </c>
+      <c r="F300">
+        <v>33</v>
+      </c>
+      <c r="G300">
+        <v>43</v>
+      </c>
+      <c r="H300">
+        <v>7</v>
+      </c>
+      <c r="I300">
+        <v>47</v>
+      </c>
+      <c r="J300">
+        <v>22</v>
+      </c>
+      <c r="K300">
+        <v>72</v>
+      </c>
+      <c r="L300">
+        <v>50</v>
+      </c>
+      <c r="M300">
+        <v>61</v>
+      </c>
+      <c r="N300">
         <v>53</v>
       </c>
-      <c r="D290" s="60"/>
-      <c r="E290" s="60" t="s">
+      <c r="O300" s="19">
+        <f t="shared" si="45"/>
+        <v>48</v>
+      </c>
+      <c r="P300" s="19">
+        <f t="shared" si="46"/>
+        <v>18.68</v>
+      </c>
+      <c r="T300">
+        <v>77</v>
+      </c>
+      <c r="U300">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="301" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B301" s="21">
+        <v>46126</v>
+      </c>
+      <c r="C301">
+        <v>79</v>
+      </c>
+      <c r="D301">
+        <v>45</v>
+      </c>
+      <c r="E301">
+        <v>61</v>
+      </c>
+      <c r="F301">
+        <v>36</v>
+      </c>
+      <c r="G301">
+        <v>41</v>
+      </c>
+      <c r="H301">
+        <v>15</v>
+      </c>
+      <c r="I301">
+        <v>53</v>
+      </c>
+      <c r="J301">
+        <v>30</v>
+      </c>
+      <c r="K301">
+        <v>63</v>
+      </c>
+      <c r="L301">
+        <v>49</v>
+      </c>
+      <c r="M301">
+        <v>74</v>
+      </c>
+      <c r="N301">
+        <v>44</v>
+      </c>
+      <c r="O301" s="19">
+        <f t="shared" si="45"/>
+        <v>48</v>
+      </c>
+      <c r="P301" s="19">
+        <f t="shared" si="46"/>
+        <v>16.86</v>
+      </c>
+      <c r="T301">
+        <v>50</v>
+      </c>
+      <c r="U301">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="302" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B302" s="21">
+        <v>46127</v>
+      </c>
+      <c r="C302">
+        <v>61</v>
+      </c>
+      <c r="D302">
+        <v>49</v>
+      </c>
+      <c r="E302">
+        <v>58</v>
+      </c>
+      <c r="F302">
+        <v>36</v>
+      </c>
+      <c r="G302">
+        <v>45</v>
+      </c>
+      <c r="H302">
+        <v>15</v>
+      </c>
+      <c r="I302">
+        <v>49</v>
+      </c>
+      <c r="J302">
+        <v>30</v>
+      </c>
+      <c r="K302">
+        <v>54</v>
+      </c>
+      <c r="L302">
+        <v>53</v>
+      </c>
+      <c r="M302">
+        <v>60</v>
+      </c>
+      <c r="N302">
+        <v>48</v>
+      </c>
+      <c r="O302" s="19">
+        <f t="shared" si="45"/>
+        <v>46</v>
+      </c>
+      <c r="P302" s="19">
+        <f t="shared" si="46"/>
+        <v>12.35</v>
+      </c>
+      <c r="T302">
+        <v>52</v>
+      </c>
+      <c r="U302">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="303" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B303" s="21">
+        <v>46128</v>
+      </c>
+      <c r="C303">
         <v>57</v>
       </c>
-      <c r="F290" s="60"/>
-      <c r="G290" s="60" t="s">
+      <c r="D303">
+        <v>48</v>
+      </c>
+      <c r="E303">
+        <v>49</v>
+      </c>
+      <c r="F303">
+        <v>46</v>
+      </c>
+      <c r="G303">
+        <v>49</v>
+      </c>
+      <c r="H303">
+        <v>39</v>
+      </c>
+      <c r="I303">
+        <v>57</v>
+      </c>
+      <c r="J303">
+        <v>50</v>
+      </c>
+      <c r="K303">
+        <v>57</v>
+      </c>
+      <c r="L303">
+        <v>51</v>
+      </c>
+      <c r="M303">
+        <v>56</v>
+      </c>
+      <c r="N303">
+        <v>49</v>
+      </c>
+      <c r="O303" s="19">
+        <f t="shared" si="45"/>
+        <v>51</v>
+      </c>
+      <c r="P303" s="19">
+        <f t="shared" si="46"/>
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="T303">
+        <v>52</v>
+      </c>
+      <c r="U303">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="304" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B304" s="21">
+        <v>46129</v>
+      </c>
+      <c r="C304">
+        <v>126</v>
+      </c>
+      <c r="D304">
+        <v>110</v>
+      </c>
+      <c r="E304">
+        <v>104</v>
+      </c>
+      <c r="F304">
+        <v>101</v>
+      </c>
+      <c r="G304">
+        <v>95</v>
+      </c>
+      <c r="H304">
+        <v>70</v>
+      </c>
+      <c r="I304">
+        <v>132</v>
+      </c>
+      <c r="J304">
+        <v>94</v>
+      </c>
+      <c r="K304">
+        <v>119</v>
+      </c>
+      <c r="L304">
+        <v>125</v>
+      </c>
+      <c r="M304">
+        <v>123</v>
+      </c>
+      <c r="N304">
+        <v>109</v>
+      </c>
+      <c r="O304" s="19">
+        <f t="shared" si="45"/>
+        <v>109</v>
+      </c>
+      <c r="P304" s="19">
+        <f t="shared" si="46"/>
+        <v>15.99</v>
+      </c>
+      <c r="T304">
+        <v>121</v>
+      </c>
+      <c r="U304">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="305" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B305" s="32"/>
+      <c r="C305" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="D305" s="62"/>
+      <c r="E305" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="F305" s="62"/>
+      <c r="G305" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="H290" s="60"/>
-      <c r="I290" s="60" t="s">
+      <c r="H305" s="62"/>
+      <c r="I305" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="J290" s="60"/>
-      <c r="K290" s="60" t="s">
+      <c r="J305" s="62"/>
+      <c r="K305" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="L290" s="60"/>
-      <c r="M290" s="60" t="s">
+      <c r="L305" s="62"/>
+      <c r="M305" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="N290" s="61"/>
-      <c r="O290" s="47"/>
-      <c r="P290" s="48"/>
-      <c r="T290" s="62" t="s">
+      <c r="N305" s="63"/>
+      <c r="O305" s="47"/>
+      <c r="P305" s="48"/>
+      <c r="T305" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="U290" s="63"/>
-    </row>
-    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C291">
-        <v>31.34</v>
-      </c>
-      <c r="D291">
-        <v>27.36</v>
-      </c>
-      <c r="E291">
-        <v>24.16</v>
-      </c>
-      <c r="F291" s="14">
-        <v>25.42</v>
-      </c>
-      <c r="G291" s="14">
-        <v>22.55</v>
-      </c>
-      <c r="H291" s="14">
-        <v>24.03</v>
-      </c>
-      <c r="I291" s="14">
-        <v>25.17</v>
-      </c>
-      <c r="J291" s="14">
-        <v>24.65</v>
-      </c>
-      <c r="K291" s="14">
-        <v>21.01</v>
-      </c>
-      <c r="L291" s="14">
-        <v>28.94</v>
-      </c>
-      <c r="M291" s="14">
-        <v>26.77</v>
-      </c>
-      <c r="N291" s="15">
-        <v>28.7</v>
+      <c r="U305" s="60"/>
+    </row>
+    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C306">
+        <v>29.34</v>
+      </c>
+      <c r="D306">
+        <v>30.21</v>
+      </c>
+      <c r="E306">
+        <v>24.61</v>
+      </c>
+      <c r="F306" s="14">
+        <v>27.28</v>
+      </c>
+      <c r="G306" s="14">
+        <v>22.28</v>
+      </c>
+      <c r="H306" s="14">
+        <v>23.15</v>
+      </c>
+      <c r="I306" s="14">
+        <v>28.87</v>
+      </c>
+      <c r="J306" s="14">
+        <v>28.82</v>
+      </c>
+      <c r="K306" s="14">
+        <v>26.2</v>
+      </c>
+      <c r="L306" s="14">
+        <v>28.06</v>
+      </c>
+      <c r="M306" s="14">
+        <v>28.45</v>
+      </c>
+      <c r="N306" s="15">
+        <v>30.56</v>
+      </c>
+      <c r="T306">
+        <v>27.27</v>
+      </c>
+      <c r="U306">
+        <v>27.18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="T290:U290"/>
+    <mergeCell ref="T305:U305"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="I290:J290"/>
-    <mergeCell ref="E290:F290"/>
-    <mergeCell ref="G290:H290"/>
-    <mergeCell ref="K290:L290"/>
-    <mergeCell ref="M290:N290"/>
+    <mergeCell ref="C305:D305"/>
+    <mergeCell ref="I305:J305"/>
+    <mergeCell ref="E305:F305"/>
+    <mergeCell ref="G305:H305"/>
+    <mergeCell ref="K305:L305"/>
+    <mergeCell ref="M305:N305"/>
   </mergeCells>
-  <conditionalFormatting sqref="C98:N258 T142:U258">
-    <cfRule type="expression" dxfId="7" priority="4">
+  <conditionalFormatting sqref="C98:N271 T142:U271">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>ABS(C98-$A98)&lt;=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>ABS(C98-$A98)&lt;=15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C291:N291">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
-      <formula>$O$290-$P$290</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
-      <formula>$O$290+$P$290</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
-      <formula>$O$290-$P$290</formula>
-      <formula>"$O$264+$P$264"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R258">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="R3:R271">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FF92D050"/>
         <color rgb="FFFF0000"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T306:U306">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C306:N306 T306 U306">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="lessThan">
+      <formula>$O$305-$P$305</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>$O$305+$P$305</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="between">
+      <formula>$O$305-$P$305</formula>
+      <formula>"$O$264+$P$264"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -81386,10 +83759,10 @@
     <mergeCell ref="C1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:Y498">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>ABS(C24-$A24) &lt;= 10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>ABS(C24-$A24) &lt;= 15</formula>
     </cfRule>
   </conditionalFormatting>

--- a/restaurant_analytics/data/data.xlsx
+++ b/restaurant_analytics/data/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cardi\Documents\git-repo\swe_dev\restaurant_analytics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6009E2D6-01D7-461F-AA44-0A1C05AEF656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B290971D-E828-478C-8969-9879FFF762BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,17 +728,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -748,11 +742,40 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -787,16 +810,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBA3A3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
@@ -806,94 +819,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBA3A3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -937,21 +863,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1283,7 +1195,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R758"/>
+  <dimension ref="A1:R763"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
@@ -17779,7 +17691,7 @@
         <v>0.66900000000000004</v>
       </c>
       <c r="G619" s="8">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="H619" s="8">
         <v>9.8000000000000007</v>
@@ -20256,7 +20168,7 @@
         <v>43</v>
       </c>
       <c r="E711" s="8">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="F711" s="8">
         <v>0</v>
@@ -20265,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="H711" s="8">
-        <v>12.5</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="712" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20282,7 +20194,7 @@
         <v>39</v>
       </c>
       <c r="E712" s="8">
-        <v>33.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="F712" s="8">
         <v>0</v>
@@ -20291,7 +20203,7 @@
         <v>0</v>
       </c>
       <c r="H712" s="8">
-        <v>7.3</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="713" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20308,16 +20220,16 @@
         <v>46</v>
       </c>
       <c r="E713" s="8">
-        <v>36.5</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="F713" s="8">
-        <v>3.1E-2</v>
+        <v>0</v>
       </c>
       <c r="G713" s="8">
         <v>0</v>
       </c>
       <c r="H713" s="8">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="714" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20334,16 +20246,16 @@
         <v>21</v>
       </c>
       <c r="E714" s="8">
-        <v>37.9</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="F714" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G714" s="8">
         <v>0</v>
       </c>
       <c r="H714" s="8">
-        <v>8.3000000000000007</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="715" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20360,16 +20272,16 @@
         <v>40</v>
       </c>
       <c r="E715" s="8">
-        <v>43.3</v>
+        <v>44</v>
       </c>
       <c r="F715" s="8">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G715" s="8">
         <v>0</v>
       </c>
       <c r="H715" s="8">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="716" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20386,16 +20298,16 @@
         <v>120</v>
       </c>
       <c r="E716" s="8">
-        <v>54.5</v>
+        <v>54.15</v>
       </c>
       <c r="F716" s="8">
-        <v>0.65</v>
+        <v>0.23</v>
       </c>
       <c r="G716" s="8">
         <v>0</v>
       </c>
       <c r="H716" s="8">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I716" s="39" t="s">
         <v>10</v>
@@ -20415,16 +20327,16 @@
         <v>157</v>
       </c>
       <c r="E717" s="8">
-        <v>52.3</v>
+        <v>53.3</v>
       </c>
       <c r="F717" s="8">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G717" s="8">
         <v>0</v>
       </c>
       <c r="H717" s="8">
-        <v>14.5</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="718" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20441,7 +20353,7 @@
         <v>54</v>
       </c>
       <c r="E718" s="8">
-        <v>48.6</v>
+        <v>42.8</v>
       </c>
       <c r="F718" s="8">
         <v>0</v>
@@ -20450,7 +20362,7 @@
         <v>0</v>
       </c>
       <c r="H718" s="8">
-        <v>16.5</v>
+        <v>12.25</v>
       </c>
       <c r="I718" t="s">
         <v>61</v>
@@ -20470,7 +20382,7 @@
         <v>28</v>
       </c>
       <c r="E719" s="8">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="F719" s="8">
         <v>0</v>
@@ -20479,7 +20391,7 @@
         <v>0</v>
       </c>
       <c r="H719" s="8">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="720" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20496,19 +20408,19 @@
         <v>33</v>
       </c>
       <c r="E720" s="8">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F720" s="8">
-        <v>1.1599999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G720" s="8">
         <v>0</v>
       </c>
       <c r="H720" s="8">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="721" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="721" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="5">
         <v>4</v>
       </c>
@@ -20522,19 +20434,19 @@
         <v>31</v>
       </c>
       <c r="E721" s="8">
-        <v>40.5</v>
+        <v>37.85</v>
       </c>
       <c r="F721" s="8">
-        <v>0.36</v>
+        <v>0.9</v>
       </c>
       <c r="G721" s="8">
         <v>0</v>
       </c>
       <c r="H721" s="8">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="722" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="722" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="5">
         <v>5</v>
       </c>
@@ -20548,19 +20460,19 @@
         <v>34</v>
       </c>
       <c r="E722" s="8">
-        <v>39.9</v>
+        <v>38</v>
       </c>
       <c r="F722" s="8">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G722" s="8">
         <v>0</v>
       </c>
       <c r="H722" s="8">
-        <v>10.9</v>
-      </c>
-    </row>
-    <row r="723" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="723" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="5">
         <v>6</v>
       </c>
@@ -20574,22 +20486,22 @@
         <v>111</v>
       </c>
       <c r="E723" s="8">
-        <v>44.1</v>
+        <v>42.25</v>
       </c>
       <c r="F723" s="8">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G723" s="8">
         <v>0</v>
       </c>
       <c r="H723" s="8">
-        <v>17</v>
+        <v>20.3</v>
       </c>
       <c r="I723" s="39" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="5">
         <v>7</v>
       </c>
@@ -20603,7 +20515,7 @@
         <v>135</v>
       </c>
       <c r="E724" s="8">
-        <v>38.299999999999997</v>
+        <v>33.85</v>
       </c>
       <c r="F724" s="8">
         <v>0</v>
@@ -20612,10 +20524,10 @@
         <v>0</v>
       </c>
       <c r="H724" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="725" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="725" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="5">
         <v>1</v>
       </c>
@@ -20629,19 +20541,19 @@
         <v>32</v>
       </c>
       <c r="E725" s="8">
-        <v>38.1</v>
+        <v>43.9</v>
       </c>
       <c r="F725" s="8">
-        <v>1.42</v>
+        <v>0.47</v>
       </c>
       <c r="G725" s="8">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H725" s="8">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="726" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="726" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="5">
         <v>2</v>
       </c>
@@ -20652,25 +20564,22 @@
         <v>46097</v>
       </c>
       <c r="D726" s="13">
-        <v>43.5</v>
+        <v>12</v>
       </c>
       <c r="E726" s="8">
-        <v>30.4</v>
+        <v>26.1</v>
       </c>
       <c r="F726" s="8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G726" s="8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H726" s="8">
-        <v>13.3</v>
-      </c>
-      <c r="J726" s="8">
-        <v>5.4749999999999996</v>
-      </c>
-    </row>
-    <row r="727" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="727" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="5">
         <v>3</v>
       </c>
@@ -20681,28 +20590,25 @@
         <v>46098</v>
       </c>
       <c r="D727" s="13">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="E727" s="8">
-        <v>29.5</v>
+        <v>20.6</v>
       </c>
       <c r="F727" s="8">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G727" s="8">
         <v>0</v>
       </c>
       <c r="H727" s="8">
-        <v>10.4</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="I727" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J727" s="8">
-        <v>8.42</v>
-      </c>
-    </row>
-    <row r="728" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="728" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="5">
         <v>4</v>
       </c>
@@ -20713,25 +20619,22 @@
         <v>46099</v>
       </c>
       <c r="D728" s="13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E728" s="8">
-        <v>34.200000000000003</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="F728" s="8">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G728" s="8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H728" s="8">
-        <v>10.3</v>
-      </c>
-      <c r="J728" s="8">
-        <v>4.1550000000000002</v>
-      </c>
-    </row>
-    <row r="729" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="729" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="5">
         <v>5</v>
       </c>
@@ -20742,25 +20645,22 @@
         <v>46100</v>
       </c>
       <c r="D729" s="13">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E729" s="8">
-        <v>38.5</v>
+        <v>45.3</v>
       </c>
       <c r="F729" s="8">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G729" s="8">
         <v>0</v>
       </c>
       <c r="H729" s="8">
-        <v>10.7</v>
-      </c>
-      <c r="J729" s="8">
-        <v>6.7650000000000006</v>
-      </c>
-    </row>
-    <row r="730" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="730" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="5">
         <v>6</v>
       </c>
@@ -20771,10 +20671,10 @@
         <v>46101</v>
       </c>
       <c r="D730" s="13">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="E730" s="8">
-        <v>49</v>
+        <v>53.65</v>
       </c>
       <c r="F730" s="8">
         <v>0</v>
@@ -20783,13 +20683,10 @@
         <v>0</v>
       </c>
       <c r="H730" s="8">
-        <v>9</v>
-      </c>
-      <c r="J730" s="8">
-        <v>14.574999999999999</v>
-      </c>
-    </row>
-    <row r="731" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="731" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="5">
         <v>7</v>
       </c>
@@ -20800,10 +20697,10 @@
         <v>46102</v>
       </c>
       <c r="D731" s="13">
-        <v>128.5</v>
+        <v>156</v>
       </c>
       <c r="E731" s="8">
-        <v>58</v>
+        <v>59.1</v>
       </c>
       <c r="F731" s="8">
         <v>0</v>
@@ -20812,13 +20709,10 @@
         <v>0</v>
       </c>
       <c r="H731" s="8">
-        <v>8</v>
-      </c>
-      <c r="J731" s="8">
-        <v>13.215</v>
-      </c>
-    </row>
-    <row r="732" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="732" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="5">
         <v>1</v>
       </c>
@@ -20829,25 +20723,22 @@
         <v>46103</v>
       </c>
       <c r="D732" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E732" s="8">
-        <v>43.5</v>
+        <v>44.8</v>
       </c>
       <c r="F732" s="8">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G732" s="8">
         <v>0</v>
       </c>
       <c r="H732" s="8">
-        <v>17</v>
-      </c>
-      <c r="J732" s="8">
-        <v>6.7200000000000006</v>
-      </c>
-    </row>
-    <row r="733" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16.649999999999999</v>
+      </c>
+    </row>
+    <row r="733" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="5">
         <v>2</v>
       </c>
@@ -20858,25 +20749,22 @@
         <v>46104</v>
       </c>
       <c r="D733" s="13">
-        <v>47.5</v>
+        <v>18</v>
       </c>
       <c r="E733" s="8">
-        <v>34</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="F733" s="8">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G733" s="8">
         <v>0</v>
       </c>
       <c r="H733" s="8">
-        <v>8</v>
-      </c>
-      <c r="J733" s="8">
-        <v>8.48</v>
-      </c>
-    </row>
-    <row r="734" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9.5500000000000007</v>
+      </c>
+    </row>
+    <row r="734" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="5">
         <v>3</v>
       </c>
@@ -20887,10 +20775,10 @@
         <v>46105</v>
       </c>
       <c r="D734" s="13">
-        <v>42.5</v>
+        <v>37</v>
       </c>
       <c r="E734" s="8">
-        <v>39.5</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="F734" s="8">
         <v>0</v>
@@ -20899,13 +20787,10 @@
         <v>0</v>
       </c>
       <c r="H734" s="8">
-        <v>5</v>
-      </c>
-      <c r="J734" s="8">
-        <v>9.11</v>
-      </c>
-    </row>
-    <row r="735" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="735" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="5">
         <v>4</v>
       </c>
@@ -20916,10 +20801,10 @@
         <v>46106</v>
       </c>
       <c r="D735" s="13">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E735" s="8">
-        <v>47.5</v>
+        <v>56.7</v>
       </c>
       <c r="F735" s="8">
         <v>0</v>
@@ -20928,13 +20813,10 @@
         <v>0</v>
       </c>
       <c r="H735" s="8">
-        <v>6</v>
-      </c>
-      <c r="J735" s="8">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="736" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="736" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="5">
         <v>5</v>
       </c>
@@ -20945,22 +20827,19 @@
         <v>46107</v>
       </c>
       <c r="D736" s="13">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="E736" s="8">
-        <v>42.5</v>
+        <v>50.7</v>
       </c>
       <c r="F736" s="8">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G736" s="8">
         <v>0</v>
       </c>
       <c r="H736" s="8">
-        <v>8</v>
-      </c>
-      <c r="J736" s="8">
-        <v>6.7850000000000001</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="737" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20974,25 +20853,22 @@
         <v>46108</v>
       </c>
       <c r="D737" s="13">
-        <v>87.5</v>
+        <v>109</v>
       </c>
       <c r="E737" s="8">
-        <v>33.5</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="F737" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G737" s="8">
         <v>0</v>
       </c>
       <c r="H737" s="8">
-        <v>8</v>
+        <v>10.85</v>
       </c>
       <c r="I737" s="39" t="s">
         <v>68</v>
-      </c>
-      <c r="J737" s="8">
-        <v>11.309999999999999</v>
       </c>
     </row>
     <row r="738" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21006,10 +20882,10 @@
         <v>46109</v>
       </c>
       <c r="D738" s="13">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E738" s="8">
-        <v>42</v>
+        <v>38.65</v>
       </c>
       <c r="F738" s="8">
         <v>0</v>
@@ -21018,10 +20894,7 @@
         <v>0</v>
       </c>
       <c r="H738" s="8">
-        <v>4</v>
-      </c>
-      <c r="J738" s="8">
-        <v>13.615</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="739" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21035,10 +20908,10 @@
         <v>46110</v>
       </c>
       <c r="D739" s="13">
-        <v>49.5</v>
+        <v>31</v>
       </c>
       <c r="E739" s="8">
-        <v>47</v>
+        <v>52.95</v>
       </c>
       <c r="F739" s="8">
         <v>0</v>
@@ -21047,10 +20920,7 @@
         <v>0</v>
       </c>
       <c r="H739" s="8">
-        <v>6</v>
-      </c>
-      <c r="J739" s="8">
-        <v>9.4550000000000001</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="740" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21064,22 +20934,19 @@
         <v>46111</v>
       </c>
       <c r="D740" s="13">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E740" s="8">
-        <v>45.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="F740" s="8">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="G740" s="8">
         <v>0</v>
       </c>
       <c r="H740" s="8">
-        <v>13</v>
-      </c>
-      <c r="J740" s="8">
-        <v>4.665</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="741" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21093,22 +20960,19 @@
         <v>46112</v>
       </c>
       <c r="D741" s="13">
-        <v>46.5</v>
+        <v>33</v>
       </c>
       <c r="E741" s="8">
-        <v>42</v>
+        <v>58.35</v>
       </c>
       <c r="F741" s="8">
-        <v>0.1</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G741" s="8">
         <v>0</v>
       </c>
       <c r="H741" s="8">
-        <v>9</v>
-      </c>
-      <c r="J741" s="8">
-        <v>10.275</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="742" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21122,22 +20986,19 @@
         <v>46113</v>
       </c>
       <c r="D742" s="13">
-        <v>50.5</v>
+        <v>35</v>
       </c>
       <c r="E742" s="8">
-        <v>49.5</v>
+        <v>38.950000000000003</v>
       </c>
       <c r="F742" s="8">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G742" s="8">
         <v>0</v>
       </c>
       <c r="H742" s="8">
-        <v>14</v>
-      </c>
-      <c r="J742" s="8">
-        <v>6.35</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="743" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21151,22 +21012,19 @@
         <v>46114</v>
       </c>
       <c r="D743" s="13">
-        <v>77.5</v>
+        <v>20</v>
       </c>
       <c r="E743" s="8">
-        <v>51</v>
+        <v>55.35</v>
       </c>
       <c r="F743" s="8">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="G743" s="8">
         <v>0</v>
       </c>
       <c r="H743" s="8">
-        <v>12</v>
-      </c>
-      <c r="J743" s="8">
-        <v>16.48</v>
+        <v>16.100000000000001</v>
       </c>
     </row>
     <row r="744" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21180,25 +21038,22 @@
         <v>46115</v>
       </c>
       <c r="D744" s="13">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E744" s="8">
-        <v>50</v>
+        <v>48.05</v>
       </c>
       <c r="F744" s="8">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G744" s="8">
         <v>0</v>
       </c>
       <c r="H744" s="8">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="I744" s="39" t="s">
         <v>11</v>
-      </c>
-      <c r="J744" s="8">
-        <v>14.5</v>
       </c>
     </row>
     <row r="745" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21212,22 +21067,19 @@
         <v>46116</v>
       </c>
       <c r="D745" s="13">
-        <v>102.5</v>
+        <v>75</v>
       </c>
       <c r="E745" s="8">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="F745" s="8">
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="G745" s="8">
         <v>0</v>
       </c>
       <c r="H745" s="8">
-        <v>7</v>
-      </c>
-      <c r="J745" s="8">
-        <v>10.785</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="746" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21244,22 +21096,22 @@
         <v>33.5</v>
       </c>
       <c r="E746" s="8">
-        <v>50.5</v>
+        <v>44.75</v>
       </c>
       <c r="F746" s="8">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
       <c r="G746" s="8">
         <v>0</v>
       </c>
       <c r="H746" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I746" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="J746" s="8">
-        <v>8.98</v>
+      <c r="J746" s="37">
+        <v>10.504999999999999</v>
       </c>
     </row>
     <row r="747" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21273,22 +21125,22 @@
         <v>46118</v>
       </c>
       <c r="D747" s="13">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E747" s="8">
-        <v>51</v>
+        <v>44.25</v>
       </c>
       <c r="F747" s="8">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G747" s="8">
         <v>0</v>
       </c>
       <c r="H747" s="8">
-        <v>10</v>
-      </c>
-      <c r="J747" s="8">
-        <v>3.6749999999999998</v>
+        <v>11.05</v>
+      </c>
+      <c r="J747" s="37">
+        <v>6.86</v>
       </c>
     </row>
     <row r="748" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21302,10 +21154,10 @@
         <v>46119</v>
       </c>
       <c r="D748" s="13">
-        <v>46.5</v>
+        <v>52.5</v>
       </c>
       <c r="E748" s="8">
-        <v>52.5</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="F748" s="8">
         <v>0</v>
@@ -21314,10 +21166,10 @@
         <v>0</v>
       </c>
       <c r="H748" s="8">
-        <v>10</v>
-      </c>
-      <c r="J748" s="8">
-        <v>8.35</v>
+        <v>8</v>
+      </c>
+      <c r="J748" s="37">
+        <v>14.695</v>
       </c>
     </row>
     <row r="749" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21331,22 +21183,22 @@
         <v>46120</v>
       </c>
       <c r="D749" s="13">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="E749" s="8">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F749" s="8">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="G749" s="8">
         <v>0</v>
       </c>
       <c r="H749" s="8">
-        <v>4</v>
-      </c>
-      <c r="J749" s="8">
-        <v>17.63</v>
+        <v>18</v>
+      </c>
+      <c r="J749" s="37">
+        <v>10.940000000000001</v>
       </c>
     </row>
     <row r="750" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21360,22 +21212,22 @@
         <v>46121</v>
       </c>
       <c r="D750" s="13">
-        <v>56.5</v>
+        <v>84.5</v>
       </c>
       <c r="E750" s="8">
-        <v>52</v>
+        <v>57.5</v>
       </c>
       <c r="F750" s="8">
-        <v>0.2</v>
+        <v>0.79</v>
       </c>
       <c r="G750" s="8">
         <v>0</v>
       </c>
       <c r="H750" s="8">
-        <v>7</v>
-      </c>
-      <c r="J750" s="8">
-        <v>7.1400000000000006</v>
+        <v>15</v>
+      </c>
+      <c r="J750" s="37">
+        <v>11.914999999999999</v>
       </c>
     </row>
     <row r="751" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21389,22 +21241,22 @@
         <v>46122</v>
       </c>
       <c r="D751" s="13">
-        <v>76</v>
+        <v>112.5</v>
       </c>
       <c r="E751" s="8">
-        <v>51</v>
+        <v>46.5</v>
       </c>
       <c r="F751" s="8">
-        <v>0.36</v>
+        <v>0.03</v>
       </c>
       <c r="G751" s="8">
         <v>0</v>
       </c>
       <c r="H751" s="8">
-        <v>8</v>
-      </c>
-      <c r="J751" s="8">
-        <v>7.5950000000000006</v>
+        <v>9</v>
+      </c>
+      <c r="J751" s="37">
+        <v>20.38</v>
       </c>
     </row>
     <row r="752" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21418,22 +21270,22 @@
         <v>46123</v>
       </c>
       <c r="D752" s="13">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E752" s="8">
-        <v>47.5</v>
+        <v>56.5</v>
       </c>
       <c r="F752" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G752" s="8">
         <v>0</v>
       </c>
       <c r="H752" s="8">
-        <v>15</v>
-      </c>
-      <c r="J752" s="8">
-        <v>16.350000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="J752" s="37">
+        <v>10.845000000000001</v>
       </c>
     </row>
     <row r="753" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21447,22 +21299,22 @@
         <v>46124</v>
       </c>
       <c r="D753" s="13">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E753" s="8">
-        <v>46.5</v>
+        <v>69</v>
       </c>
       <c r="F753" s="8">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G753" s="8">
         <v>0</v>
       </c>
       <c r="H753" s="8">
-        <v>10</v>
-      </c>
-      <c r="J753" s="8">
-        <v>4.6950000000000003</v>
+        <v>15</v>
+      </c>
+      <c r="J753" s="37">
+        <v>14.02</v>
       </c>
     </row>
     <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21476,22 +21328,22 @@
         <v>46125</v>
       </c>
       <c r="D754" s="13">
-        <v>52.5</v>
+        <v>59.5</v>
       </c>
       <c r="E754" s="8">
-        <v>48.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="F754" s="8">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G754" s="8">
         <v>0</v>
       </c>
       <c r="H754" s="8">
-        <v>4</v>
-      </c>
-      <c r="J754" s="8">
-        <v>13.96</v>
+        <v>13</v>
+      </c>
+      <c r="J754" s="37">
+        <v>12.28</v>
       </c>
     </row>
     <row r="755" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21505,22 +21357,22 @@
         <v>46126</v>
       </c>
       <c r="D755" s="13">
-        <v>51</v>
+        <v>45.5</v>
       </c>
       <c r="E755" s="8">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="F755" s="8">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="G755" s="8">
         <v>0</v>
       </c>
       <c r="H755" s="8">
-        <v>9</v>
-      </c>
-      <c r="J755" s="8">
-        <v>14.635</v>
+        <v>13</v>
+      </c>
+      <c r="J755" s="37">
+        <v>5.9950000000000001</v>
       </c>
     </row>
     <row r="756" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21534,22 +21386,22 @@
         <v>46127</v>
       </c>
       <c r="D756" s="13">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="E756" s="8">
-        <v>52.5</v>
+        <v>42</v>
       </c>
       <c r="F756" s="8">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="G756" s="8">
         <v>0</v>
       </c>
       <c r="H756" s="8">
-        <v>9</v>
-      </c>
-      <c r="J756" s="8">
-        <v>8.4049999999999994</v>
+        <v>12</v>
+      </c>
+      <c r="J756" s="37">
+        <v>6.3250000000000002</v>
       </c>
     </row>
     <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21563,22 +21415,22 @@
         <v>46128</v>
       </c>
       <c r="D757" s="13">
-        <v>52</v>
+        <v>62.5</v>
       </c>
       <c r="E757" s="8">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="F757" s="8">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="G757" s="8">
         <v>0</v>
       </c>
       <c r="H757" s="8">
-        <v>8</v>
-      </c>
-      <c r="J757" s="8">
-        <v>4.1500000000000004</v>
+        <v>10</v>
+      </c>
+      <c r="J757" s="37">
+        <v>7.125</v>
       </c>
     </row>
     <row r="758" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21592,30 +21444,175 @@
         <v>46129</v>
       </c>
       <c r="D758" s="13">
-        <v>112.5</v>
+        <v>116</v>
       </c>
       <c r="E758" s="8">
+        <v>57</v>
+      </c>
+      <c r="F758" s="8">
+        <v>0</v>
+      </c>
+      <c r="G758" s="8">
+        <v>0</v>
+      </c>
+      <c r="H758" s="8">
+        <v>7</v>
+      </c>
+      <c r="J758" s="37">
+        <v>9.3949999999999996</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="5">
+        <v>7</v>
+      </c>
+      <c r="B759" s="5">
+        <v>758</v>
+      </c>
+      <c r="C759" s="50">
+        <v>46130</v>
+      </c>
+      <c r="D759" s="13">
+        <v>135.5</v>
+      </c>
+      <c r="E759" s="8">
+        <v>56.5</v>
+      </c>
+      <c r="F759" s="8">
+        <v>0</v>
+      </c>
+      <c r="G759" s="8">
+        <v>0</v>
+      </c>
+      <c r="H759" s="8">
+        <v>6</v>
+      </c>
+      <c r="J759" s="37">
+        <v>14.775</v>
+      </c>
+    </row>
+    <row r="760" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A760" s="5">
+        <v>1</v>
+      </c>
+      <c r="B760" s="5">
+        <v>759</v>
+      </c>
+      <c r="C760" s="50">
+        <v>46131</v>
+      </c>
+      <c r="D760" s="13">
+        <v>62</v>
+      </c>
+      <c r="E760" s="8">
+        <v>56</v>
+      </c>
+      <c r="F760" s="8">
+        <v>0</v>
+      </c>
+      <c r="G760" s="8">
+        <v>0</v>
+      </c>
+      <c r="H760" s="8">
+        <v>4</v>
+      </c>
+      <c r="J760" s="37">
+        <v>17.855</v>
+      </c>
+    </row>
+    <row r="761" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A761" s="5">
+        <v>2</v>
+      </c>
+      <c r="B761" s="5">
+        <v>760</v>
+      </c>
+      <c r="C761" s="50">
+        <v>46132</v>
+      </c>
+      <c r="D761" s="13">
         <v>46</v>
       </c>
-      <c r="F758" s="8">
-        <v>0</v>
-      </c>
-      <c r="G758" s="8">
-        <v>0</v>
-      </c>
-      <c r="H758" s="8">
-        <v>10</v>
-      </c>
-      <c r="J758" s="8">
-        <v>12.469999999999999</v>
+      <c r="E761" s="8">
+        <v>60</v>
+      </c>
+      <c r="F761" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="G761" s="8">
+        <v>0</v>
+      </c>
+      <c r="H761" s="8">
+        <v>9</v>
+      </c>
+      <c r="J761" s="37">
+        <v>7.7449999999999992</v>
+      </c>
+    </row>
+    <row r="762" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A762" s="5">
+        <v>3</v>
+      </c>
+      <c r="B762" s="5">
+        <v>761</v>
+      </c>
+      <c r="C762" s="50">
+        <v>46133</v>
+      </c>
+      <c r="D762" s="13">
+        <v>50</v>
+      </c>
+      <c r="E762" s="8">
+        <v>35.9</v>
+      </c>
+      <c r="F762" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G762" s="8">
+        <v>0</v>
+      </c>
+      <c r="H762" s="8">
+        <v>5</v>
+      </c>
+      <c r="J762" s="37">
+        <v>9.495000000000001</v>
+      </c>
+    </row>
+    <row r="763" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A763" s="5">
+        <v>4</v>
+      </c>
+      <c r="B763" s="5">
+        <v>762</v>
+      </c>
+      <c r="C763" s="50">
+        <v>46134</v>
+      </c>
+      <c r="D763" s="13">
+        <v>47.5</v>
+      </c>
+      <c r="E763" s="8">
+        <v>45</v>
+      </c>
+      <c r="F763" s="8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G763" s="8">
+        <v>0</v>
+      </c>
+      <c r="H763" s="8">
+        <v>7</v>
+      </c>
+      <c r="J763" s="37">
+        <v>7.6099999999999994</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A758">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="A2:A763">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21626,7 +21623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8670AF5D-84FB-432F-8F14-677D63D19C50}">
-  <dimension ref="A1:X310"/>
+  <dimension ref="A1:X315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -37836,6 +37833,9 @@
       </c>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A272" s="13">
+        <v>12</v>
+      </c>
       <c r="B272" s="21">
         <v>46097</v>
       </c>
@@ -37883,6 +37883,14 @@
         <f t="shared" si="58"/>
         <v>3.7</v>
       </c>
+      <c r="R272" s="25">
+        <f t="shared" ref="R272:R291" si="59">O272-A272</f>
+        <v>31</v>
+      </c>
+      <c r="S272">
+        <f t="shared" ref="S272:S291" si="60">O272/A272</f>
+        <v>3.5833333333333335</v>
+      </c>
       <c r="T272">
         <v>42</v>
       </c>
@@ -37890,7 +37898,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A273" s="13">
+        <v>0</v>
+      </c>
       <c r="B273" s="21">
         <v>46098</v>
       </c>
@@ -37938,6 +37949,14 @@
         <f t="shared" si="58"/>
         <v>9.09</v>
       </c>
+      <c r="R273" s="25">
+        <f t="shared" si="59"/>
+        <v>35</v>
+      </c>
+      <c r="S273" t="e">
+        <f t="shared" si="60"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T273">
         <v>40</v>
       </c>
@@ -37945,7 +37964,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A274" s="13">
+        <v>46</v>
+      </c>
       <c r="B274" s="21">
         <v>46099</v>
       </c>
@@ -37993,6 +38015,14 @@
         <f t="shared" si="58"/>
         <v>4.37</v>
       </c>
+      <c r="R274" s="25">
+        <f t="shared" si="59"/>
+        <v>-1</v>
+      </c>
+      <c r="S274">
+        <f t="shared" si="60"/>
+        <v>0.97826086956521741</v>
+      </c>
       <c r="T274">
         <v>44</v>
       </c>
@@ -38000,7 +38030,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="275" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A275" s="13">
+        <v>58</v>
+      </c>
       <c r="B275" s="21">
         <v>46100</v>
       </c>
@@ -38048,6 +38081,14 @@
         <f t="shared" si="58"/>
         <v>6.19</v>
       </c>
+      <c r="R275" s="25">
+        <f t="shared" si="59"/>
+        <v>-3</v>
+      </c>
+      <c r="S275">
+        <f t="shared" si="60"/>
+        <v>0.94827586206896552</v>
+      </c>
       <c r="T275">
         <v>60</v>
       </c>
@@ -38055,7 +38096,10 @@
         <v>51</v>
       </c>
     </row>
-    <row r="276" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A276" s="13">
+        <v>84</v>
+      </c>
       <c r="B276" s="21">
         <v>46101</v>
       </c>
@@ -38103,6 +38147,14 @@
         <f t="shared" si="58"/>
         <v>11.9</v>
       </c>
+      <c r="R276" s="25">
+        <f t="shared" si="59"/>
+        <v>32</v>
+      </c>
+      <c r="S276">
+        <f t="shared" si="60"/>
+        <v>1.3809523809523809</v>
+      </c>
       <c r="T276">
         <v>136</v>
       </c>
@@ -38110,7 +38162,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="277" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A277" s="13">
+        <v>156</v>
+      </c>
       <c r="B277" s="21">
         <v>46102</v>
       </c>
@@ -38158,6 +38213,14 @@
         <f t="shared" si="58"/>
         <v>12.22</v>
       </c>
+      <c r="R277" s="25">
+        <f t="shared" si="59"/>
+        <v>-24</v>
+      </c>
+      <c r="S277">
+        <f t="shared" si="60"/>
+        <v>0.84615384615384615</v>
+      </c>
       <c r="T277">
         <v>130</v>
       </c>
@@ -38165,7 +38228,10 @@
         <v>132</v>
       </c>
     </row>
-    <row r="278" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A278" s="13">
+        <v>45</v>
+      </c>
       <c r="B278" s="21">
         <v>46103</v>
       </c>
@@ -38213,6 +38279,14 @@
         <f t="shared" si="58"/>
         <v>4.96</v>
       </c>
+      <c r="R278" s="25">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="S278">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
       <c r="T278">
         <v>50</v>
       </c>
@@ -38220,7 +38294,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="279" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A279" s="13">
+        <v>18</v>
+      </c>
       <c r="B279" s="21">
         <v>46104</v>
       </c>
@@ -38268,6 +38345,14 @@
         <f t="shared" si="58"/>
         <v>6.23</v>
       </c>
+      <c r="R279" s="25">
+        <f t="shared" si="59"/>
+        <v>32</v>
+      </c>
+      <c r="S279">
+        <f t="shared" si="60"/>
+        <v>2.7777777777777777</v>
+      </c>
       <c r="T279">
         <v>57</v>
       </c>
@@ -38275,7 +38360,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="280" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A280" s="13">
+        <v>37</v>
+      </c>
       <c r="B280" s="21">
         <v>46105</v>
       </c>
@@ -38323,6 +38411,14 @@
         <f t="shared" si="58"/>
         <v>7.15</v>
       </c>
+      <c r="R280" s="25">
+        <f t="shared" si="59"/>
+        <v>9</v>
+      </c>
+      <c r="S280">
+        <f t="shared" si="60"/>
+        <v>1.2432432432432432</v>
+      </c>
       <c r="T280">
         <v>66</v>
       </c>
@@ -38330,7 +38426,10 @@
         <v>42</v>
       </c>
     </row>
-    <row r="281" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A281" s="13">
+        <v>38</v>
+      </c>
       <c r="B281" s="21">
         <v>46106</v>
       </c>
@@ -38378,6 +38477,14 @@
         <f t="shared" si="58"/>
         <v>5.05</v>
       </c>
+      <c r="R281" s="25">
+        <f t="shared" si="59"/>
+        <v>8</v>
+      </c>
+      <c r="S281">
+        <f t="shared" si="60"/>
+        <v>1.2105263157894737</v>
+      </c>
       <c r="T281">
         <v>49</v>
       </c>
@@ -38385,7 +38492,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="282" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A282" s="13">
+        <v>119</v>
+      </c>
       <c r="B282" s="21">
         <v>46107</v>
       </c>
@@ -38433,6 +38543,14 @@
         <f t="shared" si="58"/>
         <v>4.38</v>
       </c>
+      <c r="R282" s="25">
+        <f t="shared" si="59"/>
+        <v>-71</v>
+      </c>
+      <c r="S282">
+        <f t="shared" si="60"/>
+        <v>0.40336134453781514</v>
+      </c>
       <c r="T282">
         <v>50</v>
       </c>
@@ -38440,7 +38558,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="283" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A283" s="13">
+        <v>109</v>
+      </c>
       <c r="B283" s="21">
         <v>46108</v>
       </c>
@@ -38488,6 +38609,14 @@
         <f t="shared" si="58"/>
         <v>10</v>
       </c>
+      <c r="R283" s="25">
+        <f t="shared" si="59"/>
+        <v>-21</v>
+      </c>
+      <c r="S283">
+        <f t="shared" si="60"/>
+        <v>0.80733944954128445</v>
+      </c>
       <c r="T283">
         <v>95</v>
       </c>
@@ -38495,7 +38624,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="284" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A284" s="13">
+        <v>148</v>
+      </c>
       <c r="B284" s="21">
         <v>46109</v>
       </c>
@@ -38543,6 +38675,14 @@
         <f t="shared" si="58"/>
         <v>11.24</v>
       </c>
+      <c r="R284" s="25">
+        <f t="shared" si="59"/>
+        <v>-20</v>
+      </c>
+      <c r="S284">
+        <f t="shared" si="60"/>
+        <v>0.86486486486486491</v>
+      </c>
       <c r="T284">
         <v>137</v>
       </c>
@@ -38550,7 +38690,10 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A285" s="13">
+        <v>31</v>
+      </c>
       <c r="B285" s="21">
         <v>46110</v>
       </c>
@@ -38598,6 +38741,14 @@
         <f t="shared" si="58"/>
         <v>5.23</v>
       </c>
+      <c r="R285" s="25">
+        <f t="shared" si="59"/>
+        <v>22</v>
+      </c>
+      <c r="S285">
+        <f t="shared" si="60"/>
+        <v>1.7096774193548387</v>
+      </c>
       <c r="T285">
         <v>66</v>
       </c>
@@ -38605,7 +38756,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="286" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A286" s="13">
+        <v>20</v>
+      </c>
       <c r="B286" s="21">
         <v>46111</v>
       </c>
@@ -38653,6 +38807,14 @@
         <f t="shared" si="58"/>
         <v>3.27</v>
       </c>
+      <c r="R286" s="25">
+        <f t="shared" si="59"/>
+        <v>23</v>
+      </c>
+      <c r="S286">
+        <f t="shared" si="60"/>
+        <v>2.15</v>
+      </c>
       <c r="T286">
         <v>41</v>
       </c>
@@ -38660,7 +38822,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A287" s="13">
+        <v>33</v>
+      </c>
       <c r="B287" s="21">
         <v>46112</v>
       </c>
@@ -38708,6 +38873,14 @@
         <f t="shared" si="58"/>
         <v>9.23</v>
       </c>
+      <c r="R287" s="25">
+        <f t="shared" si="59"/>
+        <v>16</v>
+      </c>
+      <c r="S287">
+        <f t="shared" si="60"/>
+        <v>1.4848484848484849</v>
+      </c>
       <c r="T287">
         <v>55</v>
       </c>
@@ -38715,7 +38888,10 @@
         <v>42</v>
       </c>
     </row>
-    <row r="288" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A288" s="13">
+        <v>35</v>
+      </c>
       <c r="B288" s="21">
         <v>46113</v>
       </c>
@@ -38763,6 +38939,14 @@
         <f t="shared" si="58"/>
         <v>5.12</v>
       </c>
+      <c r="R288" s="25">
+        <f t="shared" si="59"/>
+        <v>16</v>
+      </c>
+      <c r="S288">
+        <f t="shared" si="60"/>
+        <v>1.4571428571428571</v>
+      </c>
       <c r="T288">
         <v>48</v>
       </c>
@@ -38770,7 +38954,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="289" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A289" s="13">
+        <v>20</v>
+      </c>
       <c r="B289" s="21">
         <v>46114</v>
       </c>
@@ -38818,6 +39005,14 @@
         <f t="shared" si="58"/>
         <v>15.06</v>
       </c>
+      <c r="R289" s="25">
+        <f t="shared" si="59"/>
+        <v>60</v>
+      </c>
+      <c r="S289">
+        <f t="shared" si="60"/>
+        <v>4</v>
+      </c>
       <c r="T289">
         <v>90</v>
       </c>
@@ -38825,7 +39020,10 @@
         <v>67</v>
       </c>
     </row>
-    <row r="290" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A290" s="13">
+        <v>62</v>
+      </c>
       <c r="B290" s="21">
         <v>46115</v>
       </c>
@@ -38866,12 +39064,20 @@
         <v>65</v>
       </c>
       <c r="O290" s="19">
-        <f t="shared" ref="O290:O304" si="59">ROUND(AVERAGE(C290:N290,T290:U290),0)</f>
+        <f t="shared" ref="O290:O304" si="61">ROUND(AVERAGE(C290:N290,T290:U290),0)</f>
         <v>80</v>
       </c>
       <c r="P290" s="19">
-        <f t="shared" ref="P290:P304" si="60">ROUND(_xlfn.STDEV.P(C290:N290,T290:U290),2)</f>
+        <f t="shared" ref="P290:P304" si="62">ROUND(_xlfn.STDEV.P(C290:N290,T290:U290),2)</f>
         <v>12.17</v>
+      </c>
+      <c r="R290" s="25">
+        <f t="shared" si="59"/>
+        <v>18</v>
+      </c>
+      <c r="S290">
+        <f t="shared" si="60"/>
+        <v>1.2903225806451613</v>
       </c>
       <c r="T290">
         <v>90</v>
@@ -38880,7 +39086,10 @@
         <v>67</v>
       </c>
     </row>
-    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A291" s="13">
+        <v>75</v>
+      </c>
       <c r="B291" s="21">
         <v>46116</v>
       </c>
@@ -38921,12 +39130,20 @@
         <v>112</v>
       </c>
       <c r="O291" s="19">
+        <f t="shared" si="61"/>
+        <v>106</v>
+      </c>
+      <c r="P291" s="19">
+        <f t="shared" si="62"/>
+        <v>10.36</v>
+      </c>
+      <c r="R291" s="25">
         <f t="shared" si="59"/>
-        <v>106</v>
-      </c>
-      <c r="P291" s="19">
+        <v>31</v>
+      </c>
+      <c r="S291">
         <f t="shared" si="60"/>
-        <v>10.36</v>
+        <v>1.4133333333333333</v>
       </c>
       <c r="T291">
         <v>96</v>
@@ -38935,447 +39152,447 @@
         <v>103</v>
       </c>
     </row>
-    <row r="292" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B292" s="21">
         <v>46117</v>
       </c>
       <c r="C292">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D292">
+        <v>25</v>
+      </c>
+      <c r="E292">
+        <v>46</v>
+      </c>
+      <c r="F292">
+        <v>26</v>
+      </c>
+      <c r="G292">
+        <v>62</v>
+      </c>
+      <c r="H292">
+        <v>28</v>
+      </c>
+      <c r="I292">
+        <v>44</v>
+      </c>
+      <c r="J292">
+        <v>26</v>
+      </c>
+      <c r="K292">
+        <v>25</v>
+      </c>
+      <c r="L292">
+        <v>34</v>
+      </c>
+      <c r="M292">
         <v>30</v>
-      </c>
-      <c r="E292">
-        <v>47</v>
-      </c>
-      <c r="F292">
-        <v>28</v>
-      </c>
-      <c r="G292">
-        <v>38</v>
-      </c>
-      <c r="H292">
-        <v>24</v>
-      </c>
-      <c r="I292">
-        <v>46</v>
-      </c>
-      <c r="J292">
-        <v>28</v>
-      </c>
-      <c r="K292">
-        <v>45</v>
-      </c>
-      <c r="L292">
-        <v>31</v>
-      </c>
-      <c r="M292">
-        <v>37</v>
       </c>
       <c r="N292">
         <v>30</v>
       </c>
       <c r="O292" s="19">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>35</v>
       </c>
       <c r="P292" s="19">
-        <f t="shared" si="60"/>
-        <v>7.38</v>
+        <f t="shared" si="62"/>
+        <v>11.19</v>
       </c>
       <c r="T292">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="U292">
         <v>29</v>
       </c>
     </row>
-    <row r="293" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B293" s="21">
         <v>46118</v>
       </c>
       <c r="C293">
+        <v>52</v>
+      </c>
+      <c r="D293">
+        <v>40</v>
+      </c>
+      <c r="E293">
+        <v>54</v>
+      </c>
+      <c r="F293">
+        <v>39</v>
+      </c>
+      <c r="G293">
+        <v>48</v>
+      </c>
+      <c r="H293">
+        <v>41</v>
+      </c>
+      <c r="I293">
+        <v>50</v>
+      </c>
+      <c r="J293">
+        <v>40</v>
+      </c>
+      <c r="K293">
+        <v>50</v>
+      </c>
+      <c r="L293">
+        <v>43</v>
+      </c>
+      <c r="M293">
+        <v>48</v>
+      </c>
+      <c r="N293">
+        <v>42</v>
+      </c>
+      <c r="O293" s="19">
+        <f t="shared" si="61"/>
         <v>46</v>
       </c>
-      <c r="D293">
-        <v>44</v>
-      </c>
-      <c r="E293">
-        <v>50</v>
-      </c>
-      <c r="F293">
-        <v>45</v>
-      </c>
-      <c r="G293">
-        <v>47</v>
-      </c>
-      <c r="H293">
-        <v>44</v>
-      </c>
-      <c r="I293">
-        <v>46</v>
-      </c>
-      <c r="J293">
-        <v>44</v>
-      </c>
-      <c r="K293">
-        <v>47</v>
-      </c>
-      <c r="L293">
-        <v>45</v>
-      </c>
-      <c r="M293">
-        <v>44</v>
-      </c>
-      <c r="N293">
-        <v>43</v>
-      </c>
-      <c r="O293" s="19">
-        <f t="shared" si="59"/>
-        <v>45</v>
-      </c>
       <c r="P293" s="19">
-        <f t="shared" si="60"/>
-        <v>1.83</v>
+        <f t="shared" si="62"/>
+        <v>5.24</v>
       </c>
       <c r="T293">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="U293">
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B294" s="21">
         <v>46119</v>
       </c>
       <c r="C294">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D294">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E294">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F294">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G294">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H294">
         <v>43</v>
       </c>
       <c r="I294">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="J294">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K294">
+        <v>77</v>
+      </c>
+      <c r="L294">
+        <v>49</v>
+      </c>
+      <c r="M294">
+        <v>79</v>
+      </c>
+      <c r="N294">
+        <v>44</v>
+      </c>
+      <c r="O294" s="19">
+        <f t="shared" si="61"/>
+        <v>55</v>
+      </c>
+      <c r="P294" s="19">
+        <f t="shared" si="62"/>
+        <v>13.06</v>
+      </c>
+      <c r="T294">
+        <v>58</v>
+      </c>
+      <c r="U294">
         <v>47</v>
       </c>
-      <c r="L294">
-        <v>48</v>
-      </c>
-      <c r="M294">
-        <v>63</v>
-      </c>
-      <c r="N294">
-        <v>45</v>
-      </c>
-      <c r="O294" s="19">
-        <f t="shared" si="59"/>
-        <v>49</v>
-      </c>
-      <c r="P294" s="19">
-        <f t="shared" si="60"/>
-        <v>5.46</v>
-      </c>
-      <c r="T294">
-        <v>54</v>
-      </c>
-      <c r="U294">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="295" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B295" s="21">
         <v>46120</v>
       </c>
       <c r="C295">
+        <v>55</v>
+      </c>
+      <c r="D295">
+        <v>57</v>
+      </c>
+      <c r="E295">
+        <v>63</v>
+      </c>
+      <c r="F295">
         <v>51</v>
       </c>
-      <c r="D295">
-        <v>42</v>
-      </c>
-      <c r="E295">
-        <v>69</v>
-      </c>
-      <c r="F295">
-        <v>42</v>
-      </c>
       <c r="G295">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H295">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I295">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J295">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="K295">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L295">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M295">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="N295">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="O295" s="19">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
+        <v>60</v>
+      </c>
+      <c r="P295" s="19">
+        <f t="shared" si="62"/>
+        <v>8.56</v>
+      </c>
+      <c r="T295">
         <v>56</v>
       </c>
-      <c r="P295" s="19">
-        <f t="shared" si="60"/>
-        <v>17.27</v>
-      </c>
-      <c r="T295">
-        <v>68</v>
-      </c>
       <c r="U295">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="296" spans="2:21" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B296" s="21">
         <v>46121</v>
       </c>
       <c r="C296">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D296">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="E296">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F296">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="G296">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H296">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="I296">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="J296">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="K296">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L296">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="M296">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="N296">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="O296" s="19">
-        <f t="shared" si="59"/>
-        <v>57</v>
+        <f t="shared" si="61"/>
+        <v>91</v>
       </c>
       <c r="P296" s="19">
-        <f t="shared" si="60"/>
-        <v>6.7</v>
+        <f t="shared" si="62"/>
+        <v>7.5</v>
       </c>
       <c r="T296">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="U296">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="297" spans="2:21" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B297" s="21">
         <v>46122</v>
       </c>
       <c r="C297">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="D297">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E297">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F297">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G297">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="H297">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I297">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="J297">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="K297">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="L297">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="M297">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="N297">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="O297" s="19">
-        <f t="shared" si="59"/>
-        <v>79</v>
+        <f t="shared" si="61"/>
+        <v>115</v>
       </c>
       <c r="P297" s="19">
-        <f t="shared" si="60"/>
-        <v>7.12</v>
+        <f t="shared" si="62"/>
+        <v>18.22</v>
       </c>
       <c r="T297">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="U297">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="298" spans="2:21" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B298" s="21">
         <v>46123</v>
       </c>
       <c r="C298">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="D298">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E298">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F298">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G298">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H298">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="I298">
         <v>141</v>
       </c>
       <c r="J298">
+        <v>128</v>
+      </c>
+      <c r="K298">
+        <v>145</v>
+      </c>
+      <c r="L298">
+        <v>126</v>
+      </c>
+      <c r="M298">
+        <v>134</v>
+      </c>
+      <c r="N298">
+        <v>123</v>
+      </c>
+      <c r="O298" s="19">
+        <f t="shared" si="61"/>
+        <v>137</v>
+      </c>
+      <c r="P298" s="19">
+        <f t="shared" si="62"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="T298">
+        <v>147</v>
+      </c>
+      <c r="U298">
         <v>136</v>
       </c>
-      <c r="K298">
-        <v>158</v>
-      </c>
-      <c r="L298">
-        <v>152</v>
-      </c>
-      <c r="M298">
-        <v>168</v>
-      </c>
-      <c r="N298">
-        <v>138</v>
-      </c>
-      <c r="O298" s="19">
-        <f t="shared" si="59"/>
-        <v>145</v>
-      </c>
-      <c r="P298" s="19">
-        <f t="shared" si="60"/>
-        <v>11.04</v>
-      </c>
-      <c r="T298">
-        <v>149</v>
-      </c>
-      <c r="U298">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="299" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B299" s="21">
         <v>46124</v>
       </c>
       <c r="C299">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D299">
+        <v>67</v>
+      </c>
+      <c r="E299">
+        <v>66</v>
+      </c>
+      <c r="F299">
+        <v>53</v>
+      </c>
+      <c r="G299">
+        <v>59</v>
+      </c>
+      <c r="H299">
         <v>44</v>
       </c>
-      <c r="E299">
-        <v>48</v>
-      </c>
-      <c r="F299">
-        <v>46</v>
-      </c>
-      <c r="G299">
-        <v>49</v>
-      </c>
-      <c r="H299">
-        <v>45</v>
-      </c>
       <c r="I299">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="J299">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K299">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="L299">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="M299">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="N299">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="O299" s="19">
-        <f t="shared" si="59"/>
-        <v>47</v>
+        <f t="shared" si="61"/>
+        <v>64</v>
       </c>
       <c r="P299" s="19">
-        <f t="shared" si="60"/>
-        <v>3.33</v>
+        <f t="shared" si="62"/>
+        <v>10.53</v>
       </c>
       <c r="T299">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="U299">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="300" spans="2:21" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B300" s="21">
         <v>46125</v>
       </c>
@@ -39383,580 +39600,849 @@
         <v>70</v>
       </c>
       <c r="D300">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E300">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F300">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G300">
         <v>62</v>
       </c>
       <c r="H300">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I300">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="J300">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K300">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L300">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M300">
+        <v>70</v>
+      </c>
+      <c r="N300">
+        <v>57</v>
+      </c>
+      <c r="O300" s="19">
+        <f t="shared" si="61"/>
         <v>62</v>
       </c>
-      <c r="N300">
-        <v>53</v>
-      </c>
-      <c r="O300" s="19">
-        <f t="shared" si="59"/>
-        <v>57</v>
-      </c>
       <c r="P300" s="19">
-        <f t="shared" si="60"/>
-        <v>9.24</v>
+        <f t="shared" si="62"/>
+        <v>9.5299999999999994</v>
       </c>
       <c r="T300">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U300">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="301" spans="2:21" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B301" s="21">
         <v>46126</v>
       </c>
       <c r="C301">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D301">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E301">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F301">
         <v>42</v>
       </c>
       <c r="G301">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H301">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I301">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="J301">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K301">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L301">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M301">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="N301">
         <v>44</v>
       </c>
       <c r="O301" s="19">
-        <f t="shared" si="59"/>
-        <v>54</v>
+        <f t="shared" si="61"/>
+        <v>47</v>
       </c>
       <c r="P301" s="19">
-        <f t="shared" si="60"/>
-        <v>12.41</v>
+        <f t="shared" si="62"/>
+        <v>3.81</v>
       </c>
       <c r="T301">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="U301">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="302" spans="2:21" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B302" s="21">
         <v>46127</v>
       </c>
       <c r="C302">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D302">
+        <v>45</v>
+      </c>
+      <c r="E302">
+        <v>68</v>
+      </c>
+      <c r="F302">
+        <v>47</v>
+      </c>
+      <c r="G302">
+        <v>56</v>
+      </c>
+      <c r="H302">
+        <v>52</v>
+      </c>
+      <c r="I302">
+        <v>47</v>
+      </c>
+      <c r="J302">
+        <v>43</v>
+      </c>
+      <c r="K302">
+        <v>51</v>
+      </c>
+      <c r="L302">
         <v>48</v>
-      </c>
-      <c r="E302">
-        <v>57</v>
-      </c>
-      <c r="F302">
-        <v>49</v>
-      </c>
-      <c r="G302">
-        <v>51</v>
-      </c>
-      <c r="H302">
-        <v>47</v>
-      </c>
-      <c r="I302">
-        <v>58</v>
-      </c>
-      <c r="J302">
-        <v>49</v>
-      </c>
-      <c r="K302">
-        <v>54</v>
-      </c>
-      <c r="L302">
-        <v>54</v>
       </c>
       <c r="M302">
         <v>60</v>
       </c>
       <c r="N302">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O302" s="19">
-        <f t="shared" si="59"/>
-        <v>53</v>
+        <f t="shared" si="61"/>
+        <v>51</v>
       </c>
       <c r="P302" s="19">
-        <f t="shared" si="60"/>
-        <v>4.46</v>
+        <f t="shared" si="62"/>
+        <v>6.66</v>
       </c>
       <c r="T302">
         <v>57</v>
       </c>
       <c r="U302">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="303" spans="2:21" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B303" s="21">
         <v>46128</v>
       </c>
       <c r="C303">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D303">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E303">
+        <v>67</v>
+      </c>
+      <c r="F303">
+        <v>59</v>
+      </c>
+      <c r="G303">
+        <v>72</v>
+      </c>
+      <c r="H303">
+        <v>66</v>
+      </c>
+      <c r="I303">
+        <v>72</v>
+      </c>
+      <c r="J303">
+        <v>55</v>
+      </c>
+      <c r="K303">
+        <v>78</v>
+      </c>
+      <c r="L303">
         <v>58</v>
       </c>
-      <c r="F303">
-        <v>54</v>
-      </c>
-      <c r="G303">
-        <v>49</v>
-      </c>
-      <c r="H303">
-        <v>58</v>
-      </c>
-      <c r="I303">
-        <v>54</v>
-      </c>
-      <c r="J303">
-        <v>51</v>
-      </c>
-      <c r="K303">
-        <v>57</v>
-      </c>
-      <c r="L303">
-        <v>51</v>
-      </c>
       <c r="M303">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="N303">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O303" s="19">
-        <f t="shared" si="59"/>
-        <v>53</v>
+        <f t="shared" si="61"/>
+        <v>64</v>
       </c>
       <c r="P303" s="19">
-        <f t="shared" si="60"/>
-        <v>3.49</v>
+        <f t="shared" si="62"/>
+        <v>7.21</v>
       </c>
       <c r="T303">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="U303">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="304" spans="2:21" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B304" s="21">
         <v>46129</v>
       </c>
       <c r="C304">
+        <v>124</v>
+      </c>
+      <c r="D304">
+        <v>118</v>
+      </c>
+      <c r="E304">
+        <v>109</v>
+      </c>
+      <c r="F304">
+        <v>111</v>
+      </c>
+      <c r="G304">
+        <v>117</v>
+      </c>
+      <c r="H304">
+        <v>112</v>
+      </c>
+      <c r="I304">
+        <v>126</v>
+      </c>
+      <c r="J304">
+        <v>105</v>
+      </c>
+      <c r="K304">
+        <v>124</v>
+      </c>
+      <c r="L304">
+        <v>111</v>
+      </c>
+      <c r="M304">
+        <v>131</v>
+      </c>
+      <c r="N304">
+        <v>108</v>
+      </c>
+      <c r="O304" s="19">
+        <f t="shared" si="61"/>
+        <v>118</v>
+      </c>
+      <c r="P304" s="19">
+        <f t="shared" si="62"/>
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="T304">
+        <v>132</v>
+      </c>
+      <c r="U304">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="305" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B305" s="21">
+        <v>46130</v>
+      </c>
+      <c r="C305">
+        <v>132</v>
+      </c>
+      <c r="D305">
+        <v>140</v>
+      </c>
+      <c r="E305">
+        <v>121</v>
+      </c>
+      <c r="F305">
+        <v>137</v>
+      </c>
+      <c r="G305">
+        <v>149</v>
+      </c>
+      <c r="H305">
+        <v>156</v>
+      </c>
+      <c r="I305">
+        <v>147</v>
+      </c>
+      <c r="J305">
+        <v>127</v>
+      </c>
+      <c r="K305">
+        <v>129</v>
+      </c>
+      <c r="L305">
         <v>125</v>
       </c>
-      <c r="D304">
-        <v>109</v>
-      </c>
-      <c r="E304">
+      <c r="M305">
+        <v>115</v>
+      </c>
+      <c r="N305">
         <v>123</v>
       </c>
-      <c r="F304">
-        <v>114</v>
-      </c>
-      <c r="G304">
-        <v>97</v>
-      </c>
-      <c r="H304">
-        <v>105</v>
-      </c>
-      <c r="I304">
-        <v>127</v>
-      </c>
-      <c r="J304">
-        <v>108</v>
-      </c>
-      <c r="K304">
-        <v>120</v>
-      </c>
-      <c r="L304">
-        <v>125</v>
-      </c>
-      <c r="M304">
-        <v>123</v>
-      </c>
-      <c r="N304">
-        <v>113</v>
-      </c>
-      <c r="O304" s="19">
-        <f t="shared" si="59"/>
-        <v>116</v>
-      </c>
-      <c r="P304" s="19">
-        <f t="shared" si="60"/>
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="T304">
-        <v>125</v>
-      </c>
-      <c r="U304">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="305" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B305" s="30" t="s">
+      <c r="O305" s="19">
+        <f t="shared" ref="O305:O309" si="63">ROUND(AVERAGE(C305:N305,T305:U305),0)</f>
+        <v>136</v>
+      </c>
+      <c r="P305" s="19">
+        <f t="shared" ref="P305:P309" si="64">ROUND(_xlfn.STDEV.P(C305:N305,T305:U305),2)</f>
+        <v>13.32</v>
+      </c>
+      <c r="T305">
+        <v>162</v>
+      </c>
+      <c r="U305">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B306" s="21">
+        <v>46131</v>
+      </c>
+      <c r="C306">
+        <v>90</v>
+      </c>
+      <c r="D306">
+        <v>58</v>
+      </c>
+      <c r="E306">
+        <v>65</v>
+      </c>
+      <c r="F306">
+        <v>48</v>
+      </c>
+      <c r="G306">
+        <v>67</v>
+      </c>
+      <c r="H306">
+        <v>52</v>
+      </c>
+      <c r="I306">
+        <v>96</v>
+      </c>
+      <c r="J306">
+        <v>55</v>
+      </c>
+      <c r="K306">
+        <v>81</v>
+      </c>
+      <c r="L306">
+        <v>55</v>
+      </c>
+      <c r="M306">
+        <v>65</v>
+      </c>
+      <c r="N306">
+        <v>58</v>
+      </c>
+      <c r="O306" s="19">
+        <f t="shared" si="63"/>
+        <v>67</v>
+      </c>
+      <c r="P306" s="19">
+        <f t="shared" si="64"/>
+        <v>16.010000000000002</v>
+      </c>
+      <c r="T306">
+        <v>95</v>
+      </c>
+      <c r="U306">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="307" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B307" s="21">
+        <v>46132</v>
+      </c>
+      <c r="C307">
+        <v>51</v>
+      </c>
+      <c r="D307">
+        <v>45</v>
+      </c>
+      <c r="E307">
+        <v>52</v>
+      </c>
+      <c r="F307">
+        <v>41</v>
+      </c>
+      <c r="G307">
+        <v>52</v>
+      </c>
+      <c r="H307">
+        <v>39</v>
+      </c>
+      <c r="I307">
+        <v>53</v>
+      </c>
+      <c r="J307">
+        <v>42</v>
+      </c>
+      <c r="K307">
+        <v>47</v>
+      </c>
+      <c r="L307">
+        <v>48</v>
+      </c>
+      <c r="M307">
+        <v>50</v>
+      </c>
+      <c r="N307">
+        <v>46</v>
+      </c>
+      <c r="O307" s="19">
+        <f t="shared" si="63"/>
+        <v>48</v>
+      </c>
+      <c r="P307" s="19">
+        <f t="shared" si="64"/>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="T307">
+        <v>54</v>
+      </c>
+      <c r="U307">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="308" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B308" s="21">
+        <v>46133</v>
+      </c>
+      <c r="C308">
+        <v>54</v>
+      </c>
+      <c r="D308">
+        <v>42</v>
+      </c>
+      <c r="E308">
+        <v>63</v>
+      </c>
+      <c r="F308">
+        <v>41</v>
+      </c>
+      <c r="G308">
+        <v>45</v>
+      </c>
+      <c r="H308">
+        <v>38</v>
+      </c>
+      <c r="I308">
+        <v>67</v>
+      </c>
+      <c r="J308">
+        <v>49</v>
+      </c>
+      <c r="K308">
+        <v>46</v>
+      </c>
+      <c r="L308">
+        <v>51</v>
+      </c>
+      <c r="M308">
+        <v>50</v>
+      </c>
+      <c r="N308">
+        <v>43</v>
+      </c>
+      <c r="O308" s="19">
+        <f t="shared" si="63"/>
+        <v>50</v>
+      </c>
+      <c r="P308" s="19">
+        <f t="shared" si="64"/>
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="T308">
+        <v>71</v>
+      </c>
+      <c r="U308">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="309" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B309" s="21">
+        <v>46134</v>
+      </c>
+      <c r="C309">
+        <v>51</v>
+      </c>
+      <c r="D309">
         <v>40</v>
       </c>
-      <c r="C305">
-        <v>29.34</v>
-      </c>
-      <c r="D305">
-        <v>30.21</v>
-      </c>
-      <c r="E305">
-        <v>24.61</v>
-      </c>
-      <c r="F305" s="14">
-        <v>27.28</v>
-      </c>
-      <c r="G305" s="14">
-        <v>22.28</v>
-      </c>
-      <c r="H305" s="14">
-        <v>23.15</v>
-      </c>
-      <c r="I305" s="14">
-        <v>28.87</v>
-      </c>
-      <c r="J305" s="14">
-        <v>28.82</v>
-      </c>
-      <c r="K305" s="14">
-        <v>26.2</v>
-      </c>
-      <c r="L305" s="14">
-        <v>28.06</v>
-      </c>
-      <c r="M305" s="14">
-        <v>28.45</v>
-      </c>
-      <c r="N305" s="15">
-        <v>30.56</v>
-      </c>
-      <c r="O305" s="31">
-        <f>ROUND(AVERAGE(C305:N305,T305:U305),2)</f>
-        <v>27.05</v>
-      </c>
-      <c r="P305" s="31">
-        <f>ROUND(_xlfn.STDEV.P(C305:N305,T305:U305),2)</f>
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="T305">
-        <v>24.56</v>
-      </c>
-      <c r="U305">
-        <v>26.35</v>
-      </c>
-    </row>
-    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B306" s="18" t="s">
+      <c r="E309">
+        <v>62</v>
+      </c>
+      <c r="F309">
+        <v>40</v>
+      </c>
+      <c r="G309">
+        <v>47</v>
+      </c>
+      <c r="H309">
         <v>41</v>
       </c>
-      <c r="C306">
-        <v>26.27</v>
-      </c>
-      <c r="D306">
-        <v>26.22</v>
-      </c>
-      <c r="E306">
-        <v>29.18</v>
-      </c>
-      <c r="F306">
-        <v>25.22</v>
-      </c>
-      <c r="G306">
-        <v>32.25</v>
-      </c>
-      <c r="H306">
-        <v>29.23</v>
-      </c>
-      <c r="I306">
-        <v>24.57</v>
-      </c>
-      <c r="J306">
-        <v>24.75</v>
-      </c>
-      <c r="K306">
-        <v>26.81</v>
-      </c>
-      <c r="L306">
-        <v>24.03</v>
-      </c>
-      <c r="M306" s="14">
-        <v>23.43</v>
-      </c>
-      <c r="N306" s="14">
-        <v>23.13</v>
-      </c>
-      <c r="O306" s="31">
-        <f>ROUND(AVERAGE(C306:N306,T306:U306),2)</f>
-        <v>26.4</v>
-      </c>
-      <c r="P306" s="31">
-        <f>ROUND(_xlfn.STDEV.P(C306:N306,T306:U306),2)</f>
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="T306">
-        <v>27.27</v>
-      </c>
-      <c r="U306">
-        <v>27.18</v>
-      </c>
-    </row>
-    <row r="307" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C307" s="53" t="s">
+      <c r="I309">
+        <v>47</v>
+      </c>
+      <c r="J309">
+        <v>41</v>
+      </c>
+      <c r="K309">
+        <v>48</v>
+      </c>
+      <c r="L309">
+        <v>45</v>
+      </c>
+      <c r="M309">
+        <v>54</v>
+      </c>
+      <c r="N309">
+        <v>42</v>
+      </c>
+      <c r="O309" s="19">
+        <f t="shared" si="63"/>
+        <v>48</v>
+      </c>
+      <c r="P309" s="19">
+        <f t="shared" si="64"/>
+        <v>7.33</v>
+      </c>
+      <c r="T309">
+        <v>63</v>
+      </c>
+      <c r="U309">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="310" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B310" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C310">
+        <v>25.68</v>
+      </c>
+      <c r="D310">
+        <v>26.69</v>
+      </c>
+      <c r="E310">
+        <v>23.75</v>
+      </c>
+      <c r="F310" s="14">
+        <v>29.73</v>
+      </c>
+      <c r="G310" s="14">
+        <v>25.9</v>
+      </c>
+      <c r="H310" s="14">
+        <v>24.32</v>
+      </c>
+      <c r="I310" s="14">
+        <v>25.82</v>
+      </c>
+      <c r="J310" s="14">
+        <v>24.87</v>
+      </c>
+      <c r="K310" s="14">
+        <v>23.95</v>
+      </c>
+      <c r="L310" s="14">
+        <v>25.93</v>
+      </c>
+      <c r="M310" s="14">
+        <v>27.46</v>
+      </c>
+      <c r="N310" s="15">
+        <v>27.42</v>
+      </c>
+      <c r="O310" s="31">
+        <f>ROUND(AVERAGE(C310:N310,T310:U310),2)</f>
+        <v>25.98</v>
+      </c>
+      <c r="P310" s="31">
+        <f>ROUND(_xlfn.STDEV.P(C310:N310,T310:U310),2)</f>
+        <v>1.52</v>
+      </c>
+      <c r="T310">
+        <v>25.62</v>
+      </c>
+      <c r="U310">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="311" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B311" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C311">
+        <v>25.58</v>
+      </c>
+      <c r="D311">
+        <v>23.74</v>
+      </c>
+      <c r="E311">
+        <v>27.29</v>
+      </c>
+      <c r="F311">
+        <v>25.5</v>
+      </c>
+      <c r="G311">
+        <v>30.35</v>
+      </c>
+      <c r="H311">
+        <v>29.21</v>
+      </c>
+      <c r="I311">
+        <v>29.25</v>
+      </c>
+      <c r="J311">
+        <v>31.56</v>
+      </c>
+      <c r="K311">
+        <v>27.86</v>
+      </c>
+      <c r="L311">
+        <v>27.65</v>
+      </c>
+      <c r="M311" s="14">
+        <v>26.92</v>
+      </c>
+      <c r="N311" s="14">
+        <v>26.33</v>
+      </c>
+      <c r="O311" s="31">
+        <f>ROUND(AVERAGE(C311:N311,T311:U311),2)</f>
+        <v>27.48</v>
+      </c>
+      <c r="P311" s="31">
+        <f>ROUND(_xlfn.STDEV.P(C311:N311,T311:U311),2)</f>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="T311">
+        <v>27.82</v>
+      </c>
+      <c r="U311">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="312" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C312" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="D307" s="53"/>
-      <c r="E307" s="53" t="s">
+      <c r="D312" s="53"/>
+      <c r="E312" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="F307" s="53"/>
-      <c r="G307" s="53" t="s">
+      <c r="F312" s="53"/>
+      <c r="G312" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="H307" s="53"/>
-      <c r="I307" s="53" t="s">
+      <c r="H312" s="53"/>
+      <c r="I312" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="J307" s="53"/>
-      <c r="K307" s="58" t="s">
+      <c r="J312" s="53"/>
+      <c r="K312" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="L307" s="58"/>
-      <c r="M307" s="58" t="s">
+      <c r="L312" s="58"/>
+      <c r="M312" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="N307" s="58"/>
-      <c r="T307" s="53" t="s">
+      <c r="N312" s="58"/>
+      <c r="T312" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="U307" s="53"/>
-    </row>
-    <row r="308" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C308" t="s">
+      <c r="U312" s="53"/>
+    </row>
+    <row r="313" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C313" t="s">
         <v>63</v>
       </c>
-      <c r="D308" t="s">
+      <c r="D313" t="s">
         <v>64</v>
       </c>
-      <c r="E308" t="s">
+      <c r="E313" t="s">
         <v>63</v>
       </c>
-      <c r="F308" t="s">
+      <c r="F313" t="s">
         <v>64</v>
       </c>
-      <c r="G308" t="s">
+      <c r="G313" t="s">
         <v>63</v>
       </c>
-      <c r="H308" t="s">
+      <c r="H313" t="s">
         <v>64</v>
       </c>
-      <c r="I308" t="s">
+      <c r="I313" t="s">
         <v>63</v>
       </c>
-      <c r="J308" t="s">
+      <c r="J313" t="s">
         <v>64</v>
       </c>
-      <c r="K308" t="s">
+      <c r="K313" t="s">
         <v>63</v>
       </c>
-      <c r="L308" t="s">
+      <c r="L313" t="s">
         <v>64</v>
       </c>
-      <c r="M308" t="s">
+      <c r="M313" t="s">
         <v>63</v>
       </c>
-      <c r="N308" t="s">
+      <c r="N313" t="s">
         <v>64</v>
       </c>
-      <c r="T308" t="s">
+      <c r="T313" t="s">
         <v>63</v>
       </c>
-      <c r="U308" t="s">
+      <c r="U313" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B309" t="s">
+    <row r="314" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
         <v>65</v>
       </c>
-      <c r="C309">
-        <v>72.426000000000002</v>
-      </c>
-      <c r="D309">
-        <v>76.203999999999994</v>
-      </c>
-      <c r="E309">
-        <v>106.777</v>
-      </c>
-      <c r="F309">
-        <v>95.346999999999994</v>
-      </c>
-      <c r="G309">
-        <v>26.42</v>
-      </c>
-      <c r="H309">
-        <v>15.21</v>
-      </c>
-      <c r="I309">
-        <v>110.955</v>
-      </c>
-      <c r="J309">
-        <v>125.211</v>
-      </c>
-      <c r="K309">
-        <v>86.977999999999994</v>
-      </c>
-      <c r="L309">
-        <v>104.254</v>
-      </c>
-      <c r="M309">
-        <v>196.98699999999999</v>
-      </c>
-      <c r="N309">
-        <v>175.36099999999999</v>
-      </c>
-      <c r="T309">
-        <v>212.42099999999999</v>
-      </c>
-      <c r="U309">
-        <v>218.84200000000001</v>
-      </c>
-    </row>
-    <row r="310" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B310" t="s">
+      <c r="C314">
+        <v>73.944000000000003</v>
+      </c>
+      <c r="D314">
+        <v>81.881</v>
+      </c>
+      <c r="E314">
+        <v>97.981999999999999</v>
+      </c>
+      <c r="F314">
+        <v>100.489</v>
+      </c>
+      <c r="G314">
+        <v>25.925000000000001</v>
+      </c>
+      <c r="H314">
+        <v>12.782999999999999</v>
+      </c>
+      <c r="I314">
+        <v>114.309</v>
+      </c>
+      <c r="J314">
+        <v>127.94</v>
+      </c>
+      <c r="K314">
+        <v>113.486</v>
+      </c>
+      <c r="L314">
+        <v>113.773</v>
+      </c>
+      <c r="M314">
+        <v>170.458</v>
+      </c>
+      <c r="N314">
+        <v>195.36600000000001</v>
+      </c>
+      <c r="T314">
+        <v>209.27199999999999</v>
+      </c>
+      <c r="U314">
+        <v>207.24799999999999</v>
+      </c>
+    </row>
+    <row r="315" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
         <v>67</v>
       </c>
-      <c r="C310" s="32"/>
-      <c r="D310" s="32"/>
-      <c r="E310" s="32"/>
-      <c r="F310" s="32"/>
-      <c r="G310" s="32"/>
-      <c r="H310" s="32"/>
-      <c r="I310" s="52">
-        <v>0.70440000000000003</v>
-      </c>
-      <c r="J310" s="52">
-        <v>0.73480000000000001</v>
-      </c>
-      <c r="K310" s="52">
-        <v>0.69479999999999997</v>
-      </c>
-      <c r="L310" s="52">
-        <v>0.86460000000000004</v>
-      </c>
-      <c r="M310" s="52">
-        <v>0.72099999999999997</v>
-      </c>
-      <c r="N310" s="52">
-        <v>0.68920000000000003</v>
-      </c>
-      <c r="T310" s="52">
-        <v>0.8135</v>
-      </c>
-      <c r="U310" s="52">
-        <v>0.83289999999999997</v>
+      <c r="C315" s="32"/>
+      <c r="D315" s="32"/>
+      <c r="E315" s="32"/>
+      <c r="F315" s="32"/>
+      <c r="G315" s="32"/>
+      <c r="H315" s="32"/>
+      <c r="I315" s="52">
+        <v>0.74329999999999996</v>
+      </c>
+      <c r="J315" s="52">
+        <v>0.75939999999999996</v>
+      </c>
+      <c r="K315" s="52">
+        <v>0.74460000000000004</v>
+      </c>
+      <c r="L315">
+        <v>81.180000000000007</v>
+      </c>
+      <c r="M315" s="52">
+        <v>0.79969999999999997</v>
+      </c>
+      <c r="N315" s="52">
+        <v>0.7097</v>
+      </c>
+      <c r="T315" s="52">
+        <v>0.7016</v>
+      </c>
+      <c r="U315" s="52">
+        <v>0.84809999999999997</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="T307:U307"/>
+    <mergeCell ref="T312:U312"/>
     <mergeCell ref="C1:N1"/>
     <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C307:D307"/>
-    <mergeCell ref="I307:J307"/>
-    <mergeCell ref="G307:H307"/>
-    <mergeCell ref="E307:F307"/>
-    <mergeCell ref="K307:L307"/>
-    <mergeCell ref="M307:N307"/>
+    <mergeCell ref="C312:D312"/>
+    <mergeCell ref="I312:J312"/>
+    <mergeCell ref="G312:H312"/>
+    <mergeCell ref="E312:F312"/>
+    <mergeCell ref="K312:L312"/>
+    <mergeCell ref="M312:N312"/>
   </mergeCells>
   <conditionalFormatting sqref="C98:N271 T142:U271">
-    <cfRule type="expression" dxfId="25" priority="3">
-      <formula>ABS(C98-$A98)&lt;=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="11">
-      <formula>ABS(C98-$A98)&lt;=15</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C310:N310 T310:U310">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="lessThan">
+      <formula>$O$310-$P$310</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C305:N305 T305:U305">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="lessThan">
-      <formula>$O$305-$P$305</formula>
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+      <formula>$O$310+$P$310</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
-      <formula>$O$305+$P$305</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="30" operator="between">
-      <formula>$O$305-$P$305</formula>
+    <cfRule type="cellIs" dxfId="12" priority="30" operator="between">
+      <formula>$O$310-$P$310</formula>
       <formula>"$O$264+$P$264"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C306:N306 T306:U306">
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="C311:N311 T311:U311">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThan">
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R79 R81:R271">
+  <conditionalFormatting sqref="R3:R79 R81:R291">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -39966,6 +40452,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C98:N291 T142:U291">
+    <cfRule type="expression" dxfId="10" priority="3">
+      <formula>ABS(C98-$A98)&lt;=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>ABS(C98-$A98)&lt;=15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -39973,7 +40467,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9BE2AF-C5F8-4B32-A88A-8E9C9CBC1046}">
-  <dimension ref="A1:W306"/>
+  <dimension ref="A1:W311"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -55778,6 +56272,9 @@
       </c>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A272" s="13">
+        <v>12</v>
+      </c>
       <c r="B272" s="21">
         <v>46097</v>
       </c>
@@ -55825,6 +56322,14 @@
         <f t="shared" si="44"/>
         <v>7.25</v>
       </c>
+      <c r="R272" s="25">
+        <f t="shared" ref="R272:R291" si="45">O272-A272</f>
+        <v>32</v>
+      </c>
+      <c r="S272">
+        <f t="shared" ref="S272:S291" si="46">O272/A272</f>
+        <v>3.6666666666666665</v>
+      </c>
       <c r="T272">
         <v>43</v>
       </c>
@@ -55832,7 +56337,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="273" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A273" s="13">
+        <v>0</v>
+      </c>
       <c r="B273" s="21">
         <v>46098</v>
       </c>
@@ -55880,6 +56388,14 @@
         <f t="shared" si="44"/>
         <v>7.75</v>
       </c>
+      <c r="R273" s="25">
+        <f t="shared" si="45"/>
+        <v>36</v>
+      </c>
+      <c r="S273" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T273">
         <v>43</v>
       </c>
@@ -55887,7 +56403,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="274" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A274" s="13">
+        <v>46</v>
+      </c>
       <c r="B274" s="21">
         <v>46099</v>
       </c>
@@ -55935,6 +56454,14 @@
         <f t="shared" si="44"/>
         <v>3.94</v>
       </c>
+      <c r="R274" s="25">
+        <f t="shared" si="45"/>
+        <v>-3</v>
+      </c>
+      <c r="S274">
+        <f t="shared" si="46"/>
+        <v>0.93478260869565222</v>
+      </c>
       <c r="T274">
         <v>41</v>
       </c>
@@ -55942,7 +56469,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="275" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A275" s="13">
+        <v>58</v>
+      </c>
       <c r="B275" s="21">
         <v>46100</v>
       </c>
@@ -55990,6 +56520,14 @@
         <f t="shared" si="44"/>
         <v>7.34</v>
       </c>
+      <c r="R275" s="25">
+        <f t="shared" si="45"/>
+        <v>-5</v>
+      </c>
+      <c r="S275">
+        <f t="shared" si="46"/>
+        <v>0.91379310344827591</v>
+      </c>
       <c r="T275">
         <v>59</v>
       </c>
@@ -55997,7 +56535,10 @@
         <v>51</v>
       </c>
     </row>
-    <row r="276" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A276" s="13">
+        <v>84</v>
+      </c>
       <c r="B276" s="21">
         <v>46101</v>
       </c>
@@ -56045,6 +56586,14 @@
         <f t="shared" si="44"/>
         <v>17.25</v>
       </c>
+      <c r="R276" s="25">
+        <f t="shared" si="45"/>
+        <v>24</v>
+      </c>
+      <c r="S276">
+        <f t="shared" si="46"/>
+        <v>1.2857142857142858</v>
+      </c>
       <c r="T276">
         <v>126</v>
       </c>
@@ -56052,7 +56601,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="277" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A277" s="13">
+        <v>156</v>
+      </c>
       <c r="B277" s="21">
         <v>46102</v>
       </c>
@@ -56100,6 +56652,14 @@
         <f t="shared" si="44"/>
         <v>14.21</v>
       </c>
+      <c r="R277" s="25">
+        <f t="shared" si="45"/>
+        <v>-31</v>
+      </c>
+      <c r="S277">
+        <f t="shared" si="46"/>
+        <v>0.80128205128205132</v>
+      </c>
       <c r="T277">
         <v>114</v>
       </c>
@@ -56107,7 +56667,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="278" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A278" s="13">
+        <v>45</v>
+      </c>
       <c r="B278" s="21">
         <v>46103</v>
       </c>
@@ -56155,6 +56718,14 @@
         <f t="shared" si="44"/>
         <v>8.48</v>
       </c>
+      <c r="R278" s="25">
+        <f t="shared" si="45"/>
+        <v>-2</v>
+      </c>
+      <c r="S278">
+        <f t="shared" si="46"/>
+        <v>0.9555555555555556</v>
+      </c>
       <c r="T278">
         <v>50</v>
       </c>
@@ -56162,7 +56733,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A279" s="13">
+        <v>18</v>
+      </c>
       <c r="B279" s="21">
         <v>46104</v>
       </c>
@@ -56210,6 +56784,14 @@
         <f t="shared" si="44"/>
         <v>10.73</v>
       </c>
+      <c r="R279" s="25">
+        <f t="shared" si="45"/>
+        <v>27</v>
+      </c>
+      <c r="S279">
+        <f t="shared" si="46"/>
+        <v>2.5</v>
+      </c>
       <c r="T279">
         <v>50</v>
       </c>
@@ -56217,7 +56799,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="280" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A280" s="13">
+        <v>37</v>
+      </c>
       <c r="B280" s="21">
         <v>46105</v>
       </c>
@@ -56265,6 +56850,14 @@
         <f t="shared" si="44"/>
         <v>11.07</v>
       </c>
+      <c r="R280" s="25">
+        <f t="shared" si="45"/>
+        <v>2</v>
+      </c>
+      <c r="S280">
+        <f t="shared" si="46"/>
+        <v>1.0540540540540539</v>
+      </c>
       <c r="T280">
         <v>57</v>
       </c>
@@ -56272,7 +56865,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="281" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A281" s="13">
+        <v>38</v>
+      </c>
       <c r="B281" s="21">
         <v>46106</v>
       </c>
@@ -56320,6 +56916,14 @@
         <f t="shared" si="44"/>
         <v>11.45</v>
       </c>
+      <c r="R281" s="25">
+        <f t="shared" si="45"/>
+        <v>2</v>
+      </c>
+      <c r="S281">
+        <f t="shared" si="46"/>
+        <v>1.0526315789473684</v>
+      </c>
       <c r="T281">
         <v>55</v>
       </c>
@@ -56327,7 +56931,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A282" s="13">
+        <v>119</v>
+      </c>
       <c r="B282" s="21">
         <v>46107</v>
       </c>
@@ -56375,6 +56982,14 @@
         <f t="shared" si="44"/>
         <v>9.19</v>
       </c>
+      <c r="R282" s="25">
+        <f t="shared" si="45"/>
+        <v>-73</v>
+      </c>
+      <c r="S282">
+        <f t="shared" si="46"/>
+        <v>0.38655462184873951</v>
+      </c>
       <c r="T282">
         <v>59</v>
       </c>
@@ -56382,7 +56997,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="283" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A283" s="13">
+        <v>109</v>
+      </c>
       <c r="B283" s="21">
         <v>46108</v>
       </c>
@@ -56430,6 +57048,14 @@
         <f t="shared" si="44"/>
         <v>12.62</v>
       </c>
+      <c r="R283" s="25">
+        <f t="shared" si="45"/>
+        <v>-22</v>
+      </c>
+      <c r="S283">
+        <f t="shared" si="46"/>
+        <v>0.79816513761467889</v>
+      </c>
       <c r="T283">
         <v>88</v>
       </c>
@@ -56437,7 +57063,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="284" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A284" s="13">
+        <v>148</v>
+      </c>
       <c r="B284" s="21">
         <v>46109</v>
       </c>
@@ -56485,6 +57114,14 @@
         <f t="shared" si="44"/>
         <v>15.99</v>
       </c>
+      <c r="R284" s="25">
+        <f t="shared" si="45"/>
+        <v>-26</v>
+      </c>
+      <c r="S284">
+        <f t="shared" si="46"/>
+        <v>0.82432432432432434</v>
+      </c>
       <c r="T284">
         <v>127</v>
       </c>
@@ -56492,7 +57129,10 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A285" s="13">
+        <v>31</v>
+      </c>
       <c r="B285" s="21">
         <v>46110</v>
       </c>
@@ -56540,6 +57180,14 @@
         <f t="shared" si="44"/>
         <v>13.68</v>
       </c>
+      <c r="R285" s="25">
+        <f t="shared" si="45"/>
+        <v>15</v>
+      </c>
+      <c r="S285">
+        <f t="shared" si="46"/>
+        <v>1.4838709677419355</v>
+      </c>
       <c r="T285">
         <v>61</v>
       </c>
@@ -56547,7 +57195,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="286" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A286" s="13">
+        <v>20</v>
+      </c>
       <c r="B286" s="21">
         <v>46111</v>
       </c>
@@ -56595,6 +57246,14 @@
         <f t="shared" si="44"/>
         <v>6.06</v>
       </c>
+      <c r="R286" s="25">
+        <f t="shared" si="45"/>
+        <v>23</v>
+      </c>
+      <c r="S286">
+        <f t="shared" si="46"/>
+        <v>2.15</v>
+      </c>
       <c r="T286">
         <v>43</v>
       </c>
@@ -56602,7 +57261,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="287" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A287" s="13">
+        <v>33</v>
+      </c>
       <c r="B287" s="21">
         <v>46112</v>
       </c>
@@ -56650,6 +57312,14 @@
         <f t="shared" si="44"/>
         <v>11.32</v>
       </c>
+      <c r="R287" s="25">
+        <f t="shared" si="45"/>
+        <v>11</v>
+      </c>
+      <c r="S287">
+        <f t="shared" si="46"/>
+        <v>1.3333333333333333</v>
+      </c>
       <c r="T287">
         <v>49</v>
       </c>
@@ -56657,7 +57327,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="288" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A288" s="13">
+        <v>35</v>
+      </c>
       <c r="B288" s="21">
         <v>46113</v>
       </c>
@@ -56705,6 +57378,14 @@
         <f t="shared" si="44"/>
         <v>7.58</v>
       </c>
+      <c r="R288" s="25">
+        <f t="shared" si="45"/>
+        <v>15</v>
+      </c>
+      <c r="S288">
+        <f t="shared" si="46"/>
+        <v>1.4285714285714286</v>
+      </c>
       <c r="T288">
         <v>52</v>
       </c>
@@ -56712,7 +57393,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="289" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A289" s="13">
+        <v>20</v>
+      </c>
       <c r="B289" s="21">
         <v>46114</v>
       </c>
@@ -56760,6 +57444,14 @@
         <f t="shared" si="44"/>
         <v>17.899999999999999</v>
       </c>
+      <c r="R289" s="25">
+        <f t="shared" si="45"/>
+        <v>55</v>
+      </c>
+      <c r="S289">
+        <f t="shared" si="46"/>
+        <v>3.75</v>
+      </c>
       <c r="T289">
         <v>85</v>
       </c>
@@ -56767,7 +57459,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="290" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A290" s="13">
+        <v>62</v>
+      </c>
       <c r="B290" s="21">
         <v>46115</v>
       </c>
@@ -56808,12 +57503,20 @@
         <v>66</v>
       </c>
       <c r="O290" s="19">
-        <f t="shared" ref="O290:O304" si="45">ROUND(AVERAGE(C290:N290,T290,U290),0)</f>
+        <f t="shared" ref="O290:O304" si="47">ROUND(AVERAGE(C290:N290,T290,U290),0)</f>
         <v>70</v>
       </c>
       <c r="P290" s="19">
-        <f t="shared" ref="P290:P304" si="46">ROUND(_xlfn.STDEV.P(C290:N290,T290,U290),2)</f>
+        <f t="shared" ref="P290:P304" si="48">ROUND(_xlfn.STDEV.P(C290:N290,T290,U290),2)</f>
         <v>16.829999999999998</v>
+      </c>
+      <c r="R290" s="25">
+        <f t="shared" si="45"/>
+        <v>8</v>
+      </c>
+      <c r="S290">
+        <f t="shared" si="46"/>
+        <v>1.1290322580645162</v>
       </c>
       <c r="T290">
         <v>69</v>
@@ -56822,7 +57525,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="291" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A291" s="13">
+        <v>75</v>
+      </c>
       <c r="B291" s="21">
         <v>46116</v>
       </c>
@@ -56863,12 +57569,20 @@
         <v>110</v>
       </c>
       <c r="O291" s="19">
+        <f t="shared" si="47"/>
+        <v>99</v>
+      </c>
+      <c r="P291" s="19">
+        <f t="shared" si="48"/>
+        <v>11.21</v>
+      </c>
+      <c r="R291" s="25">
         <f t="shared" si="45"/>
-        <v>99</v>
-      </c>
-      <c r="P291" s="19">
+        <v>24</v>
+      </c>
+      <c r="S291">
         <f t="shared" si="46"/>
-        <v>11.21</v>
+        <v>1.32</v>
       </c>
       <c r="T291">
         <v>78</v>
@@ -56877,822 +57591,1062 @@
         <v>100</v>
       </c>
     </row>
-    <row r="292" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B292" s="21">
         <v>46117</v>
       </c>
       <c r="C292">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D292">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E292">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F292">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G292">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H292">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I292">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J292">
         <v>18</v>
       </c>
       <c r="K292">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="L292">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M292">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N292">
+        <v>30</v>
+      </c>
+      <c r="O292" s="19">
+        <f t="shared" si="47"/>
         <v>32</v>
       </c>
-      <c r="O292" s="19">
-        <f t="shared" si="45"/>
-        <v>32</v>
-      </c>
       <c r="P292" s="19">
-        <f t="shared" si="46"/>
-        <v>10.58</v>
+        <f t="shared" si="48"/>
+        <v>9.82</v>
       </c>
       <c r="T292">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="U292">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="293" spans="2:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B293" s="21">
         <v>46118</v>
       </c>
       <c r="C293">
+        <v>53</v>
+      </c>
+      <c r="D293">
+        <v>41</v>
+      </c>
+      <c r="E293">
+        <v>57</v>
+      </c>
+      <c r="F293">
+        <v>32</v>
+      </c>
+      <c r="G293">
         <v>46</v>
       </c>
-      <c r="D293">
+      <c r="H293">
+        <v>25</v>
+      </c>
+      <c r="I293">
+        <v>49</v>
+      </c>
+      <c r="J293">
+        <v>35</v>
+      </c>
+      <c r="K293">
+        <v>50</v>
+      </c>
+      <c r="L293">
+        <v>43</v>
+      </c>
+      <c r="M293">
+        <v>49</v>
+      </c>
+      <c r="N293">
+        <v>43</v>
+      </c>
+      <c r="O293" s="19">
+        <f t="shared" si="47"/>
         <v>44</v>
       </c>
-      <c r="E293">
+      <c r="P293" s="19">
+        <f t="shared" si="48"/>
+        <v>8.48</v>
+      </c>
+      <c r="T293">
         <v>50</v>
       </c>
-      <c r="F293">
+      <c r="U293">
         <v>38</v>
       </c>
-      <c r="G293">
-        <v>41</v>
-      </c>
-      <c r="H293">
-        <v>30</v>
-      </c>
-      <c r="I293">
-        <v>41</v>
-      </c>
-      <c r="J293">
-        <v>33</v>
-      </c>
-      <c r="K293">
-        <v>47</v>
-      </c>
-      <c r="L293">
-        <v>45</v>
-      </c>
-      <c r="M293">
-        <v>44</v>
-      </c>
-      <c r="N293">
-        <v>44</v>
-      </c>
-      <c r="O293" s="19">
-        <f t="shared" si="45"/>
-        <v>41</v>
-      </c>
-      <c r="P293" s="19">
-        <f t="shared" si="46"/>
-        <v>5.52</v>
-      </c>
-      <c r="T293">
-        <v>41</v>
-      </c>
-      <c r="U293">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="294" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B294" s="21">
         <v>46119</v>
       </c>
       <c r="C294">
+        <v>72</v>
+      </c>
+      <c r="D294">
+        <v>46</v>
+      </c>
+      <c r="E294">
+        <v>59</v>
+      </c>
+      <c r="F294">
+        <v>37</v>
+      </c>
+      <c r="G294">
+        <v>46</v>
+      </c>
+      <c r="H294">
+        <v>22</v>
+      </c>
+      <c r="I294">
+        <v>53</v>
+      </c>
+      <c r="J294">
+        <v>30</v>
+      </c>
+      <c r="K294">
+        <v>77</v>
+      </c>
+      <c r="L294">
         <v>49</v>
       </c>
-      <c r="D294">
+      <c r="M294">
+        <v>80</v>
+      </c>
+      <c r="N294">
         <v>45</v>
       </c>
-      <c r="E294">
-        <v>60</v>
-      </c>
-      <c r="F294">
-        <v>34</v>
-      </c>
-      <c r="G294">
-        <v>42</v>
-      </c>
-      <c r="H294">
-        <v>21</v>
-      </c>
-      <c r="I294">
-        <v>43</v>
-      </c>
-      <c r="J294">
-        <v>27</v>
-      </c>
-      <c r="K294">
-        <v>47</v>
-      </c>
-      <c r="L294">
-        <v>48</v>
-      </c>
-      <c r="M294">
-        <v>64</v>
-      </c>
-      <c r="N294">
-        <v>46</v>
-      </c>
       <c r="O294" s="19">
-        <f t="shared" si="45"/>
-        <v>44</v>
+        <f t="shared" si="47"/>
+        <v>50</v>
       </c>
       <c r="P294" s="19">
-        <f t="shared" si="46"/>
-        <v>11.24</v>
+        <f t="shared" si="48"/>
+        <v>16.329999999999998</v>
       </c>
       <c r="T294">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U294">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="295" spans="2:21" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B295" s="21">
         <v>46120</v>
       </c>
       <c r="C295">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D295">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E295">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F295">
         <v>44</v>
       </c>
       <c r="G295">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H295">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I295">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J295">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K295">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L295">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M295">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="N295">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="O295" s="19">
-        <f t="shared" si="45"/>
-        <v>58</v>
+        <f t="shared" si="47"/>
+        <v>55</v>
       </c>
       <c r="P295" s="19">
-        <f t="shared" si="46"/>
-        <v>17.989999999999998</v>
+        <f t="shared" si="48"/>
+        <v>13.32</v>
       </c>
       <c r="T295">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="U295">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="296" spans="2:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B296" s="21">
         <v>46121</v>
       </c>
       <c r="C296">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D296">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="E296">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="F296">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G296">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H296">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I296">
+        <v>70</v>
+      </c>
+      <c r="J296">
         <v>63</v>
       </c>
-      <c r="J296">
-        <v>56</v>
-      </c>
       <c r="K296">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L296">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="M296">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="N296">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="O296" s="19">
-        <f t="shared" si="45"/>
-        <v>56</v>
+        <f t="shared" si="47"/>
+        <v>78</v>
       </c>
       <c r="P296" s="19">
-        <f t="shared" si="46"/>
-        <v>7.58</v>
+        <f t="shared" si="48"/>
+        <v>16.329999999999998</v>
       </c>
       <c r="T296">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="U296">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="297" spans="2:21" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B297" s="21">
         <v>46122</v>
       </c>
       <c r="C297">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="D297">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E297">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F297">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="G297">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H297">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="I297">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J297">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="K297">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="L297">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="M297">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="N297">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="O297" s="19">
-        <f t="shared" si="45"/>
-        <v>73</v>
+        <f t="shared" si="47"/>
+        <v>110</v>
       </c>
       <c r="P297" s="19">
-        <f t="shared" si="46"/>
-        <v>8.07</v>
+        <f t="shared" si="48"/>
+        <v>22.54</v>
       </c>
       <c r="T297">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="U297">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="298" spans="2:21" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B298" s="21">
         <v>46123</v>
       </c>
       <c r="C298">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="D298">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E298">
+        <v>118</v>
+      </c>
+      <c r="F298">
         <v>136</v>
       </c>
-      <c r="F298">
-        <v>134</v>
-      </c>
       <c r="G298">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="H298">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="I298">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="J298">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="K298">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L298">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="M298">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="N298">
+        <v>121</v>
+      </c>
+      <c r="O298" s="19">
+        <f t="shared" si="47"/>
         <v>135</v>
       </c>
-      <c r="O298" s="19">
-        <f t="shared" si="45"/>
-        <v>131</v>
-      </c>
       <c r="P298" s="19">
-        <f t="shared" si="46"/>
-        <v>21.66</v>
+        <f t="shared" si="48"/>
+        <v>12.89</v>
       </c>
       <c r="T298">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="U298">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="299" spans="2:21" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B299" s="21">
         <v>46124</v>
       </c>
       <c r="C299">
+        <v>65</v>
+      </c>
+      <c r="D299">
+        <v>68</v>
+      </c>
+      <c r="E299">
+        <v>63</v>
+      </c>
+      <c r="F299">
+        <v>47</v>
+      </c>
+      <c r="G299">
+        <v>49</v>
+      </c>
+      <c r="H299">
+        <v>13</v>
+      </c>
+      <c r="I299">
+        <v>71</v>
+      </c>
+      <c r="J299">
+        <v>45</v>
+      </c>
+      <c r="K299">
+        <v>88</v>
+      </c>
+      <c r="L299">
+        <v>61</v>
+      </c>
+      <c r="M299">
+        <v>80</v>
+      </c>
+      <c r="N299">
+        <v>60</v>
+      </c>
+      <c r="O299" s="19">
+        <f t="shared" si="47"/>
+        <v>58</v>
+      </c>
+      <c r="P299" s="19">
+        <f t="shared" si="48"/>
+        <v>17.510000000000002</v>
+      </c>
+      <c r="T299">
+        <v>62</v>
+      </c>
+      <c r="U299">
         <v>46</v>
       </c>
-      <c r="D299">
-        <v>44</v>
-      </c>
-      <c r="E299">
-        <v>47</v>
-      </c>
-      <c r="F299">
-        <v>41</v>
-      </c>
-      <c r="G299">
-        <v>41</v>
-      </c>
-      <c r="H299">
-        <v>28</v>
-      </c>
-      <c r="I299">
-        <v>41</v>
-      </c>
-      <c r="J299">
-        <v>41</v>
-      </c>
-      <c r="K299">
-        <v>47</v>
-      </c>
-      <c r="L299">
-        <v>48</v>
-      </c>
-      <c r="M299">
-        <v>56</v>
-      </c>
-      <c r="N299">
-        <v>44</v>
-      </c>
-      <c r="O299" s="19">
-        <f t="shared" si="45"/>
-        <v>43</v>
-      </c>
-      <c r="P299" s="19">
-        <f t="shared" si="46"/>
-        <v>6.06</v>
-      </c>
-      <c r="T299">
-        <v>43</v>
-      </c>
-      <c r="U299">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="300" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B300" s="21">
         <v>46125</v>
       </c>
       <c r="C300">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D300">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E300">
+        <v>58</v>
+      </c>
+      <c r="F300">
+        <v>47</v>
+      </c>
+      <c r="G300">
+        <v>49</v>
+      </c>
+      <c r="H300">
+        <v>16</v>
+      </c>
+      <c r="I300">
+        <v>70</v>
+      </c>
+      <c r="J300">
         <v>50</v>
       </c>
-      <c r="F300">
-        <v>33</v>
-      </c>
-      <c r="G300">
-        <v>43</v>
-      </c>
-      <c r="H300">
-        <v>7</v>
-      </c>
-      <c r="I300">
+      <c r="K300">
+        <v>77</v>
+      </c>
+      <c r="L300">
+        <v>56</v>
+      </c>
+      <c r="M300">
+        <v>75</v>
+      </c>
+      <c r="N300">
+        <v>57</v>
+      </c>
+      <c r="O300" s="19">
+        <f t="shared" si="47"/>
+        <v>57</v>
+      </c>
+      <c r="P300" s="19">
+        <f t="shared" si="48"/>
+        <v>15.03</v>
+      </c>
+      <c r="T300">
+        <v>60</v>
+      </c>
+      <c r="U300">
         <v>47</v>
       </c>
-      <c r="J300">
-        <v>22</v>
-      </c>
-      <c r="K300">
-        <v>72</v>
-      </c>
-      <c r="L300">
-        <v>50</v>
-      </c>
-      <c r="M300">
-        <v>61</v>
-      </c>
-      <c r="N300">
-        <v>53</v>
-      </c>
-      <c r="O300" s="19">
-        <f t="shared" si="45"/>
-        <v>48</v>
-      </c>
-      <c r="P300" s="19">
-        <f t="shared" si="46"/>
-        <v>18.68</v>
-      </c>
-      <c r="T300">
-        <v>77</v>
-      </c>
-      <c r="U300">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="301" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B301" s="21">
         <v>46126</v>
       </c>
       <c r="C301">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D301">
         <v>45</v>
       </c>
       <c r="E301">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F301">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G301">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H301">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I301">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J301">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K301">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L301">
+        <v>46</v>
+      </c>
+      <c r="M301">
         <v>49</v>
       </c>
-      <c r="M301">
-        <v>74</v>
-      </c>
       <c r="N301">
+        <v>45</v>
+      </c>
+      <c r="O301" s="19">
+        <f t="shared" si="47"/>
         <v>44</v>
       </c>
-      <c r="O301" s="19">
-        <f t="shared" si="45"/>
-        <v>48</v>
-      </c>
       <c r="P301" s="19">
-        <f t="shared" si="46"/>
-        <v>16.86</v>
+        <f t="shared" si="48"/>
+        <v>8.18</v>
       </c>
       <c r="T301">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="U301">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="302" spans="2:21" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B302" s="21">
         <v>46127</v>
       </c>
       <c r="C302">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D302">
+        <v>45</v>
+      </c>
+      <c r="E302">
+        <v>63</v>
+      </c>
+      <c r="F302">
+        <v>47</v>
+      </c>
+      <c r="G302">
+        <v>47</v>
+      </c>
+      <c r="H302">
+        <v>41</v>
+      </c>
+      <c r="I302">
+        <v>51</v>
+      </c>
+      <c r="J302">
+        <v>38</v>
+      </c>
+      <c r="K302">
+        <v>51</v>
+      </c>
+      <c r="L302">
+        <v>48</v>
+      </c>
+      <c r="M302">
+        <v>57</v>
+      </c>
+      <c r="N302">
+        <v>45</v>
+      </c>
+      <c r="O302" s="19">
+        <f t="shared" si="47"/>
         <v>49</v>
       </c>
-      <c r="E302">
-        <v>58</v>
-      </c>
-      <c r="F302">
-        <v>36</v>
-      </c>
-      <c r="G302">
-        <v>45</v>
-      </c>
-      <c r="H302">
-        <v>15</v>
-      </c>
-      <c r="I302">
-        <v>49</v>
-      </c>
-      <c r="J302">
-        <v>30</v>
-      </c>
-      <c r="K302">
-        <v>54</v>
-      </c>
-      <c r="L302">
-        <v>53</v>
-      </c>
-      <c r="M302">
-        <v>60</v>
-      </c>
-      <c r="N302">
-        <v>48</v>
-      </c>
-      <c r="O302" s="19">
-        <f t="shared" si="45"/>
+      <c r="P302" s="19">
+        <f t="shared" si="48"/>
+        <v>5.99</v>
+      </c>
+      <c r="T302">
+        <v>50</v>
+      </c>
+      <c r="U302">
         <v>46</v>
       </c>
-      <c r="P302" s="19">
-        <f t="shared" si="46"/>
-        <v>12.35</v>
-      </c>
-      <c r="T302">
-        <v>52</v>
-      </c>
-      <c r="U302">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="303" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B303" s="21">
         <v>46128</v>
       </c>
       <c r="C303">
+        <v>55</v>
+      </c>
+      <c r="D303">
         <v>57</v>
       </c>
-      <c r="D303">
-        <v>48</v>
-      </c>
       <c r="E303">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F303">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G303">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H303">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I303">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J303">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K303">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="L303">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M303">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="N303">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O303" s="19">
-        <f t="shared" si="45"/>
-        <v>51</v>
+        <f t="shared" si="47"/>
+        <v>61</v>
       </c>
       <c r="P303" s="19">
-        <f t="shared" si="46"/>
-        <v>4.8099999999999996</v>
+        <f t="shared" si="48"/>
+        <v>7.04</v>
       </c>
       <c r="T303">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U303">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="304" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B304" s="21">
         <v>46129</v>
       </c>
       <c r="C304">
+        <v>123</v>
+      </c>
+      <c r="D304">
+        <v>119</v>
+      </c>
+      <c r="E304">
+        <v>103</v>
+      </c>
+      <c r="F304">
+        <v>113</v>
+      </c>
+      <c r="G304">
+        <v>109</v>
+      </c>
+      <c r="H304">
+        <v>116</v>
+      </c>
+      <c r="I304">
+        <v>92</v>
+      </c>
+      <c r="J304">
+        <v>111</v>
+      </c>
+      <c r="K304">
+        <v>124</v>
+      </c>
+      <c r="L304">
+        <v>111</v>
+      </c>
+      <c r="M304">
+        <v>130</v>
+      </c>
+      <c r="N304">
+        <v>106</v>
+      </c>
+      <c r="O304" s="19">
+        <f t="shared" si="47"/>
+        <v>114</v>
+      </c>
+      <c r="P304" s="19">
+        <f t="shared" si="48"/>
+        <v>10.41</v>
+      </c>
+      <c r="T304">
+        <v>132</v>
+      </c>
+      <c r="U304">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="305" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B305" s="21">
+        <v>46130</v>
+      </c>
+      <c r="C305">
+        <v>132</v>
+      </c>
+      <c r="D305">
+        <v>140</v>
+      </c>
+      <c r="E305">
+        <v>119</v>
+      </c>
+      <c r="F305">
+        <v>137</v>
+      </c>
+      <c r="G305">
+        <v>146</v>
+      </c>
+      <c r="H305">
+        <v>171</v>
+      </c>
+      <c r="I305">
+        <v>128</v>
+      </c>
+      <c r="J305">
+        <v>136</v>
+      </c>
+      <c r="K305">
+        <v>129</v>
+      </c>
+      <c r="L305">
+        <v>125</v>
+      </c>
+      <c r="M305">
+        <v>116</v>
+      </c>
+      <c r="N305">
+        <v>121</v>
+      </c>
+      <c r="O305" s="19">
+        <f t="shared" ref="O305:O309" si="49">ROUND(AVERAGE(C305:N305,T305,U305),0)</f>
+        <v>135</v>
+      </c>
+      <c r="P305" s="19">
+        <f t="shared" ref="P305:P309" si="50">ROUND(_xlfn.STDEV.P(C305:N305,T305,U305),2)</f>
+        <v>16.23</v>
+      </c>
+      <c r="T305">
+        <v>169</v>
+      </c>
+      <c r="U305">
         <v>126</v>
       </c>
-      <c r="D304">
-        <v>110</v>
-      </c>
-      <c r="E304">
-        <v>104</v>
-      </c>
-      <c r="F304">
-        <v>101</v>
-      </c>
-      <c r="G304">
-        <v>95</v>
-      </c>
-      <c r="H304">
-        <v>70</v>
-      </c>
-      <c r="I304">
-        <v>132</v>
-      </c>
-      <c r="J304">
+    </row>
+    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B306" s="21">
+        <v>46131</v>
+      </c>
+      <c r="C306">
         <v>94</v>
       </c>
-      <c r="K304">
-        <v>119</v>
-      </c>
-      <c r="L304">
-        <v>125</v>
-      </c>
-      <c r="M304">
-        <v>123</v>
-      </c>
-      <c r="N304">
-        <v>109</v>
-      </c>
-      <c r="O304" s="19">
-        <f t="shared" si="45"/>
-        <v>109</v>
-      </c>
-      <c r="P304" s="19">
-        <f t="shared" si="46"/>
-        <v>15.99</v>
-      </c>
-      <c r="T304">
-        <v>121</v>
-      </c>
-      <c r="U304">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="305" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B305" s="32"/>
-      <c r="C305" s="61" t="s">
+      <c r="D306">
+        <v>58</v>
+      </c>
+      <c r="E306">
+        <v>55</v>
+      </c>
+      <c r="F306">
+        <v>33</v>
+      </c>
+      <c r="G306">
+        <v>49</v>
+      </c>
+      <c r="H306">
+        <v>22</v>
+      </c>
+      <c r="I306">
+        <v>60</v>
+      </c>
+      <c r="J306">
+        <v>39</v>
+      </c>
+      <c r="K306">
+        <v>81</v>
+      </c>
+      <c r="L306">
+        <v>55</v>
+      </c>
+      <c r="M306">
+        <v>65</v>
+      </c>
+      <c r="N306">
+        <v>56</v>
+      </c>
+      <c r="O306" s="19">
+        <f t="shared" si="49"/>
+        <v>57</v>
+      </c>
+      <c r="P306" s="19">
+        <f t="shared" si="50"/>
+        <v>19.7</v>
+      </c>
+      <c r="T306">
+        <v>88</v>
+      </c>
+      <c r="U306">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="307" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B307" s="21">
+        <v>46132</v>
+      </c>
+      <c r="C307">
+        <v>52</v>
+      </c>
+      <c r="D307">
+        <v>46</v>
+      </c>
+      <c r="E307">
         <v>53</v>
       </c>
-      <c r="D305" s="62"/>
-      <c r="E305" s="62" t="s">
+      <c r="F307">
+        <v>34</v>
+      </c>
+      <c r="G307">
+        <v>47</v>
+      </c>
+      <c r="H307">
+        <v>13</v>
+      </c>
+      <c r="I307">
         <v>57</v>
       </c>
-      <c r="F305" s="62"/>
-      <c r="G305" s="62" t="s">
+      <c r="J307">
+        <v>32</v>
+      </c>
+      <c r="K307">
+        <v>47</v>
+      </c>
+      <c r="L307">
+        <v>49</v>
+      </c>
+      <c r="M307">
+        <v>49</v>
+      </c>
+      <c r="N307">
+        <v>45</v>
+      </c>
+      <c r="O307" s="19">
+        <f t="shared" si="49"/>
+        <v>44</v>
+      </c>
+      <c r="P307" s="19">
+        <f t="shared" si="50"/>
+        <v>10.93</v>
+      </c>
+      <c r="T307">
+        <v>52</v>
+      </c>
+      <c r="U307">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="308" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B308" s="21">
+        <v>46133</v>
+      </c>
+      <c r="C308">
+        <v>56</v>
+      </c>
+      <c r="D308">
+        <v>43</v>
+      </c>
+      <c r="E308">
+        <v>64</v>
+      </c>
+      <c r="F308">
+        <v>58</v>
+      </c>
+      <c r="G308">
+        <v>41</v>
+      </c>
+      <c r="H308">
+        <v>64</v>
+      </c>
+      <c r="I308">
+        <v>51</v>
+      </c>
+      <c r="J308">
+        <v>35</v>
+      </c>
+      <c r="K308">
+        <v>47</v>
+      </c>
+      <c r="L308">
+        <v>51</v>
+      </c>
+      <c r="M308">
+        <v>44</v>
+      </c>
+      <c r="N308">
+        <v>46</v>
+      </c>
+      <c r="O308" s="19">
+        <f t="shared" si="49"/>
+        <v>50</v>
+      </c>
+      <c r="P308" s="19">
+        <f t="shared" si="50"/>
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="T308">
+        <v>64</v>
+      </c>
+      <c r="U308">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="309" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B309" s="21">
+        <v>46134</v>
+      </c>
+      <c r="C309">
+        <v>51</v>
+      </c>
+      <c r="D309">
+        <v>41</v>
+      </c>
+      <c r="E309">
+        <v>56</v>
+      </c>
+      <c r="F309">
+        <v>52</v>
+      </c>
+      <c r="G309">
+        <v>46</v>
+      </c>
+      <c r="H309">
+        <v>41</v>
+      </c>
+      <c r="I309">
+        <v>51</v>
+      </c>
+      <c r="J309">
+        <v>32</v>
+      </c>
+      <c r="K309">
+        <v>48</v>
+      </c>
+      <c r="L309">
+        <v>45</v>
+      </c>
+      <c r="M309">
+        <v>56</v>
+      </c>
+      <c r="N309">
+        <v>42</v>
+      </c>
+      <c r="O309" s="19">
+        <f t="shared" si="49"/>
+        <v>47</v>
+      </c>
+      <c r="P309" s="19">
+        <f t="shared" si="50"/>
+        <v>7.89</v>
+      </c>
+      <c r="T309">
+        <v>62</v>
+      </c>
+      <c r="U309">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="310" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B310" s="32"/>
+      <c r="C310" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="D310" s="62"/>
+      <c r="E310" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="F310" s="62"/>
+      <c r="G310" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="H305" s="62"/>
-      <c r="I305" s="62" t="s">
+      <c r="H310" s="62"/>
+      <c r="I310" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="J305" s="62"/>
-      <c r="K305" s="62" t="s">
+      <c r="J310" s="62"/>
+      <c r="K310" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="L305" s="62"/>
-      <c r="M305" s="62" t="s">
+      <c r="L310" s="62"/>
+      <c r="M310" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="N305" s="63"/>
-      <c r="O305" s="47"/>
-      <c r="P305" s="48"/>
-      <c r="T305" s="59" t="s">
+      <c r="N310" s="63"/>
+      <c r="O310" s="47"/>
+      <c r="P310" s="48"/>
+      <c r="T310" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="U305" s="60"/>
-    </row>
-    <row r="306" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C306">
-        <v>29.34</v>
-      </c>
-      <c r="D306">
-        <v>30.21</v>
-      </c>
-      <c r="E306">
-        <v>24.61</v>
-      </c>
-      <c r="F306" s="14">
-        <v>27.28</v>
-      </c>
-      <c r="G306" s="14">
-        <v>22.28</v>
-      </c>
-      <c r="H306" s="14">
-        <v>23.15</v>
-      </c>
-      <c r="I306" s="14">
-        <v>28.87</v>
-      </c>
-      <c r="J306" s="14">
-        <v>28.82</v>
-      </c>
-      <c r="K306" s="14">
-        <v>26.2</v>
-      </c>
-      <c r="L306" s="14">
-        <v>28.06</v>
-      </c>
-      <c r="M306" s="14">
-        <v>28.45</v>
-      </c>
-      <c r="N306" s="15">
-        <v>30.56</v>
-      </c>
-      <c r="T306">
-        <v>27.27</v>
-      </c>
-      <c r="U306">
-        <v>27.18</v>
-      </c>
+      <c r="U310" s="60"/>
+    </row>
+    <row r="311" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="F311" s="14"/>
+      <c r="G311" s="14"/>
+      <c r="H311" s="14"/>
+      <c r="I311" s="14"/>
+      <c r="J311" s="14"/>
+      <c r="K311" s="14"/>
+      <c r="L311" s="14"/>
+      <c r="M311" s="14"/>
+      <c r="N311" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="T305:U305"/>
+    <mergeCell ref="T310:U310"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C305:D305"/>
-    <mergeCell ref="I305:J305"/>
-    <mergeCell ref="E305:F305"/>
-    <mergeCell ref="G305:H305"/>
-    <mergeCell ref="K305:L305"/>
-    <mergeCell ref="M305:N305"/>
+    <mergeCell ref="C310:D310"/>
+    <mergeCell ref="I310:J310"/>
+    <mergeCell ref="E310:F310"/>
+    <mergeCell ref="G310:H310"/>
+    <mergeCell ref="K310:L310"/>
+    <mergeCell ref="M310:N310"/>
   </mergeCells>
-  <conditionalFormatting sqref="C98:N271 T142:U271">
-    <cfRule type="expression" dxfId="16" priority="8">
-      <formula>ABS(C98-$A98)&lt;=5</formula>
+  <conditionalFormatting sqref="C311:N311 T311:U311">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+      <formula>$O$310+$P$310</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="9">
-      <formula>ABS(C98-$A98)&lt;=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10">
-      <formula>ABS(C98-$A98)&lt;=15</formula>
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="between">
+      <formula>$O$310-$P$310</formula>
+      <formula>"$O$264+$P$264"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R271">
+  <conditionalFormatting sqref="R3:R291">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -57702,21 +58656,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T306:U306">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="T311:U311 C311:N311">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+      <formula>$O$310-$P$310</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T311:U311">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C306:N306 T306 U306">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="lessThan">
-      <formula>$O$305-$P$305</formula>
+  <conditionalFormatting sqref="C98:N291 T142:U291">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>ABS(C98-$A98)&lt;=5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
-      <formula>$O$305+$P$305</formula>
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>ABS(C98-$A98)&lt;=10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="between">
-      <formula>$O$305-$P$305</formula>
-      <formula>"$O$264+$P$264"</formula>
+    <cfRule type="expression" dxfId="2" priority="10">
+      <formula>ABS(C98-$A98)&lt;=15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -83759,10 +84717,10 @@
     <mergeCell ref="C1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="C24:Y498">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>ABS(C24-$A24) &lt;= 10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>ABS(C24-$A24) &lt;= 15</formula>
     </cfRule>
   </conditionalFormatting>
